--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8589FC-558D-49A9-B053-9E057D702821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2E7D78-865E-4102-9C11-BAFC462EEF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8301,7 +8301,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>348</v>
+        <v>17</v>
       </c>
       <c r="D16" s="6">
         <v>15</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2E7D78-865E-4102-9C11-BAFC462EEF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB270BC9-40DD-4753-B416-B3B16DB8C069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8120" uniqueCount="2315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8117" uniqueCount="2314">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -5146,9 +5146,6 @@
   </si>
   <si>
     <t>23-4-2026</t>
-  </si>
-  <si>
-    <t>4-5-206</t>
   </si>
   <si>
     <t>هيتر 110سم 380 فولت</t>
@@ -36518,7 +36515,7 @@
     </row>
     <row r="800" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A800" s="40">
-        <v>1105001</v>
+        <v>11105001</v>
       </c>
       <c r="B800" s="6" t="s">
         <v>1348</v>
@@ -37206,15 +37203,17 @@
         <v>1379</v>
       </c>
       <c r="C819" s="6" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D819" s="6">
-        <v>133</v>
-      </c>
-      <c r="E819" s="6"/>
+        <v>1702.4</v>
+      </c>
+      <c r="E819" s="6">
+        <v>45.61</v>
+      </c>
       <c r="F819" s="46">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>77646.464000000007</v>
       </c>
       <c r="G819" s="6">
         <v>706</v>
@@ -46580,8 +46579,8 @@
       <c r="J1079" s="6">
         <v>6342</v>
       </c>
-      <c r="K1079" s="12" t="s">
-        <v>1703</v>
+      <c r="K1079" s="12">
+        <v>46117</v>
       </c>
     </row>
     <row r="1080" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -46616,8 +46615,8 @@
       <c r="J1080" s="6">
         <v>6342</v>
       </c>
-      <c r="K1080" s="12" t="s">
-        <v>1703</v>
+      <c r="K1080" s="12">
+        <v>46117</v>
       </c>
     </row>
     <row r="1081" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -46625,7 +46624,7 @@
         <v>1314</v>
       </c>
       <c r="B1081" s="6" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="C1081" s="6" t="s">
         <v>17</v>
@@ -46652,16 +46651,16 @@
       <c r="J1081" s="6">
         <v>6342</v>
       </c>
-      <c r="K1081" s="12" t="s">
-        <v>1703</v>
+      <c r="K1081" s="12">
+        <v>46117</v>
       </c>
     </row>
     <row r="1082" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1082" s="31" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1082" s="6" t="s">
         <v>1705</v>
-      </c>
-      <c r="B1082" s="6" t="s">
-        <v>1706</v>
       </c>
       <c r="C1082" s="13" t="s">
         <v>17</v>
@@ -46683,7 +46682,7 @@
         <v>1702</v>
       </c>
       <c r="I1082" s="6" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="J1082" s="6">
         <v>6343</v>
@@ -46697,7 +46696,7 @@
         <v>938</v>
       </c>
       <c r="B1083" s="26" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C1083" s="19" t="s">
         <v>40</v>
@@ -46716,7 +46715,7 @@
         <v>59846</v>
       </c>
       <c r="H1083" s="27" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="I1083" s="19" t="s">
         <v>602</v>
@@ -46730,10 +46729,10 @@
     </row>
     <row r="1084" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1084" s="35" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1084" s="18" t="s">
         <v>1710</v>
-      </c>
-      <c r="B1084" s="18" t="s">
-        <v>1711</v>
       </c>
       <c r="C1084" s="20" t="s">
         <v>40</v>
@@ -46769,7 +46768,7 @@
         <v>1600</v>
       </c>
       <c r="B1085" s="18" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C1085" s="19" t="s">
         <v>40</v>
@@ -46805,7 +46804,7 @@
         <v>201</v>
       </c>
       <c r="B1086" s="18" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C1086" s="19" t="s">
         <v>40</v>
@@ -46824,7 +46823,7 @@
         <v>59846</v>
       </c>
       <c r="H1086" s="27" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="I1086" s="19" t="s">
         <v>602</v>
@@ -46838,10 +46837,10 @@
     </row>
     <row r="1087" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1087" s="35" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B1087" s="18" t="s">
         <v>1715</v>
-      </c>
-      <c r="B1087" s="18" t="s">
-        <v>1716</v>
       </c>
       <c r="C1087" s="19" t="s">
         <v>40</v>
@@ -46860,7 +46859,7 @@
         <v>59846</v>
       </c>
       <c r="H1087" s="27" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="I1087" s="19" t="s">
         <v>602</v>
@@ -46877,7 +46876,7 @@
         <v>979</v>
       </c>
       <c r="B1088" s="18" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="C1088" s="19" t="s">
         <v>40</v>
@@ -46896,7 +46895,7 @@
         <v>59846</v>
       </c>
       <c r="H1088" s="27" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="I1088" s="19" t="s">
         <v>602</v>
@@ -46910,10 +46909,10 @@
     </row>
     <row r="1089" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1089" s="35" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B1089" s="18" t="s">
         <v>1720</v>
-      </c>
-      <c r="B1089" s="18" t="s">
-        <v>1721</v>
       </c>
       <c r="C1089" s="19" t="s">
         <v>40</v>
@@ -46932,7 +46931,7 @@
         <v>59846</v>
       </c>
       <c r="H1089" s="27" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="I1089" s="19" t="s">
         <v>602</v>
@@ -46949,7 +46948,7 @@
         <v>427</v>
       </c>
       <c r="B1090" s="6" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="C1090" s="6" t="s">
         <v>17</v>
@@ -46982,10 +46981,10 @@
     </row>
     <row r="1091" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1091" s="31" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1091" s="17" t="s">
         <v>1724</v>
-      </c>
-      <c r="B1091" s="17" t="s">
-        <v>1725</v>
       </c>
       <c r="C1091" s="6" t="s">
         <v>17</v>
@@ -47021,7 +47020,7 @@
         <v>581</v>
       </c>
       <c r="B1092" s="6" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="C1092" s="6" t="s">
         <v>17</v>
@@ -47054,10 +47053,10 @@
     </row>
     <row r="1093" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1093" s="31" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1093" s="6" t="s">
         <v>1727</v>
-      </c>
-      <c r="B1093" s="6" t="s">
-        <v>1728</v>
       </c>
       <c r="C1093" s="6" t="s">
         <v>17</v>
@@ -47090,10 +47089,10 @@
     </row>
     <row r="1094" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1094" s="31" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1094" s="6" t="s">
         <v>1729</v>
-      </c>
-      <c r="B1094" s="6" t="s">
-        <v>1730</v>
       </c>
       <c r="C1094" s="6" t="s">
         <v>17</v>
@@ -47126,10 +47125,10 @@
     </row>
     <row r="1095" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1095" s="31" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B1095" s="6" t="s">
         <v>1731</v>
-      </c>
-      <c r="B1095" s="6" t="s">
-        <v>1732</v>
       </c>
       <c r="C1095" s="6" t="s">
         <v>17</v>
@@ -47163,7 +47162,7 @@
     <row r="1096" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1096" s="41"/>
       <c r="B1096" s="6" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="C1096" s="6" t="s">
         <v>17</v>
@@ -47196,10 +47195,10 @@
     </row>
     <row r="1097" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1097" s="31" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B1097" s="6" t="s">
         <v>1734</v>
-      </c>
-      <c r="B1097" s="6" t="s">
-        <v>1735</v>
       </c>
       <c r="C1097" s="6" t="s">
         <v>17</v>
@@ -47232,10 +47231,10 @@
     </row>
     <row r="1098" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1098" s="31" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B1098" s="6" t="s">
         <v>1736</v>
-      </c>
-      <c r="B1098" s="6" t="s">
-        <v>1737</v>
       </c>
       <c r="C1098" s="6" t="s">
         <v>17</v>
@@ -47304,10 +47303,10 @@
     </row>
     <row r="1100" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1100" s="31" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1100" s="6" t="s">
         <v>1738</v>
-      </c>
-      <c r="B1100" s="6" t="s">
-        <v>1739</v>
       </c>
       <c r="C1100" s="6" t="s">
         <v>17</v>
@@ -47340,10 +47339,10 @@
     </row>
     <row r="1101" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1101" s="32" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B1101" s="6" t="s">
         <v>1740</v>
-      </c>
-      <c r="B1101" s="6" t="s">
-        <v>1741</v>
       </c>
       <c r="C1101" s="6" t="s">
         <v>17</v>
@@ -47376,10 +47375,10 @@
     </row>
     <row r="1102" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1102" s="32" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1102" s="6" t="s">
         <v>1742</v>
-      </c>
-      <c r="B1102" s="6" t="s">
-        <v>1743</v>
       </c>
       <c r="C1102" s="6" t="s">
         <v>17</v>
@@ -47412,10 +47411,10 @@
     </row>
     <row r="1103" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1103" s="31" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1103" s="6" t="s">
         <v>1744</v>
-      </c>
-      <c r="B1103" s="6" t="s">
-        <v>1745</v>
       </c>
       <c r="C1103" s="6" t="s">
         <v>17</v>
@@ -47448,10 +47447,10 @@
     </row>
     <row r="1104" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1104" s="31" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1104" s="6" t="s">
         <v>1746</v>
-      </c>
-      <c r="B1104" s="6" t="s">
-        <v>1747</v>
       </c>
       <c r="C1104" s="6" t="s">
         <v>17</v>
@@ -47484,10 +47483,10 @@
     </row>
     <row r="1105" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1105" s="31" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1105" s="6" t="s">
         <v>1748</v>
-      </c>
-      <c r="B1105" s="6" t="s">
-        <v>1749</v>
       </c>
       <c r="C1105" s="6" t="s">
         <v>17</v>
@@ -47523,7 +47522,7 @@
         <v>217</v>
       </c>
       <c r="B1106" s="6" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="C1106" s="6" t="s">
         <v>17</v>
@@ -47542,7 +47541,7 @@
         <v>93</v>
       </c>
       <c r="H1106" s="12" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="I1106" s="6" t="s">
         <v>346</v>
@@ -47578,7 +47577,7 @@
         <v>93</v>
       </c>
       <c r="H1107" s="12" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="I1107" s="6" t="s">
         <v>346</v>
@@ -47595,7 +47594,7 @@
         <v>443</v>
       </c>
       <c r="B1108" s="6" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="C1108" s="6" t="s">
         <v>17</v>
@@ -47614,7 +47613,7 @@
         <v>93</v>
       </c>
       <c r="H1108" s="12" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="I1108" s="6" t="s">
         <v>346</v>
@@ -47631,7 +47630,7 @@
         <v>340</v>
       </c>
       <c r="B1109" s="6" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="C1109" s="6" t="s">
         <v>17</v>
@@ -47650,7 +47649,7 @@
         <v>93</v>
       </c>
       <c r="H1109" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1109" s="6" t="s">
         <v>346</v>
@@ -47664,10 +47663,10 @@
     </row>
     <row r="1110" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1110" s="32" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1110" s="6" t="s">
         <v>1755</v>
-      </c>
-      <c r="B1110" s="6" t="s">
-        <v>1756</v>
       </c>
       <c r="C1110" s="6" t="s">
         <v>17</v>
@@ -47686,7 +47685,7 @@
         <v>93</v>
       </c>
       <c r="H1110" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1110" s="6" t="s">
         <v>346</v>
@@ -47700,10 +47699,10 @@
     </row>
     <row r="1111" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1111" s="31" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B1111" s="6" t="s">
         <v>1757</v>
-      </c>
-      <c r="B1111" s="6" t="s">
-        <v>1758</v>
       </c>
       <c r="C1111" s="6" t="s">
         <v>17</v>
@@ -47722,7 +47721,7 @@
         <v>713</v>
       </c>
       <c r="H1111" s="12" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="I1111" s="6" t="s">
         <v>37</v>
@@ -47736,10 +47735,10 @@
     </row>
     <row r="1112" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1112" s="31" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B1112" s="6" t="s">
         <v>1760</v>
-      </c>
-      <c r="B1112" s="6" t="s">
-        <v>1761</v>
       </c>
       <c r="C1112" s="6" t="s">
         <v>17</v>
@@ -47758,7 +47757,7 @@
         <v>713</v>
       </c>
       <c r="H1112" s="12" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="I1112" s="6" t="s">
         <v>37</v>
@@ -47772,10 +47771,10 @@
     </row>
     <row r="1113" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1113" s="31" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B1113" s="6" t="s">
         <v>1762</v>
-      </c>
-      <c r="B1113" s="6" t="s">
-        <v>1763</v>
       </c>
       <c r="C1113" s="6" t="s">
         <v>17</v>
@@ -47794,7 +47793,7 @@
         <v>6350</v>
       </c>
       <c r="H1113" s="12" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="I1113" s="6" t="s">
         <v>445</v>
@@ -47811,7 +47810,7 @@
         <v>286</v>
       </c>
       <c r="B1114" s="6" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="C1114" s="6" t="s">
         <v>17</v>
@@ -47830,16 +47829,16 @@
         <v>26</v>
       </c>
       <c r="H1114" s="12" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="I1114" s="6" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="J1114" s="6">
         <v>6351</v>
       </c>
       <c r="K1114" s="12" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1115" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -47847,7 +47846,7 @@
         <v>286</v>
       </c>
       <c r="B1115" s="6" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="C1115" s="6" t="s">
         <v>17</v>
@@ -47875,15 +47874,15 @@
         <v>6358</v>
       </c>
       <c r="K1115" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1116" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1116" s="31" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1116" s="6" t="s">
         <v>1769</v>
-      </c>
-      <c r="B1116" s="6" t="s">
-        <v>1770</v>
       </c>
       <c r="C1116" s="6" t="s">
         <v>17</v>
@@ -47911,15 +47910,15 @@
         <v>6359</v>
       </c>
       <c r="K1116" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1117" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1117" s="31" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1117" s="6" t="s">
         <v>1771</v>
-      </c>
-      <c r="B1117" s="6" t="s">
-        <v>1772</v>
       </c>
       <c r="C1117" s="6" t="s">
         <v>17</v>
@@ -47947,15 +47946,15 @@
         <v>6359</v>
       </c>
       <c r="K1117" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1118" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1118" s="32" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1118" s="6" t="s">
         <v>1773</v>
-      </c>
-      <c r="B1118" s="6" t="s">
-        <v>1774</v>
       </c>
       <c r="C1118" s="6" t="s">
         <v>17</v>
@@ -47974,7 +47973,7 @@
         <v>142</v>
       </c>
       <c r="H1118" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1118" s="6" t="s">
         <v>36</v>
@@ -47983,7 +47982,7 @@
         <v>6360</v>
       </c>
       <c r="K1118" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1119" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -47991,7 +47990,7 @@
         <v>321</v>
       </c>
       <c r="B1119" s="6" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C1119" s="6" t="s">
         <v>17</v>
@@ -48010,7 +48009,7 @@
         <v>142</v>
       </c>
       <c r="H1119" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1119" s="6" t="s">
         <v>36</v>
@@ -48019,15 +48018,15 @@
         <v>6360</v>
       </c>
       <c r="K1119" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1120" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1120" s="32" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1120" s="6" t="s">
         <v>1776</v>
-      </c>
-      <c r="B1120" s="6" t="s">
-        <v>1777</v>
       </c>
       <c r="C1120" s="6" t="s">
         <v>17</v>
@@ -48046,7 +48045,7 @@
         <v>143</v>
       </c>
       <c r="H1120" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1120" s="6" t="s">
         <v>36</v>
@@ -48055,7 +48054,7 @@
         <v>6361</v>
       </c>
       <c r="K1120" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1121" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48063,7 +48062,7 @@
         <v>303</v>
       </c>
       <c r="B1121" s="6" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C1121" s="6" t="s">
         <v>17</v>
@@ -48082,7 +48081,7 @@
         <v>94</v>
       </c>
       <c r="H1121" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1121" s="6" t="s">
         <v>346</v>
@@ -48091,13 +48090,13 @@
         <v>6362</v>
       </c>
       <c r="K1121" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1122" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1122" s="31"/>
       <c r="B1122" s="6" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C1122" s="6" t="s">
         <v>17</v>
@@ -48116,7 +48115,7 @@
         <v>94</v>
       </c>
       <c r="H1122" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1122" s="6" t="s">
         <v>346</v>
@@ -48125,7 +48124,7 @@
         <v>6362</v>
       </c>
       <c r="K1122" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1123" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48133,7 +48132,7 @@
         <v>333</v>
       </c>
       <c r="B1123" s="6" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1123" s="6" t="s">
         <v>17</v>
@@ -48152,7 +48151,7 @@
         <v>94</v>
       </c>
       <c r="H1123" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1123" s="6" t="s">
         <v>346</v>
@@ -48161,7 +48160,7 @@
         <v>6362</v>
       </c>
       <c r="K1123" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1124" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48169,7 +48168,7 @@
         <v>269</v>
       </c>
       <c r="B1124" s="6" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="C1124" s="6" t="s">
         <v>17</v>
@@ -48188,7 +48187,7 @@
         <v>94</v>
       </c>
       <c r="H1124" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1124" s="6" t="s">
         <v>346</v>
@@ -48197,7 +48196,7 @@
         <v>6362</v>
       </c>
       <c r="K1124" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1125" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48224,7 +48223,7 @@
         <v>94</v>
       </c>
       <c r="H1125" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1125" s="6" t="s">
         <v>346</v>
@@ -48233,7 +48232,7 @@
         <v>6362</v>
       </c>
       <c r="K1125" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1126" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48241,7 +48240,7 @@
         <v>323</v>
       </c>
       <c r="B1126" s="6" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C1126" s="6" t="s">
         <v>17</v>
@@ -48260,7 +48259,7 @@
         <v>14057</v>
       </c>
       <c r="H1126" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1126" s="6" t="s">
         <v>116</v>
@@ -48269,7 +48268,7 @@
         <v>6363</v>
       </c>
       <c r="K1126" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1127" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48296,7 +48295,7 @@
         <v>14057</v>
       </c>
       <c r="H1127" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1127" s="6" t="s">
         <v>116</v>
@@ -48305,7 +48304,7 @@
         <v>6363</v>
       </c>
       <c r="K1127" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1128" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48332,7 +48331,7 @@
         <v>14057</v>
       </c>
       <c r="H1128" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1128" s="6" t="s">
         <v>116</v>
@@ -48341,7 +48340,7 @@
         <v>6363</v>
       </c>
       <c r="K1128" s="12" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1129" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48349,7 +48348,7 @@
         <v>289</v>
       </c>
       <c r="B1129" s="6" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C1129" s="6" t="s">
         <v>17</v>
@@ -48368,7 +48367,7 @@
         <v>2464</v>
       </c>
       <c r="H1129" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1129" s="6" t="s">
         <v>799</v>
@@ -48377,7 +48376,7 @@
         <v>6364</v>
       </c>
       <c r="K1129" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1130" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48385,7 +48384,7 @@
         <v>560</v>
       </c>
       <c r="B1130" s="6" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="C1130" s="6" t="s">
         <v>17</v>
@@ -48404,7 +48403,7 @@
         <v>2464</v>
       </c>
       <c r="H1130" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1130" s="6" t="s">
         <v>799</v>
@@ -48413,7 +48412,7 @@
         <v>6364</v>
       </c>
       <c r="K1130" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1131" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48421,7 +48420,7 @@
         <v>562</v>
       </c>
       <c r="B1131" s="6" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="C1131" s="6" t="s">
         <v>17</v>
@@ -48440,7 +48439,7 @@
         <v>2464</v>
       </c>
       <c r="H1131" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1131" s="6" t="s">
         <v>799</v>
@@ -48449,15 +48448,15 @@
         <v>6364</v>
       </c>
       <c r="K1131" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1132" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1132" s="32" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1132" s="6" t="s">
         <v>1787</v>
-      </c>
-      <c r="B1132" s="6" t="s">
-        <v>1788</v>
       </c>
       <c r="C1132" s="6" t="s">
         <v>17</v>
@@ -48476,7 +48475,7 @@
         <v>2464</v>
       </c>
       <c r="H1132" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1132" s="6" t="s">
         <v>799</v>
@@ -48485,7 +48484,7 @@
         <v>6364</v>
       </c>
       <c r="K1132" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1133" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48493,7 +48492,7 @@
         <v>1437</v>
       </c>
       <c r="B1133" s="6" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C1133" s="6" t="s">
         <v>17</v>
@@ -48512,7 +48511,7 @@
         <v>2464</v>
       </c>
       <c r="H1133" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1133" s="6" t="s">
         <v>799</v>
@@ -48521,7 +48520,7 @@
         <v>6364</v>
       </c>
       <c r="K1133" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1134" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48529,7 +48528,7 @@
         <v>721</v>
       </c>
       <c r="B1134" s="6" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="C1134" s="6" t="s">
         <v>17</v>
@@ -48548,7 +48547,7 @@
         <v>2464</v>
       </c>
       <c r="H1134" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1134" s="6" t="s">
         <v>799</v>
@@ -48557,15 +48556,15 @@
         <v>6364</v>
       </c>
       <c r="K1134" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1135" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1135" s="34" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1135" s="6" t="s">
         <v>1791</v>
-      </c>
-      <c r="B1135" s="6" t="s">
-        <v>1792</v>
       </c>
       <c r="C1135" s="6" t="s">
         <v>17</v>
@@ -48584,7 +48583,7 @@
         <v>2464</v>
       </c>
       <c r="H1135" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1135" s="6" t="s">
         <v>799</v>
@@ -48593,7 +48592,7 @@
         <v>6364</v>
       </c>
       <c r="K1135" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1136" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48620,7 +48619,7 @@
         <v>2464</v>
       </c>
       <c r="H1136" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1136" s="6" t="s">
         <v>799</v>
@@ -48629,7 +48628,7 @@
         <v>6364</v>
       </c>
       <c r="K1136" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1137" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48656,7 +48655,7 @@
         <v>2464</v>
       </c>
       <c r="H1137" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1137" s="6" t="s">
         <v>799</v>
@@ -48665,7 +48664,7 @@
         <v>6364</v>
       </c>
       <c r="K1137" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1138" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48692,7 +48691,7 @@
         <v>2464</v>
       </c>
       <c r="H1138" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1138" s="6" t="s">
         <v>799</v>
@@ -48701,7 +48700,7 @@
         <v>6364</v>
       </c>
       <c r="K1138" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1139" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48709,7 +48708,7 @@
         <v>287</v>
       </c>
       <c r="B1139" s="6" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="C1139" s="6" t="s">
         <v>17</v>
@@ -48728,7 +48727,7 @@
         <v>2464</v>
       </c>
       <c r="H1139" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1139" s="6" t="s">
         <v>799</v>
@@ -48737,7 +48736,7 @@
         <v>6364</v>
       </c>
       <c r="K1139" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1140" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48764,7 +48763,7 @@
         <v>2464</v>
       </c>
       <c r="H1140" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1140" s="6" t="s">
         <v>799</v>
@@ -48773,7 +48772,7 @@
         <v>6364</v>
       </c>
       <c r="K1140" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1141" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48800,7 +48799,7 @@
         <v>2464</v>
       </c>
       <c r="H1141" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1141" s="6" t="s">
         <v>799</v>
@@ -48809,7 +48808,7 @@
         <v>6365</v>
       </c>
       <c r="K1141" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1142" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48817,7 +48816,7 @@
         <v>1278</v>
       </c>
       <c r="B1142" s="6" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="C1142" s="6" t="s">
         <v>17</v>
@@ -48836,7 +48835,7 @@
         <v>2464</v>
       </c>
       <c r="H1142" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1142" s="6" t="s">
         <v>799</v>
@@ -48845,7 +48844,7 @@
         <v>6365</v>
       </c>
       <c r="K1142" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1143" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48853,7 +48852,7 @@
         <v>301</v>
       </c>
       <c r="B1143" s="6" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="C1143" s="6" t="s">
         <v>17</v>
@@ -48872,7 +48871,7 @@
         <v>2464</v>
       </c>
       <c r="H1143" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1143" s="6" t="s">
         <v>799</v>
@@ -48881,7 +48880,7 @@
         <v>6365</v>
       </c>
       <c r="K1143" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1144" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48908,7 +48907,7 @@
         <v>2464</v>
       </c>
       <c r="H1144" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="I1144" s="6" t="s">
         <v>799</v>
@@ -48917,7 +48916,7 @@
         <v>6365</v>
       </c>
       <c r="K1144" s="12" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1145" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48925,7 +48924,7 @@
         <v>723</v>
       </c>
       <c r="B1145" s="6" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C1145" s="6" t="s">
         <v>17</v>
@@ -48944,7 +48943,7 @@
         <v>2468</v>
       </c>
       <c r="H1145" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1145" s="6" t="s">
         <v>799</v>
@@ -48961,7 +48960,7 @@
         <v>286</v>
       </c>
       <c r="B1146" s="6" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="C1146" s="6" t="s">
         <v>17</v>
@@ -48980,7 +48979,7 @@
         <v>2468</v>
       </c>
       <c r="H1146" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1146" s="6" t="s">
         <v>799</v>
@@ -49016,7 +49015,7 @@
         <v>2468</v>
       </c>
       <c r="H1147" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1147" s="6" t="s">
         <v>799</v>
@@ -49030,10 +49029,10 @@
     </row>
     <row r="1148" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1148" s="31" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B1148" s="6" t="s">
         <v>1798</v>
-      </c>
-      <c r="B1148" s="6" t="s">
-        <v>1799</v>
       </c>
       <c r="C1148" s="6" t="s">
         <v>17</v>
@@ -49052,7 +49051,7 @@
         <v>2468</v>
       </c>
       <c r="H1148" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1148" s="6" t="s">
         <v>799</v>
@@ -49066,10 +49065,10 @@
     </row>
     <row r="1149" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1149" s="32" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1149" s="6" t="s">
         <v>1800</v>
-      </c>
-      <c r="B1149" s="6" t="s">
-        <v>1801</v>
       </c>
       <c r="C1149" s="6" t="s">
         <v>17</v>
@@ -49088,7 +49087,7 @@
         <v>2468</v>
       </c>
       <c r="H1149" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1149" s="6" t="s">
         <v>799</v>
@@ -49124,7 +49123,7 @@
         <v>2468</v>
       </c>
       <c r="H1150" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1150" s="6" t="s">
         <v>799</v>
@@ -49160,7 +49159,7 @@
         <v>2468</v>
       </c>
       <c r="H1151" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1151" s="6" t="s">
         <v>799</v>
@@ -49177,7 +49176,7 @@
         <v>907</v>
       </c>
       <c r="B1152" s="6" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="C1152" s="6" t="s">
         <v>17</v>
@@ -49196,7 +49195,7 @@
         <v>2468</v>
       </c>
       <c r="H1152" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1152" s="6" t="s">
         <v>799</v>
@@ -49213,7 +49212,7 @@
         <v>295</v>
       </c>
       <c r="B1153" s="6" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="C1153" s="6" t="s">
         <v>17</v>
@@ -49232,7 +49231,7 @@
         <v>2468</v>
       </c>
       <c r="H1153" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1153" s="6" t="s">
         <v>799</v>
@@ -49249,7 +49248,7 @@
         <v>1278</v>
       </c>
       <c r="B1154" s="6" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C1154" s="6" t="s">
         <v>17</v>
@@ -49268,7 +49267,7 @@
         <v>2472</v>
       </c>
       <c r="H1154" s="12" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="I1154" s="6" t="s">
         <v>799</v>
@@ -49285,7 +49284,7 @@
         <v>372</v>
       </c>
       <c r="B1155" s="6" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="C1155" s="6" t="s">
         <v>17</v>
@@ -49318,10 +49317,10 @@
     </row>
     <row r="1156" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1156" s="33" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B1156" s="6" t="s">
         <v>1807</v>
-      </c>
-      <c r="B1156" s="6" t="s">
-        <v>1808</v>
       </c>
       <c r="C1156" s="6" t="s">
         <v>17</v>
@@ -49357,7 +49356,7 @@
         <v>405</v>
       </c>
       <c r="B1157" s="6" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C1157" s="6" t="s">
         <v>17</v>
@@ -49501,7 +49500,7 @@
         <v>255</v>
       </c>
       <c r="B1161" s="6" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="C1161" s="6" t="s">
         <v>17</v>
@@ -49537,7 +49536,7 @@
         <v>206</v>
       </c>
       <c r="B1162" s="6" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="C1162" s="6" t="s">
         <v>17</v>
@@ -49645,7 +49644,7 @@
         <v>355</v>
       </c>
       <c r="B1165" s="6" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1165" s="6" t="s">
         <v>17</v>
@@ -49825,7 +49824,7 @@
         <v>756</v>
       </c>
       <c r="B1170" s="6" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="C1170" s="6" t="s">
         <v>17</v>
@@ -49933,7 +49932,7 @@
         <v>401</v>
       </c>
       <c r="B1173" s="6" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C1173" s="6" t="s">
         <v>17</v>
@@ -50002,10 +50001,10 @@
     </row>
     <row r="1175" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1175" s="32" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1175" s="6" t="s">
         <v>1815</v>
-      </c>
-      <c r="B1175" s="6" t="s">
-        <v>1816</v>
       </c>
       <c r="C1175" s="6" t="s">
         <v>17</v>
@@ -50077,7 +50076,7 @@
         <v>765</v>
       </c>
       <c r="B1177" s="6" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="C1177" s="6" t="s">
         <v>17</v>
@@ -50149,7 +50148,7 @@
         <v>421</v>
       </c>
       <c r="B1179" s="6" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="C1179" s="6" t="s">
         <v>17</v>
@@ -50185,7 +50184,7 @@
         <v>777</v>
       </c>
       <c r="B1180" s="6" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C1180" s="6" t="s">
         <v>17</v>
@@ -50257,7 +50256,7 @@
         <v>395</v>
       </c>
       <c r="B1182" s="6" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="C1182" s="6" t="s">
         <v>17</v>
@@ -50290,10 +50289,10 @@
     </row>
     <row r="1183" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1183" s="34" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1183" s="6" t="s">
         <v>1821</v>
-      </c>
-      <c r="B1183" s="6" t="s">
-        <v>1822</v>
       </c>
       <c r="C1183" s="6" t="s">
         <v>17</v>
@@ -50326,10 +50325,10 @@
     </row>
     <row r="1184" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1184" s="34" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1184" s="6" t="s">
         <v>1823</v>
-      </c>
-      <c r="B1184" s="6" t="s">
-        <v>1824</v>
       </c>
       <c r="C1184" s="6" t="s">
         <v>17</v>
@@ -50362,10 +50361,10 @@
     </row>
     <row r="1185" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1185" s="34" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1185" s="6" t="s">
         <v>1825</v>
-      </c>
-      <c r="B1185" s="6" t="s">
-        <v>1826</v>
       </c>
       <c r="C1185" s="6" t="s">
         <v>17</v>
@@ -50398,10 +50397,10 @@
     </row>
     <row r="1186" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1186" s="34" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1186" s="6" t="s">
         <v>1827</v>
-      </c>
-      <c r="B1186" s="6" t="s">
-        <v>1828</v>
       </c>
       <c r="C1186" s="6" t="s">
         <v>17</v>
@@ -50437,7 +50436,7 @@
         <v>210</v>
       </c>
       <c r="B1187" s="6" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="C1187" s="6" t="s">
         <v>17</v>
@@ -50456,7 +50455,7 @@
         <v>5024</v>
       </c>
       <c r="H1187" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1187" s="6" t="s">
         <v>66</v>
@@ -50470,10 +50469,10 @@
     </row>
     <row r="1188" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1188" s="31" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1188" s="6" t="s">
         <v>1831</v>
-      </c>
-      <c r="B1188" s="6" t="s">
-        <v>1832</v>
       </c>
       <c r="C1188" s="6" t="s">
         <v>17</v>
@@ -50492,7 +50491,7 @@
         <v>5024</v>
       </c>
       <c r="H1188" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1188" s="6" t="s">
         <v>66</v>
@@ -50528,7 +50527,7 @@
         <v>5024</v>
       </c>
       <c r="H1189" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1189" s="6" t="s">
         <v>66</v>
@@ -50564,7 +50563,7 @@
         <v>5024</v>
       </c>
       <c r="H1190" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1190" s="6" t="s">
         <v>66</v>
@@ -50581,7 +50580,7 @@
         <v>316</v>
       </c>
       <c r="B1191" s="6" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="C1191" s="6" t="s">
         <v>17</v>
@@ -50600,7 +50599,7 @@
         <v>5024</v>
       </c>
       <c r="H1191" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1191" s="6" t="s">
         <v>66</v>
@@ -50614,10 +50613,10 @@
     </row>
     <row r="1192" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1192" s="31" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B1192" s="6" t="s">
         <v>1834</v>
-      </c>
-      <c r="B1192" s="6" t="s">
-        <v>1835</v>
       </c>
       <c r="C1192" s="6" t="s">
         <v>17</v>
@@ -50636,7 +50635,7 @@
         <v>5024</v>
       </c>
       <c r="H1192" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1192" s="6" t="s">
         <v>66</v>
@@ -50650,10 +50649,10 @@
     </row>
     <row r="1193" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1193" s="31" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B1193" s="6" t="s">
         <v>1836</v>
-      </c>
-      <c r="B1193" s="6" t="s">
-        <v>1837</v>
       </c>
       <c r="C1193" s="6" t="s">
         <v>17</v>
@@ -50672,7 +50671,7 @@
         <v>5024</v>
       </c>
       <c r="H1193" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1193" s="6" t="s">
         <v>66</v>
@@ -50708,7 +50707,7 @@
         <v>5024</v>
       </c>
       <c r="H1194" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1194" s="6" t="s">
         <v>66</v>
@@ -50725,7 +50724,7 @@
         <v>962</v>
       </c>
       <c r="B1195" s="6" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="C1195" s="6" t="s">
         <v>17</v>
@@ -50744,7 +50743,7 @@
         <v>5024</v>
       </c>
       <c r="H1195" s="12" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="I1195" s="6" t="s">
         <v>66</v>
@@ -50797,7 +50796,7 @@
         <v>641</v>
       </c>
       <c r="B1197" s="6" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="C1197" s="6" t="s">
         <v>17</v>
@@ -50830,10 +50829,10 @@
     </row>
     <row r="1198" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1198" s="31" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1198" s="6" t="s">
         <v>1840</v>
-      </c>
-      <c r="B1198" s="6" t="s">
-        <v>1841</v>
       </c>
       <c r="C1198" s="6" t="s">
         <v>17</v>
@@ -50869,7 +50868,7 @@
         <v>342</v>
       </c>
       <c r="B1199" s="6" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="C1199" s="6" t="s">
         <v>17</v>
@@ -50905,7 +50904,7 @@
         <v>209</v>
       </c>
       <c r="B1200" s="6" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="C1200" s="6" t="s">
         <v>17</v>
@@ -50941,7 +50940,7 @@
         <v>194</v>
       </c>
       <c r="B1201" s="6" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="C1201" s="6" t="s">
         <v>17</v>
@@ -50974,10 +50973,10 @@
     </row>
     <row r="1202" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1202" s="31" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1202" s="6" t="s">
         <v>1845</v>
-      </c>
-      <c r="B1202" s="6" t="s">
-        <v>1846</v>
       </c>
       <c r="C1202" s="6" t="s">
         <v>17</v>
@@ -51013,7 +51012,7 @@
         <v>1048</v>
       </c>
       <c r="B1203" s="6" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="C1203" s="6" t="s">
         <v>17</v>
@@ -51049,7 +51048,7 @@
         <v>217</v>
       </c>
       <c r="B1204" s="6" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="C1204" s="6" t="s">
         <v>17</v>
@@ -51082,10 +51081,10 @@
     </row>
     <row r="1205" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1205" s="32" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1205" s="6" t="s">
         <v>1849</v>
-      </c>
-      <c r="B1205" s="6" t="s">
-        <v>1850</v>
       </c>
       <c r="C1205" s="6" t="s">
         <v>17</v>
@@ -51121,7 +51120,7 @@
         <v>204</v>
       </c>
       <c r="B1206" s="6" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="C1206" s="6" t="s">
         <v>17</v>
@@ -51157,7 +51156,7 @@
         <v>259</v>
       </c>
       <c r="B1207" s="6" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="C1207" s="6" t="s">
         <v>17</v>
@@ -51176,7 +51175,7 @@
         <v>24592</v>
       </c>
       <c r="H1207" s="12" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="I1207" s="6" t="s">
         <v>75</v>
@@ -51193,7 +51192,7 @@
         <v>264</v>
       </c>
       <c r="B1208" s="6" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="C1208" s="6" t="s">
         <v>17</v>
@@ -51212,7 +51211,7 @@
         <v>829</v>
       </c>
       <c r="H1208" s="12" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="I1208" s="6" t="s">
         <v>83</v>
@@ -51226,10 +51225,10 @@
     </row>
     <row r="1209" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1209" s="31" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B1209" s="6" t="s">
         <v>1856</v>
-      </c>
-      <c r="B1209" s="6" t="s">
-        <v>1857</v>
       </c>
       <c r="C1209" s="6" t="s">
         <v>17</v>
@@ -51248,10 +51247,10 @@
         <v>31</v>
       </c>
       <c r="H1209" s="12" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="I1209" s="6" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="J1209" s="6">
         <v>6382</v>
@@ -51265,7 +51264,7 @@
         <v>1532</v>
       </c>
       <c r="B1210" s="6" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C1210" s="6" t="s">
         <v>17</v>
@@ -51284,10 +51283,10 @@
         <v>31</v>
       </c>
       <c r="H1210" s="12" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="I1210" s="6" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="J1210" s="6">
         <v>6382</v>
@@ -51301,7 +51300,7 @@
         <v>1534</v>
       </c>
       <c r="B1211" s="6" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="C1211" s="6" t="s">
         <v>17</v>
@@ -51320,10 +51319,10 @@
         <v>31</v>
       </c>
       <c r="H1211" s="12" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="I1211" s="6" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="J1211" s="6">
         <v>6382</v>
@@ -51334,10 +51333,10 @@
     </row>
     <row r="1212" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1212" s="31" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1212" s="6" t="s">
         <v>1861</v>
-      </c>
-      <c r="B1212" s="6" t="s">
-        <v>1862</v>
       </c>
       <c r="C1212" s="6" t="s">
         <v>17</v>
@@ -51356,7 +51355,7 @@
         <v>24600</v>
       </c>
       <c r="H1212" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1212" s="6" t="s">
         <v>75</v>
@@ -51371,7 +51370,7 @@
     <row r="1213" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1213" s="42"/>
       <c r="B1213" s="18" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="C1213" s="18" t="s">
         <v>17</v>
@@ -51390,7 +51389,7 @@
         <v>105</v>
       </c>
       <c r="H1213" s="21" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1213" s="18" t="s">
         <v>346</v>
@@ -51404,10 +51403,10 @@
     </row>
     <row r="1214" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1214" s="32" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B1214" s="6" t="s">
         <v>1864</v>
-      </c>
-      <c r="B1214" s="6" t="s">
-        <v>1865</v>
       </c>
       <c r="C1214" s="6" t="s">
         <v>17</v>
@@ -51426,7 +51425,7 @@
         <v>106</v>
       </c>
       <c r="H1214" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1214" s="6" t="s">
         <v>346</v>
@@ -51440,10 +51439,10 @@
     </row>
     <row r="1215" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1215" s="31" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B1215" s="6" t="s">
         <v>1866</v>
-      </c>
-      <c r="B1215" s="6" t="s">
-        <v>1867</v>
       </c>
       <c r="C1215" s="6" t="s">
         <v>17</v>
@@ -51462,7 +51461,7 @@
         <v>106</v>
       </c>
       <c r="H1215" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1215" s="6" t="s">
         <v>346</v>
@@ -51476,10 +51475,10 @@
     </row>
     <row r="1216" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1216" s="33" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1216" s="6" t="s">
         <v>1868</v>
-      </c>
-      <c r="B1216" s="6" t="s">
-        <v>1869</v>
       </c>
       <c r="C1216" s="6" t="s">
         <v>17</v>
@@ -51498,7 +51497,7 @@
         <v>106</v>
       </c>
       <c r="H1216" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1216" s="6" t="s">
         <v>346</v>
@@ -51512,10 +51511,10 @@
     </row>
     <row r="1217" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1217" s="33" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B1217" s="6" t="s">
         <v>1870</v>
-      </c>
-      <c r="B1217" s="6" t="s">
-        <v>1871</v>
       </c>
       <c r="C1217" s="6" t="s">
         <v>17</v>
@@ -51534,7 +51533,7 @@
         <v>106</v>
       </c>
       <c r="H1217" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1217" s="6" t="s">
         <v>346</v>
@@ -51548,10 +51547,10 @@
     </row>
     <row r="1218" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1218" s="33" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1218" s="6" t="s">
         <v>1872</v>
-      </c>
-      <c r="B1218" s="6" t="s">
-        <v>1873</v>
       </c>
       <c r="C1218" s="6" t="s">
         <v>17</v>
@@ -51570,7 +51569,7 @@
         <v>106</v>
       </c>
       <c r="H1218" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1218" s="6" t="s">
         <v>346</v>
@@ -51584,10 +51583,10 @@
     </row>
     <row r="1219" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1219" s="31" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1219" s="6" t="s">
         <v>1874</v>
-      </c>
-      <c r="B1219" s="6" t="s">
-        <v>1875</v>
       </c>
       <c r="C1219" s="6" t="s">
         <v>17</v>
@@ -51606,7 +51605,7 @@
         <v>106</v>
       </c>
       <c r="H1219" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1219" s="6" t="s">
         <v>346</v>
@@ -51623,7 +51622,7 @@
         <v>269</v>
       </c>
       <c r="B1220" s="6" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="C1220" s="6" t="s">
         <v>17</v>
@@ -51642,7 +51641,7 @@
         <v>106</v>
       </c>
       <c r="H1220" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1220" s="6" t="s">
         <v>346</v>
@@ -51659,7 +51658,7 @@
         <v>304</v>
       </c>
       <c r="B1221" s="6" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="C1221" s="6" t="s">
         <v>17</v>
@@ -51678,7 +51677,7 @@
         <v>106</v>
       </c>
       <c r="H1221" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1221" s="6" t="s">
         <v>346</v>
@@ -51695,7 +51694,7 @@
         <v>303</v>
       </c>
       <c r="B1222" s="6" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C1222" s="6" t="s">
         <v>17</v>
@@ -51714,7 +51713,7 @@
         <v>106</v>
       </c>
       <c r="H1222" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1222" s="6" t="s">
         <v>346</v>
@@ -51728,10 +51727,10 @@
     </row>
     <row r="1223" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1223" s="31" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B1223" s="6" t="s">
         <v>1878</v>
-      </c>
-      <c r="B1223" s="6" t="s">
-        <v>1879</v>
       </c>
       <c r="C1223" s="6" t="s">
         <v>17</v>
@@ -51750,7 +51749,7 @@
         <v>106</v>
       </c>
       <c r="H1223" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1223" s="6" t="s">
         <v>346</v>
@@ -51767,7 +51766,7 @@
         <v>270</v>
       </c>
       <c r="B1224" s="6" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="C1224" s="6" t="s">
         <v>17</v>
@@ -51786,7 +51785,7 @@
         <v>106</v>
       </c>
       <c r="H1224" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1224" s="6" t="s">
         <v>346</v>
@@ -51800,10 +51799,10 @@
     </row>
     <row r="1225" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1225" s="31" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B1225" s="6" t="s">
         <v>1881</v>
-      </c>
-      <c r="B1225" s="6" t="s">
-        <v>1882</v>
       </c>
       <c r="C1225" s="6" t="s">
         <v>17</v>
@@ -51822,7 +51821,7 @@
         <v>14159</v>
       </c>
       <c r="H1225" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1225" s="6" t="s">
         <v>116</v>
@@ -51839,7 +51838,7 @@
         <v>220</v>
       </c>
       <c r="B1226" s="6" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="C1226" s="6" t="s">
         <v>40</v>
@@ -51858,7 +51857,7 @@
         <v>14159</v>
       </c>
       <c r="H1226" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1226" s="6" t="s">
         <v>116</v>
@@ -51873,7 +51872,7 @@
     <row r="1227" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1227" s="31"/>
       <c r="B1227" s="17" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="C1227" s="6" t="s">
         <v>17</v>
@@ -51892,7 +51891,7 @@
         <v>14159</v>
       </c>
       <c r="H1227" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1227" s="6" t="s">
         <v>116</v>
@@ -51909,7 +51908,7 @@
         <v>292</v>
       </c>
       <c r="B1228" s="6" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C1228" s="6" t="s">
         <v>40</v>
@@ -51928,7 +51927,7 @@
         <v>6002130</v>
       </c>
       <c r="H1228" s="12" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="I1228" s="6" t="s">
         <v>347</v>
@@ -51945,7 +51944,7 @@
         <v>291</v>
       </c>
       <c r="B1229" s="6" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C1229" s="6" t="s">
         <v>40</v>
@@ -51964,7 +51963,7 @@
         <v>6002130</v>
       </c>
       <c r="H1229" s="12" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="I1229" s="6" t="s">
         <v>347</v>
@@ -51981,7 +51980,7 @@
         <v>1264</v>
       </c>
       <c r="B1230" s="6" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="C1230" s="6" t="s">
         <v>17</v>
@@ -52000,7 +51999,7 @@
         <v>1266</v>
       </c>
       <c r="H1230" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1230" s="6" t="s">
         <v>1180</v>
@@ -52036,7 +52035,7 @@
         <v>1266</v>
       </c>
       <c r="H1231" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1231" s="6" t="s">
         <v>1180</v>
@@ -52053,7 +52052,7 @@
         <v>1183</v>
       </c>
       <c r="B1232" s="6" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="C1232" s="6" t="s">
         <v>17</v>
@@ -52072,7 +52071,7 @@
         <v>1266</v>
       </c>
       <c r="H1232" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1232" s="6" t="s">
         <v>1180</v>
@@ -52108,7 +52107,7 @@
         <v>1266</v>
       </c>
       <c r="H1233" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1233" s="6" t="s">
         <v>1180</v>
@@ -52122,10 +52121,10 @@
     </row>
     <row r="1234" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1234" s="31" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B1234" s="6" t="s">
         <v>1892</v>
-      </c>
-      <c r="B1234" s="6" t="s">
-        <v>1893</v>
       </c>
       <c r="C1234" s="6" t="s">
         <v>40</v>
@@ -52144,7 +52143,7 @@
         <v>111</v>
       </c>
       <c r="H1234" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1234" s="6" t="s">
         <v>346</v>
@@ -52158,10 +52157,10 @@
     </row>
     <row r="1235" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1235" s="31" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1235" s="6" t="s">
         <v>1894</v>
-      </c>
-      <c r="B1235" s="6" t="s">
-        <v>1895</v>
       </c>
       <c r="C1235" s="6" t="s">
         <v>17</v>
@@ -52180,7 +52179,7 @@
         <v>111</v>
       </c>
       <c r="H1235" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1235" s="6" t="s">
         <v>346</v>
@@ -52194,10 +52193,10 @@
     </row>
     <row r="1236" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1236" s="31" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1236" s="6" t="s">
         <v>1896</v>
-      </c>
-      <c r="B1236" s="6" t="s">
-        <v>1897</v>
       </c>
       <c r="C1236" s="6" t="s">
         <v>17</v>
@@ -52216,7 +52215,7 @@
         <v>111</v>
       </c>
       <c r="H1236" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1236" s="6" t="s">
         <v>346</v>
@@ -52233,7 +52232,7 @@
         <v>912</v>
       </c>
       <c r="B1237" s="6" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="C1237" s="6" t="s">
         <v>40</v>
@@ -52252,7 +52251,7 @@
         <v>111</v>
       </c>
       <c r="H1237" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1237" s="6" t="s">
         <v>346</v>
@@ -52269,7 +52268,7 @@
         <v>221</v>
       </c>
       <c r="B1238" s="6" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="C1238" s="6" t="s">
         <v>17</v>
@@ -52288,7 +52287,7 @@
         <v>14190</v>
       </c>
       <c r="H1238" s="12" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="I1238" s="6" t="s">
         <v>116</v>
@@ -52324,7 +52323,7 @@
         <v>14190</v>
       </c>
       <c r="H1239" s="12" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="I1239" s="6" t="s">
         <v>116</v>
@@ -52341,7 +52340,7 @@
         <v>440</v>
       </c>
       <c r="B1240" s="6" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="C1240" s="6" t="s">
         <v>17</v>
@@ -52360,7 +52359,7 @@
         <v>14190</v>
       </c>
       <c r="H1240" s="12" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="I1240" s="6" t="s">
         <v>116</v>
@@ -52377,7 +52376,7 @@
         <v>1030</v>
       </c>
       <c r="B1241" s="6" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="C1241" s="6" t="s">
         <v>17</v>
@@ -52396,7 +52395,7 @@
         <v>14190</v>
       </c>
       <c r="H1241" s="12" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="I1241" s="6" t="s">
         <v>116</v>
@@ -52410,10 +52409,10 @@
     </row>
     <row r="1242" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1242" s="31" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B1242" s="6" t="s">
         <v>1903</v>
-      </c>
-      <c r="B1242" s="6" t="s">
-        <v>1904</v>
       </c>
       <c r="C1242" s="6" t="s">
         <v>17</v>
@@ -52435,7 +52434,7 @@
         <v>1549</v>
       </c>
       <c r="I1242" s="6" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="J1242" s="6">
         <v>6395</v>
@@ -52446,10 +52445,10 @@
     </row>
     <row r="1243" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1243" s="31" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B1243" s="6" t="s">
         <v>1906</v>
-      </c>
-      <c r="B1243" s="6" t="s">
-        <v>1907</v>
       </c>
       <c r="C1243" s="6" t="s">
         <v>17</v>
@@ -52471,7 +52470,7 @@
         <v>1549</v>
       </c>
       <c r="I1243" s="6" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="J1243" s="6">
         <v>6395</v>
@@ -52482,10 +52481,10 @@
     </row>
     <row r="1244" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1244" s="31" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B1244" s="6" t="s">
         <v>1908</v>
-      </c>
-      <c r="B1244" s="6" t="s">
-        <v>1909</v>
       </c>
       <c r="C1244" s="6" t="s">
         <v>40</v>
@@ -52504,7 +52503,7 @@
         <v>140</v>
       </c>
       <c r="H1244" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1244" s="6" t="s">
         <v>112</v>
@@ -52518,10 +52517,10 @@
     </row>
     <row r="1245" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1245" s="31" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B1245" s="6" t="s">
         <v>1910</v>
-      </c>
-      <c r="B1245" s="6" t="s">
-        <v>1911</v>
       </c>
       <c r="C1245" s="6" t="s">
         <v>40</v>
@@ -52540,7 +52539,7 @@
         <v>140</v>
       </c>
       <c r="H1245" s="12" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="I1245" s="6" t="s">
         <v>112</v>
@@ -52576,7 +52575,7 @@
         <v>4953</v>
       </c>
       <c r="H1246" s="12" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="I1246" s="6" t="s">
         <v>66</v>
@@ -52612,7 +52611,7 @@
         <v>4953</v>
       </c>
       <c r="H1247" s="12" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="I1247" s="6" t="s">
         <v>66</v>
@@ -52629,7 +52628,7 @@
         <v>235</v>
       </c>
       <c r="B1248" s="6" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C1248" s="6" t="s">
         <v>17</v>
@@ -52662,10 +52661,10 @@
     </row>
     <row r="1249" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1249" s="31" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B1249" s="6" t="s">
         <v>1914</v>
-      </c>
-      <c r="B1249" s="6" t="s">
-        <v>1915</v>
       </c>
       <c r="C1249" s="6" t="s">
         <v>17</v>
@@ -52701,7 +52700,7 @@
         <v>338</v>
       </c>
       <c r="B1250" s="6" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C1250" s="6" t="s">
         <v>17</v>
@@ -52734,10 +52733,10 @@
     </row>
     <row r="1251" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1251" s="31" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B1251" s="6" t="s">
         <v>1917</v>
-      </c>
-      <c r="B1251" s="6" t="s">
-        <v>1918</v>
       </c>
       <c r="C1251" s="6" t="s">
         <v>17</v>
@@ -52773,7 +52772,7 @@
         <v>341</v>
       </c>
       <c r="B1252" s="6" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="C1252" s="6" t="s">
         <v>17</v>
@@ -52806,10 +52805,10 @@
     </row>
     <row r="1253" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1253" s="31" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1253" s="6" t="s">
         <v>1831</v>
-      </c>
-      <c r="B1253" s="6" t="s">
-        <v>1832</v>
       </c>
       <c r="C1253" s="6" t="s">
         <v>17</v>
@@ -52845,7 +52844,7 @@
         <v>960</v>
       </c>
       <c r="B1254" s="17" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="C1254" s="6" t="s">
         <v>17</v>
@@ -52881,7 +52880,7 @@
         <v>310</v>
       </c>
       <c r="B1255" s="6" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="C1255" s="6" t="s">
         <v>17</v>
@@ -52917,7 +52916,7 @@
         <v>316</v>
       </c>
       <c r="B1256" s="6" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="C1256" s="6" t="s">
         <v>17</v>
@@ -52950,10 +52949,10 @@
     </row>
     <row r="1257" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1257" s="31" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1257" s="6" t="s">
         <v>1922</v>
-      </c>
-      <c r="B1257" s="6" t="s">
-        <v>1923</v>
       </c>
       <c r="C1257" s="6" t="s">
         <v>17</v>
@@ -53008,7 +53007,7 @@
         <v>12686</v>
       </c>
       <c r="H1258" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1258" s="6" t="s">
         <v>497</v>
@@ -53022,10 +53021,10 @@
     </row>
     <row r="1259" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1259" s="31" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1259" s="6" t="s">
         <v>1924</v>
-      </c>
-      <c r="B1259" s="6" t="s">
-        <v>1925</v>
       </c>
       <c r="C1259" s="6" t="s">
         <v>17</v>
@@ -53044,7 +53043,7 @@
         <v>12686</v>
       </c>
       <c r="H1259" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1259" s="6" t="s">
         <v>497</v>
@@ -53058,10 +53057,10 @@
     </row>
     <row r="1260" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1260" s="31" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1260" s="6" t="s">
         <v>1926</v>
-      </c>
-      <c r="B1260" s="6" t="s">
-        <v>1927</v>
       </c>
       <c r="C1260" s="6" t="s">
         <v>17</v>
@@ -53080,7 +53079,7 @@
         <v>12686</v>
       </c>
       <c r="H1260" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1260" s="6" t="s">
         <v>497</v>
@@ -53097,7 +53096,7 @@
         <v>195</v>
       </c>
       <c r="B1261" s="6" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="C1261" s="6" t="s">
         <v>17</v>
@@ -53116,7 +53115,7 @@
         <v>12686</v>
       </c>
       <c r="H1261" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1261" s="6" t="s">
         <v>497</v>
@@ -53133,7 +53132,7 @@
         <v>712</v>
       </c>
       <c r="B1262" s="6" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="C1262" s="6" t="s">
         <v>17</v>
@@ -53152,7 +53151,7 @@
         <v>12686</v>
       </c>
       <c r="H1262" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1262" s="6" t="s">
         <v>497</v>
@@ -53169,7 +53168,7 @@
         <v>1411</v>
       </c>
       <c r="B1263" s="6" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="C1263" s="6" t="s">
         <v>17</v>
@@ -53188,7 +53187,7 @@
         <v>12686</v>
       </c>
       <c r="H1263" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1263" s="6" t="s">
         <v>497</v>
@@ -53202,10 +53201,10 @@
     </row>
     <row r="1264" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1264" s="31" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1264" s="6" t="s">
         <v>1931</v>
-      </c>
-      <c r="B1264" s="6" t="s">
-        <v>1932</v>
       </c>
       <c r="C1264" s="6" t="s">
         <v>17</v>
@@ -53224,7 +53223,7 @@
         <v>12686</v>
       </c>
       <c r="H1264" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1264" s="6" t="s">
         <v>497</v>
@@ -53238,10 +53237,10 @@
     </row>
     <row r="1265" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1265" s="31" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1265" s="6" t="s">
         <v>1933</v>
-      </c>
-      <c r="B1265" s="6" t="s">
-        <v>1934</v>
       </c>
       <c r="C1265" s="6" t="s">
         <v>17</v>
@@ -53260,7 +53259,7 @@
         <v>12686</v>
       </c>
       <c r="H1265" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1265" s="6" t="s">
         <v>497</v>
@@ -53277,7 +53276,7 @@
         <v>594</v>
       </c>
       <c r="B1266" s="6" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="C1266" s="6" t="s">
         <v>17</v>
@@ -53296,7 +53295,7 @@
         <v>12686</v>
       </c>
       <c r="H1266" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1266" s="6" t="s">
         <v>497</v>
@@ -53313,7 +53312,7 @@
         <v>1183</v>
       </c>
       <c r="B1267" s="6" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="C1267" s="6" t="s">
         <v>17</v>
@@ -53332,7 +53331,7 @@
         <v>1267</v>
       </c>
       <c r="H1267" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1267" s="6" t="s">
         <v>1180</v>
@@ -53346,10 +53345,10 @@
     </row>
     <row r="1268" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1268" s="32" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1268" s="6" t="s">
         <v>1936</v>
-      </c>
-      <c r="B1268" s="6" t="s">
-        <v>1937</v>
       </c>
       <c r="C1268" s="6" t="s">
         <v>17</v>
@@ -53368,7 +53367,7 @@
         <v>1267</v>
       </c>
       <c r="H1268" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1268" s="6" t="s">
         <v>1180</v>
@@ -53404,7 +53403,7 @@
         <v>1267</v>
       </c>
       <c r="H1269" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1269" s="6" t="s">
         <v>1180</v>
@@ -53440,7 +53439,7 @@
         <v>1267</v>
       </c>
       <c r="H1270" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1270" s="6" t="s">
         <v>1180</v>
@@ -53454,10 +53453,10 @@
     </row>
     <row r="1271" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1271" s="32" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1271" s="6" t="s">
         <v>1938</v>
-      </c>
-      <c r="B1271" s="6" t="s">
-        <v>1939</v>
       </c>
       <c r="C1271" s="6" t="s">
         <v>17</v>
@@ -53476,7 +53475,7 @@
         <v>1267</v>
       </c>
       <c r="H1271" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1271" s="6" t="s">
         <v>1180</v>
@@ -53493,7 +53492,7 @@
         <v>436</v>
       </c>
       <c r="B1272" s="6" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C1272" s="6" t="s">
         <v>17</v>
@@ -53512,7 +53511,7 @@
         <v>1267</v>
       </c>
       <c r="H1272" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1272" s="6" t="s">
         <v>1180</v>
@@ -53526,10 +53525,10 @@
     </row>
     <row r="1273" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1273" s="32" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1273" s="6" t="s">
         <v>1941</v>
-      </c>
-      <c r="B1273" s="6" t="s">
-        <v>1942</v>
       </c>
       <c r="C1273" s="6" t="s">
         <v>17</v>
@@ -53548,7 +53547,7 @@
         <v>1267</v>
       </c>
       <c r="H1273" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1273" s="6" t="s">
         <v>1180</v>
@@ -53562,10 +53561,10 @@
     </row>
     <row r="1274" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1274" s="32" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1274" s="6" t="s">
         <v>1943</v>
-      </c>
-      <c r="B1274" s="6" t="s">
-        <v>1944</v>
       </c>
       <c r="C1274" s="6" t="s">
         <v>17</v>
@@ -53584,7 +53583,7 @@
         <v>1267</v>
       </c>
       <c r="H1274" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1274" s="6" t="s">
         <v>1180</v>
@@ -53598,10 +53597,10 @@
     </row>
     <row r="1275" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1275" s="32" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1275" s="6" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1275" s="6" t="s">
-        <v>1946</v>
       </c>
       <c r="C1275" s="6" t="s">
         <v>17</v>
@@ -53620,7 +53619,7 @@
         <v>1267</v>
       </c>
       <c r="H1275" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1275" s="6" t="s">
         <v>1180</v>
@@ -53637,7 +53636,7 @@
         <v>1247</v>
       </c>
       <c r="B1276" s="6" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="C1276" s="6" t="s">
         <v>17</v>
@@ -53656,7 +53655,7 @@
         <v>1267</v>
       </c>
       <c r="H1276" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1276" s="6" t="s">
         <v>1180</v>
@@ -53673,7 +53672,7 @@
         <v>1229</v>
       </c>
       <c r="B1277" s="6" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="C1277" s="6" t="s">
         <v>17</v>
@@ -53692,7 +53691,7 @@
         <v>1265</v>
       </c>
       <c r="H1277" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1277" s="6" t="s">
         <v>1180</v>
@@ -53706,10 +53705,10 @@
     </row>
     <row r="1278" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1278" s="32" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1278" s="6" t="s">
         <v>1949</v>
-      </c>
-      <c r="B1278" s="6" t="s">
-        <v>1950</v>
       </c>
       <c r="C1278" s="6" t="s">
         <v>17</v>
@@ -53728,7 +53727,7 @@
         <v>1265</v>
       </c>
       <c r="H1278" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1278" s="6" t="s">
         <v>1180</v>
@@ -53742,10 +53741,10 @@
     </row>
     <row r="1279" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1279" s="32" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1279" s="6" t="s">
         <v>1951</v>
-      </c>
-      <c r="B1279" s="6" t="s">
-        <v>1952</v>
       </c>
       <c r="C1279" s="6" t="s">
         <v>17</v>
@@ -53764,7 +53763,7 @@
         <v>1265</v>
       </c>
       <c r="H1279" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1279" s="6" t="s">
         <v>1180</v>
@@ -53781,7 +53780,7 @@
         <v>1424</v>
       </c>
       <c r="B1280" s="6" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C1280" s="6" t="s">
         <v>17</v>
@@ -53800,7 +53799,7 @@
         <v>1265</v>
       </c>
       <c r="H1280" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1280" s="6" t="s">
         <v>1180</v>
@@ -53836,7 +53835,7 @@
         <v>1265</v>
       </c>
       <c r="H1281" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1281" s="6" t="s">
         <v>1180</v>
@@ -53872,7 +53871,7 @@
         <v>1265</v>
       </c>
       <c r="H1282" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1282" s="6" t="s">
         <v>1180</v>
@@ -53889,7 +53888,7 @@
         <v>1144</v>
       </c>
       <c r="B1283" s="6" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="C1283" s="6" t="s">
         <v>17</v>
@@ -53908,7 +53907,7 @@
         <v>1265</v>
       </c>
       <c r="H1283" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1283" s="6" t="s">
         <v>1180</v>
@@ -53944,7 +53943,7 @@
         <v>1265</v>
       </c>
       <c r="H1284" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1284" s="6" t="s">
         <v>1180</v>
@@ -53980,7 +53979,7 @@
         <v>1265</v>
       </c>
       <c r="H1285" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1285" s="6" t="s">
         <v>1180</v>
@@ -53997,7 +53996,7 @@
         <v>1252</v>
       </c>
       <c r="B1286" s="6" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C1286" s="6" t="s">
         <v>17</v>
@@ -54016,7 +54015,7 @@
         <v>1265</v>
       </c>
       <c r="H1286" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1286" s="6" t="s">
         <v>1180</v>
@@ -54033,7 +54032,7 @@
         <v>1201</v>
       </c>
       <c r="B1287" s="6" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C1287" s="6" t="s">
         <v>17</v>
@@ -54052,7 +54051,7 @@
         <v>1265</v>
       </c>
       <c r="H1287" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1287" s="6" t="s">
         <v>1180</v>
@@ -54066,10 +54065,10 @@
     </row>
     <row r="1288" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1288" s="32" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B1288" s="6" t="s">
         <v>1957</v>
-      </c>
-      <c r="B1288" s="6" t="s">
-        <v>1958</v>
       </c>
       <c r="C1288" s="6" t="s">
         <v>17</v>
@@ -54088,7 +54087,7 @@
         <v>1265</v>
       </c>
       <c r="H1288" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1288" s="6" t="s">
         <v>1180</v>
@@ -54105,7 +54104,7 @@
         <v>1235</v>
       </c>
       <c r="B1289" s="6" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C1289" s="6" t="s">
         <v>17</v>
@@ -54124,7 +54123,7 @@
         <v>1265</v>
       </c>
       <c r="H1289" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1289" s="6" t="s">
         <v>1180</v>
@@ -54160,7 +54159,7 @@
         <v>1265</v>
       </c>
       <c r="H1290" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1290" s="6" t="s">
         <v>1180</v>
@@ -54196,7 +54195,7 @@
         <v>1265</v>
       </c>
       <c r="H1291" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1291" s="6" t="s">
         <v>1180</v>
@@ -54213,7 +54212,7 @@
         <v>1197</v>
       </c>
       <c r="B1292" s="6" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="C1292" s="6" t="s">
         <v>17</v>
@@ -54232,7 +54231,7 @@
         <v>1265</v>
       </c>
       <c r="H1292" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1292" s="6" t="s">
         <v>1180</v>
@@ -54268,7 +54267,7 @@
         <v>1265</v>
       </c>
       <c r="H1293" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1293" s="6" t="s">
         <v>1180</v>
@@ -54304,7 +54303,7 @@
         <v>1265</v>
       </c>
       <c r="H1294" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1294" s="6" t="s">
         <v>1180</v>
@@ -54321,7 +54320,7 @@
         <v>515</v>
       </c>
       <c r="B1295" s="6" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C1295" s="6" t="s">
         <v>17</v>
@@ -54349,7 +54348,7 @@
         <v>6403</v>
       </c>
       <c r="K1295" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1296" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54357,7 +54356,7 @@
         <v>518</v>
       </c>
       <c r="B1296" s="6" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C1296" s="6" t="s">
         <v>17</v>
@@ -54385,7 +54384,7 @@
         <v>6403</v>
       </c>
       <c r="K1296" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1297" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54393,7 +54392,7 @@
         <v>520</v>
       </c>
       <c r="B1297" s="6" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C1297" s="6" t="s">
         <v>17</v>
@@ -54421,7 +54420,7 @@
         <v>6403</v>
       </c>
       <c r="K1297" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1298" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54429,7 +54428,7 @@
         <v>495</v>
       </c>
       <c r="B1298" s="6" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C1298" s="6" t="s">
         <v>17</v>
@@ -54457,7 +54456,7 @@
         <v>6404</v>
       </c>
       <c r="K1298" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1299" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54493,15 +54492,15 @@
         <v>6404</v>
       </c>
       <c r="K1299" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1300" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1300" s="31" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B1300" s="6" t="s">
         <v>1966</v>
-      </c>
-      <c r="B1300" s="6" t="s">
-        <v>1967</v>
       </c>
       <c r="C1300" s="6" t="s">
         <v>17</v>
@@ -54529,7 +54528,7 @@
         <v>6404</v>
       </c>
       <c r="K1300" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1301" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54537,7 +54536,7 @@
         <v>590</v>
       </c>
       <c r="B1301" s="6" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="C1301" s="6" t="s">
         <v>17</v>
@@ -54565,15 +54564,15 @@
         <v>6404</v>
       </c>
       <c r="K1301" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1302" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1302" s="31" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1302" s="6" t="s">
         <v>1969</v>
-      </c>
-      <c r="B1302" s="6" t="s">
-        <v>1970</v>
       </c>
       <c r="C1302" s="6" t="s">
         <v>17</v>
@@ -54601,7 +54600,7 @@
         <v>6404</v>
       </c>
       <c r="K1302" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1303" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54609,7 +54608,7 @@
         <v>194</v>
       </c>
       <c r="B1303" s="6" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C1303" s="6" t="s">
         <v>17</v>
@@ -54637,15 +54636,15 @@
         <v>6404</v>
       </c>
       <c r="K1303" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1304" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1304" s="31" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1304" s="6" t="s">
         <v>1972</v>
-      </c>
-      <c r="B1304" s="6" t="s">
-        <v>1973</v>
       </c>
       <c r="C1304" s="6" t="s">
         <v>17</v>
@@ -54673,7 +54672,7 @@
         <v>6404</v>
       </c>
       <c r="K1304" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1305" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54709,7 +54708,7 @@
         <v>6404</v>
       </c>
       <c r="K1305" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1306" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54717,7 +54716,7 @@
         <v>1488</v>
       </c>
       <c r="B1306" s="6" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C1306" s="6" t="s">
         <v>17</v>
@@ -54745,7 +54744,7 @@
         <v>6405</v>
       </c>
       <c r="K1306" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1307" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54753,7 +54752,7 @@
         <v>1038</v>
       </c>
       <c r="B1307" s="6" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C1307" s="6" t="s">
         <v>40</v>
@@ -54781,7 +54780,7 @@
         <v>6405</v>
       </c>
       <c r="K1307" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1308" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54789,7 +54788,7 @@
         <v>308</v>
       </c>
       <c r="B1308" s="17" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C1308" s="6" t="s">
         <v>17</v>
@@ -54817,15 +54816,15 @@
         <v>6405</v>
       </c>
       <c r="K1308" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1309" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1309" s="31" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1309" s="6" t="s">
         <v>1977</v>
-      </c>
-      <c r="B1309" s="6" t="s">
-        <v>1978</v>
       </c>
       <c r="C1309" s="6" t="s">
         <v>17</v>
@@ -54847,21 +54846,21 @@
         <v>46147</v>
       </c>
       <c r="I1309" s="6" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J1309" s="6">
         <v>6406</v>
       </c>
       <c r="K1309" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1310" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1310" s="31" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1310" s="6" t="s">
         <v>1980</v>
-      </c>
-      <c r="B1310" s="6" t="s">
-        <v>1981</v>
       </c>
       <c r="C1310" s="6" t="s">
         <v>17</v>
@@ -54883,13 +54882,13 @@
         <v>46147</v>
       </c>
       <c r="I1310" s="6" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J1310" s="6">
         <v>6406</v>
       </c>
       <c r="K1310" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1311" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54897,7 +54896,7 @@
         <v>1069</v>
       </c>
       <c r="B1311" s="6" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="C1311" s="6" t="s">
         <v>17</v>
@@ -54925,15 +54924,15 @@
         <v>6407</v>
       </c>
       <c r="K1311" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1312" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1312" s="31" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B1312" s="6" t="s">
         <v>1983</v>
-      </c>
-      <c r="B1312" s="6" t="s">
-        <v>1984</v>
       </c>
       <c r="C1312" s="6" t="s">
         <v>17</v>
@@ -54961,15 +54960,15 @@
         <v>6408</v>
       </c>
       <c r="K1312" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1313" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1313" s="34" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1313" s="6" t="s">
         <v>1985</v>
-      </c>
-      <c r="B1313" s="6" t="s">
-        <v>1986</v>
       </c>
       <c r="C1313" s="6" t="s">
         <v>17</v>
@@ -54997,7 +54996,7 @@
         <v>6408</v>
       </c>
       <c r="K1313" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1314" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55005,7 +55004,7 @@
         <v>723</v>
       </c>
       <c r="B1314" s="6" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C1314" s="6" t="s">
         <v>17</v>
@@ -55033,7 +55032,7 @@
         <v>6408</v>
       </c>
       <c r="K1314" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1315" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55041,7 +55040,7 @@
         <v>333</v>
       </c>
       <c r="B1315" s="6" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="C1315" s="6" t="s">
         <v>17</v>
@@ -55069,15 +55068,15 @@
         <v>6408</v>
       </c>
       <c r="K1315" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1316" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1316" s="31" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1316" s="6" t="s">
         <v>1988</v>
-      </c>
-      <c r="B1316" s="6" t="s">
-        <v>1989</v>
       </c>
       <c r="C1316" s="6" t="s">
         <v>17</v>
@@ -55105,15 +55104,15 @@
         <v>6408</v>
       </c>
       <c r="K1316" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1317" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1317" s="31" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1317" s="6" t="s">
         <v>1990</v>
-      </c>
-      <c r="B1317" s="6" t="s">
-        <v>1991</v>
       </c>
       <c r="C1317" s="6" t="s">
         <v>17</v>
@@ -55141,15 +55140,15 @@
         <v>6408</v>
       </c>
       <c r="K1317" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1318" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1318" s="31" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1318" s="6" t="s">
         <v>1992</v>
-      </c>
-      <c r="B1318" s="6" t="s">
-        <v>1993</v>
       </c>
       <c r="C1318" s="6" t="s">
         <v>17</v>
@@ -55177,7 +55176,7 @@
         <v>6408</v>
       </c>
       <c r="K1318" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1319" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55185,7 +55184,7 @@
         <v>291</v>
       </c>
       <c r="B1319" s="6" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="C1319" s="6" t="s">
         <v>40</v>
@@ -55213,7 +55212,7 @@
         <v>6409</v>
       </c>
       <c r="K1319" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1320" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55221,7 +55220,7 @@
         <v>292</v>
       </c>
       <c r="B1320" s="6" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C1320" s="6" t="s">
         <v>40</v>
@@ -55249,7 +55248,7 @@
         <v>6409</v>
       </c>
       <c r="K1320" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1321" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55257,7 +55256,7 @@
         <v>687</v>
       </c>
       <c r="B1321" s="6" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C1321" s="6" t="s">
         <v>17</v>
@@ -55285,12 +55284,12 @@
         <v>6410</v>
       </c>
       <c r="K1321" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1322" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1322" s="31" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B1322" s="6" t="s">
         <v>512</v>
@@ -55321,7 +55320,7 @@
         <v>6411</v>
       </c>
       <c r="K1322" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1323" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55357,7 +55356,7 @@
         <v>6411</v>
       </c>
       <c r="K1323" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1324" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55393,15 +55392,15 @@
         <v>6411</v>
       </c>
       <c r="K1324" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1325" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1325" s="35" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B1325" s="18" t="s">
         <v>1997</v>
-      </c>
-      <c r="B1325" s="18" t="s">
-        <v>1998</v>
       </c>
       <c r="C1325" s="19" t="s">
         <v>40</v>
@@ -55429,15 +55428,15 @@
         <v>6412</v>
       </c>
       <c r="K1325" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1326" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1326" s="35" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B1326" s="18" t="s">
         <v>1999</v>
-      </c>
-      <c r="B1326" s="18" t="s">
-        <v>2000</v>
       </c>
       <c r="C1326" s="19" t="s">
         <v>40</v>
@@ -55465,15 +55464,15 @@
         <v>6412</v>
       </c>
       <c r="K1326" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1327" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1327" s="35" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B1327" s="18" t="s">
         <v>2001</v>
-      </c>
-      <c r="B1327" s="18" t="s">
-        <v>2002</v>
       </c>
       <c r="C1327" s="19" t="s">
         <v>40</v>
@@ -55501,15 +55500,15 @@
         <v>6412</v>
       </c>
       <c r="K1327" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1328" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1328" s="35" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B1328" s="18" t="s">
         <v>2003</v>
-      </c>
-      <c r="B1328" s="18" t="s">
-        <v>2004</v>
       </c>
       <c r="C1328" s="19" t="s">
         <v>40</v>
@@ -55537,15 +55536,15 @@
         <v>6412</v>
       </c>
       <c r="K1328" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1329" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1329" s="35" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B1329" s="18" t="s">
         <v>2005</v>
-      </c>
-      <c r="B1329" s="18" t="s">
-        <v>2006</v>
       </c>
       <c r="C1329" s="19" t="s">
         <v>40</v>
@@ -55573,7 +55572,7 @@
         <v>6412</v>
       </c>
       <c r="K1329" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1330" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55600,24 +55599,24 @@
         <v>1717</v>
       </c>
       <c r="H1330" s="12" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="I1330" s="6" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="J1330" s="6">
         <v>6413</v>
       </c>
       <c r="K1330" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1331" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1331" s="31" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1331" s="6" t="s">
         <v>2008</v>
-      </c>
-      <c r="B1331" s="6" t="s">
-        <v>2009</v>
       </c>
       <c r="C1331" s="6" t="s">
         <v>40</v>
@@ -55639,21 +55638,21 @@
         <v>46028</v>
       </c>
       <c r="I1331" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="J1331" s="6">
         <v>6414</v>
       </c>
       <c r="K1331" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1332" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1332" s="31" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B1332" s="6" t="s">
         <v>2011</v>
-      </c>
-      <c r="B1332" s="6" t="s">
-        <v>2012</v>
       </c>
       <c r="C1332" s="6" t="s">
         <v>40</v>
@@ -55675,13 +55674,13 @@
         <v>46028</v>
       </c>
       <c r="I1332" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="J1332" s="6">
         <v>6414</v>
       </c>
       <c r="K1332" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1333" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55689,7 +55688,7 @@
         <v>1243</v>
       </c>
       <c r="B1333" s="6" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C1333" s="6" t="s">
         <v>17</v>
@@ -55708,7 +55707,7 @@
         <v>112</v>
       </c>
       <c r="H1333" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1333" s="6" t="s">
         <v>346</v>
@@ -55717,7 +55716,7 @@
         <v>6415</v>
       </c>
       <c r="K1333" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1334" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55725,7 +55724,7 @@
         <v>284</v>
       </c>
       <c r="B1334" s="6" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C1334" s="6" t="s">
         <v>17</v>
@@ -55744,7 +55743,7 @@
         <v>112</v>
       </c>
       <c r="H1334" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1334" s="6" t="s">
         <v>346</v>
@@ -55753,7 +55752,7 @@
         <v>6415</v>
       </c>
       <c r="K1334" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1335" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55761,7 +55760,7 @@
         <v>273</v>
       </c>
       <c r="B1335" s="6" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C1335" s="6" t="s">
         <v>17</v>
@@ -55780,7 +55779,7 @@
         <v>112</v>
       </c>
       <c r="H1335" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1335" s="6" t="s">
         <v>346</v>
@@ -55789,7 +55788,7 @@
         <v>6415</v>
       </c>
       <c r="K1335" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1336" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55797,7 +55796,7 @@
         <v>1077</v>
       </c>
       <c r="B1336" s="6" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C1336" s="6" t="s">
         <v>17</v>
@@ -55816,7 +55815,7 @@
         <v>112</v>
       </c>
       <c r="H1336" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1336" s="6" t="s">
         <v>346</v>
@@ -55825,7 +55824,7 @@
         <v>6415</v>
       </c>
       <c r="K1336" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1337" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55833,7 +55832,7 @@
         <v>1268</v>
       </c>
       <c r="B1337" s="6" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C1337" s="6" t="s">
         <v>17</v>
@@ -55852,7 +55851,7 @@
         <v>112</v>
       </c>
       <c r="H1337" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1337" s="6" t="s">
         <v>346</v>
@@ -55861,7 +55860,7 @@
         <v>6415</v>
       </c>
       <c r="K1337" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1338" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55869,7 +55868,7 @@
         <v>1079</v>
       </c>
       <c r="B1338" s="6" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C1338" s="6" t="s">
         <v>17</v>
@@ -55888,7 +55887,7 @@
         <v>112</v>
       </c>
       <c r="H1338" s="12" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I1338" s="6" t="s">
         <v>346</v>
@@ -55897,7 +55896,7 @@
         <v>6415</v>
       </c>
       <c r="K1338" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1339" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55905,7 +55904,7 @@
         <v>813</v>
       </c>
       <c r="B1339" s="6" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C1339" s="6" t="s">
         <v>17</v>
@@ -55933,15 +55932,15 @@
         <v>6416</v>
       </c>
       <c r="K1339" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1340" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1340" s="31" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1340" s="6" t="s">
         <v>2020</v>
-      </c>
-      <c r="B1340" s="6" t="s">
-        <v>2021</v>
       </c>
       <c r="C1340" s="6" t="s">
         <v>17</v>
@@ -55969,15 +55968,15 @@
         <v>6416</v>
       </c>
       <c r="K1340" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1341" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1341" s="31" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1341" s="6" t="s">
         <v>2022</v>
-      </c>
-      <c r="B1341" s="6" t="s">
-        <v>2023</v>
       </c>
       <c r="C1341" s="6" t="s">
         <v>17</v>
@@ -56005,15 +56004,15 @@
         <v>6416</v>
       </c>
       <c r="K1341" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1342" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1342" s="31" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B1342" s="6" t="s">
         <v>2024</v>
-      </c>
-      <c r="B1342" s="6" t="s">
-        <v>2025</v>
       </c>
       <c r="C1342" s="6" t="s">
         <v>17</v>
@@ -56041,7 +56040,7 @@
         <v>6416</v>
       </c>
       <c r="K1342" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1343" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56049,7 +56048,7 @@
         <v>809</v>
       </c>
       <c r="B1343" s="6" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C1343" s="6" t="s">
         <v>17</v>
@@ -56077,15 +56076,15 @@
         <v>6416</v>
       </c>
       <c r="K1343" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1344" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1344" s="31" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B1344" s="6" t="s">
         <v>2027</v>
-      </c>
-      <c r="B1344" s="6" t="s">
-        <v>2028</v>
       </c>
       <c r="C1344" s="6" t="s">
         <v>17</v>
@@ -56113,7 +56112,7 @@
         <v>6416</v>
       </c>
       <c r="K1344" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1345" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56149,15 +56148,15 @@
         <v>6416</v>
       </c>
       <c r="K1345" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1346" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1346" s="31" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1346" s="6" t="s">
         <v>2029</v>
-      </c>
-      <c r="B1346" s="6" t="s">
-        <v>2030</v>
       </c>
       <c r="C1346" s="6" t="s">
         <v>17</v>
@@ -56185,7 +56184,7 @@
         <v>6416</v>
       </c>
       <c r="K1346" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1347" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56193,7 +56192,7 @@
         <v>841</v>
       </c>
       <c r="B1347" s="6" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C1347" s="6" t="s">
         <v>17</v>
@@ -56221,15 +56220,15 @@
         <v>6417</v>
       </c>
       <c r="K1347" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1348" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1348" s="31" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1348" s="6" t="s">
         <v>2032</v>
-      </c>
-      <c r="B1348" s="6" t="s">
-        <v>2033</v>
       </c>
       <c r="C1348" s="6" t="s">
         <v>17</v>
@@ -56257,15 +56256,15 @@
         <v>6417</v>
       </c>
       <c r="K1348" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1349" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1349" s="31" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1349" s="6" t="s">
         <v>2034</v>
-      </c>
-      <c r="B1349" s="6" t="s">
-        <v>2035</v>
       </c>
       <c r="C1349" s="6" t="s">
         <v>17</v>
@@ -56293,15 +56292,15 @@
         <v>6417</v>
       </c>
       <c r="K1349" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1350" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1350" s="31" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1350" s="6" t="s">
         <v>2036</v>
-      </c>
-      <c r="B1350" s="6" t="s">
-        <v>2037</v>
       </c>
       <c r="C1350" s="6" t="s">
         <v>17</v>
@@ -56329,15 +56328,15 @@
         <v>6417</v>
       </c>
       <c r="K1350" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1351" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1351" s="31" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1351" s="6" t="s">
         <v>2038</v>
-      </c>
-      <c r="B1351" s="6" t="s">
-        <v>2039</v>
       </c>
       <c r="C1351" s="6" t="s">
         <v>17</v>
@@ -56365,12 +56364,12 @@
         <v>6417</v>
       </c>
       <c r="K1351" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1352" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1352" s="31" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B1352" s="6" t="s">
         <v>836</v>
@@ -56401,15 +56400,15 @@
         <v>6417</v>
       </c>
       <c r="K1352" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1353" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1353" s="31" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B1353" s="6" t="s">
         <v>2041</v>
-      </c>
-      <c r="B1353" s="6" t="s">
-        <v>2042</v>
       </c>
       <c r="C1353" s="6" t="s">
         <v>17</v>
@@ -56437,15 +56436,15 @@
         <v>6417</v>
       </c>
       <c r="K1353" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1354" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1354" s="31" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1354" s="6" t="s">
         <v>2043</v>
-      </c>
-      <c r="B1354" s="6" t="s">
-        <v>2044</v>
       </c>
       <c r="C1354" s="6" t="s">
         <v>17</v>
@@ -56473,7 +56472,7 @@
         <v>6417</v>
       </c>
       <c r="K1354" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1355" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56481,7 +56480,7 @@
         <v>1463</v>
       </c>
       <c r="B1355" s="6" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C1355" s="6" t="s">
         <v>17</v>
@@ -56509,7 +56508,7 @@
         <v>6417</v>
       </c>
       <c r="K1355" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1356" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56517,7 +56516,7 @@
         <v>853</v>
       </c>
       <c r="B1356" s="6" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="C1356" s="6" t="s">
         <v>17</v>
@@ -56545,7 +56544,7 @@
         <v>6417</v>
       </c>
       <c r="K1356" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1357" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56553,7 +56552,7 @@
         <v>13101019</v>
       </c>
       <c r="B1357" s="18" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="C1357" s="18" t="s">
         <v>17</v>
@@ -56581,7 +56580,7 @@
         <v>6417</v>
       </c>
       <c r="K1357" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1358" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56589,7 +56588,7 @@
         <v>819</v>
       </c>
       <c r="B1358" s="6" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="C1358" s="6" t="s">
         <v>17</v>
@@ -56617,7 +56616,7 @@
         <v>6418</v>
       </c>
       <c r="K1358" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1359" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56625,7 +56624,7 @@
         <v>809</v>
       </c>
       <c r="B1359" s="6" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="C1359" s="6" t="s">
         <v>17</v>
@@ -56653,15 +56652,15 @@
         <v>6418</v>
       </c>
       <c r="K1359" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1360" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1360" s="31" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1360" s="6" t="s">
         <v>2050</v>
-      </c>
-      <c r="B1360" s="6" t="s">
-        <v>2051</v>
       </c>
       <c r="C1360" s="6" t="s">
         <v>17</v>
@@ -56689,15 +56688,15 @@
         <v>6418</v>
       </c>
       <c r="K1360" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1361" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1361" s="31" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1361" s="6" t="s">
         <v>2052</v>
-      </c>
-      <c r="B1361" s="6" t="s">
-        <v>2053</v>
       </c>
       <c r="C1361" s="6" t="s">
         <v>17</v>
@@ -56725,15 +56724,15 @@
         <v>6418</v>
       </c>
       <c r="K1361" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1362" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1362" s="31" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1362" s="6" t="s">
         <v>2054</v>
-      </c>
-      <c r="B1362" s="6" t="s">
-        <v>2055</v>
       </c>
       <c r="C1362" s="6" t="s">
         <v>17</v>
@@ -56761,15 +56760,15 @@
         <v>6418</v>
       </c>
       <c r="K1362" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1363" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1363" s="31" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1363" s="6" t="s">
         <v>2056</v>
-      </c>
-      <c r="B1363" s="6" t="s">
-        <v>2057</v>
       </c>
       <c r="C1363" s="6" t="s">
         <v>17</v>
@@ -56797,15 +56796,15 @@
         <v>6418</v>
       </c>
       <c r="K1363" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1364" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1364" s="31" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1364" s="6" t="s">
         <v>2058</v>
-      </c>
-      <c r="B1364" s="6" t="s">
-        <v>2059</v>
       </c>
       <c r="C1364" s="6" t="s">
         <v>17</v>
@@ -56833,15 +56832,15 @@
         <v>6418</v>
       </c>
       <c r="K1364" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1365" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1365" s="31" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1365" s="6" t="s">
         <v>2060</v>
-      </c>
-      <c r="B1365" s="6" t="s">
-        <v>2061</v>
       </c>
       <c r="C1365" s="6" t="s">
         <v>17</v>
@@ -56869,15 +56868,15 @@
         <v>6418</v>
       </c>
       <c r="K1365" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1366" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1366" s="31" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B1366" s="6" t="s">
         <v>2062</v>
-      </c>
-      <c r="B1366" s="6" t="s">
-        <v>2063</v>
       </c>
       <c r="C1366" s="6" t="s">
         <v>17</v>
@@ -56905,7 +56904,7 @@
         <v>6418</v>
       </c>
       <c r="K1366" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1367" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56941,13 +56940,13 @@
         <v>6418</v>
       </c>
       <c r="K1367" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1368" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1368" s="42"/>
       <c r="B1368" s="18" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="C1368" s="18" t="s">
         <v>348</v>
@@ -56975,7 +56974,7 @@
         <v>6418</v>
       </c>
       <c r="K1368" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1369" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56983,7 +56982,7 @@
         <v>815</v>
       </c>
       <c r="B1369" s="6" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="C1369" s="6" t="s">
         <v>17</v>
@@ -57011,7 +57010,7 @@
         <v>6419</v>
       </c>
       <c r="K1369" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1370" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57019,7 +57018,7 @@
         <v>13101032</v>
       </c>
       <c r="B1370" s="18" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="C1370" s="18" t="s">
         <v>17</v>
@@ -57047,15 +57046,15 @@
         <v>6419</v>
       </c>
       <c r="K1370" s="21" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1371" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1371" s="31" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B1371" s="6" t="s">
         <v>2067</v>
-      </c>
-      <c r="B1371" s="6" t="s">
-        <v>2068</v>
       </c>
       <c r="C1371" s="6" t="s">
         <v>17</v>
@@ -57083,15 +57082,15 @@
         <v>6419</v>
       </c>
       <c r="K1371" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1372" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1372" s="31" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1372" s="6" t="s">
         <v>2069</v>
-      </c>
-      <c r="B1372" s="6" t="s">
-        <v>2070</v>
       </c>
       <c r="C1372" s="6" t="s">
         <v>707</v>
@@ -57119,15 +57118,15 @@
         <v>6419</v>
       </c>
       <c r="K1372" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1373" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1373" s="31" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B1373" s="6" t="s">
         <v>2071</v>
-      </c>
-      <c r="B1373" s="6" t="s">
-        <v>2072</v>
       </c>
       <c r="C1373" s="6" t="s">
         <v>348</v>
@@ -57155,7 +57154,7 @@
         <v>6419</v>
       </c>
       <c r="K1373" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1374" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57163,7 +57162,7 @@
         <v>515</v>
       </c>
       <c r="B1374" s="6" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C1374" s="6" t="s">
         <v>17</v>
@@ -57191,7 +57190,7 @@
         <v>6420</v>
       </c>
       <c r="K1374" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1375" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57199,7 +57198,7 @@
         <v>518</v>
       </c>
       <c r="B1375" s="6" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="C1375" s="6" t="s">
         <v>17</v>
@@ -57227,7 +57226,7 @@
         <v>6420</v>
       </c>
       <c r="K1375" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1376" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57235,7 +57234,7 @@
         <v>520</v>
       </c>
       <c r="B1376" s="6" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C1376" s="6" t="s">
         <v>17</v>
@@ -57263,7 +57262,7 @@
         <v>6420</v>
       </c>
       <c r="K1376" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1377" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57299,7 +57298,7 @@
         <v>6421</v>
       </c>
       <c r="K1377" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1378" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57335,7 +57334,7 @@
         <v>6421</v>
       </c>
       <c r="K1378" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1379" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57343,7 +57342,7 @@
         <v>454</v>
       </c>
       <c r="B1379" s="6" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="C1379" s="6" t="s">
         <v>17</v>
@@ -57371,7 +57370,7 @@
         <v>6421</v>
       </c>
       <c r="K1379" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1380" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57379,7 +57378,7 @@
         <v>1309</v>
       </c>
       <c r="B1380" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="C1380" s="6" t="s">
         <v>17</v>
@@ -57407,7 +57406,7 @@
         <v>6421</v>
       </c>
       <c r="K1380" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1381" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57415,7 +57414,7 @@
         <v>1307</v>
       </c>
       <c r="B1381" s="6" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="C1381" s="6" t="s">
         <v>17</v>
@@ -57443,7 +57442,7 @@
         <v>6421</v>
       </c>
       <c r="K1381" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1382" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57479,7 +57478,7 @@
         <v>6421</v>
       </c>
       <c r="K1382" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1383" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57487,7 +57486,7 @@
         <v>914</v>
       </c>
       <c r="B1383" s="6" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="C1383" s="6" t="s">
         <v>17</v>
@@ -57515,7 +57514,7 @@
         <v>6422</v>
       </c>
       <c r="K1383" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1384" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57523,7 +57522,7 @@
         <v>1071</v>
       </c>
       <c r="B1384" s="6" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="C1384" s="6" t="s">
         <v>17</v>
@@ -57551,7 +57550,7 @@
         <v>6423</v>
       </c>
       <c r="K1384" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1385" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57587,7 +57586,7 @@
         <v>6423</v>
       </c>
       <c r="K1385" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1386" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57595,7 +57594,7 @@
         <v>1307</v>
       </c>
       <c r="B1386" s="6" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="C1386" s="6" t="s">
         <v>17</v>
@@ -57623,15 +57622,15 @@
         <v>6423</v>
       </c>
       <c r="K1386" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1387" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1387" s="31" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B1387" s="6" t="s">
         <v>2081</v>
-      </c>
-      <c r="B1387" s="6" t="s">
-        <v>2082</v>
       </c>
       <c r="C1387" s="6" t="s">
         <v>17</v>
@@ -57659,15 +57658,15 @@
         <v>6423</v>
       </c>
       <c r="K1387" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1388" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1388" s="32" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1388" s="6" t="s">
         <v>2083</v>
-      </c>
-      <c r="B1388" s="6" t="s">
-        <v>2084</v>
       </c>
       <c r="C1388" s="6" t="s">
         <v>17</v>
@@ -57695,13 +57694,13 @@
         <v>6423</v>
       </c>
       <c r="K1388" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1389" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1389" s="42"/>
       <c r="B1389" s="18" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="C1389" s="18" t="s">
         <v>17</v>
@@ -57729,13 +57728,13 @@
         <v>6424</v>
       </c>
       <c r="K1389" s="21" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1390" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1390" s="42"/>
       <c r="B1390" s="18" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="C1390" s="18" t="s">
         <v>17</v>
@@ -57763,13 +57762,13 @@
         <v>6424</v>
       </c>
       <c r="K1390" s="21" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1391" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1391" s="42"/>
       <c r="B1391" s="18" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="C1391" s="18" t="s">
         <v>17</v>
@@ -57797,7 +57796,7 @@
         <v>6424</v>
       </c>
       <c r="K1391" s="21" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1392" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57833,15 +57832,15 @@
         <v>6424</v>
       </c>
       <c r="K1392" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1393" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1393" s="31" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B1393" s="6" t="s">
         <v>2088</v>
-      </c>
-      <c r="B1393" s="6" t="s">
-        <v>2089</v>
       </c>
       <c r="C1393" s="6" t="s">
         <v>17</v>
@@ -57869,15 +57868,15 @@
         <v>6425</v>
       </c>
       <c r="K1393" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1394" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1394" s="31" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1394" s="6" t="s">
         <v>2090</v>
-      </c>
-      <c r="B1394" s="6" t="s">
-        <v>2091</v>
       </c>
       <c r="C1394" s="6" t="s">
         <v>17</v>
@@ -57905,7 +57904,7 @@
         <v>6425</v>
       </c>
       <c r="K1394" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1395" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57913,7 +57912,7 @@
         <v>1673</v>
       </c>
       <c r="B1395" s="6" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="C1395" s="6" t="s">
         <v>17</v>
@@ -57941,15 +57940,15 @@
         <v>6425</v>
       </c>
       <c r="K1395" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1396" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1396" s="31" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1396" s="6" t="s">
         <v>2093</v>
-      </c>
-      <c r="B1396" s="6" t="s">
-        <v>2094</v>
       </c>
       <c r="C1396" s="6" t="s">
         <v>17</v>
@@ -57977,13 +57976,13 @@
         <v>6425</v>
       </c>
       <c r="K1396" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1397" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1397" s="42"/>
       <c r="B1397" s="18" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="C1397" s="18" t="s">
         <v>40</v>
@@ -58011,15 +58010,15 @@
         <v>6426</v>
       </c>
       <c r="K1397" s="21" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1398" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1398" s="31" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B1398" s="6" t="s">
         <v>2096</v>
-      </c>
-      <c r="B1398" s="6" t="s">
-        <v>2097</v>
       </c>
       <c r="C1398" s="6" t="s">
         <v>17</v>
@@ -58047,15 +58046,15 @@
         <v>6426</v>
       </c>
       <c r="K1398" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1399" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1399" s="31" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1399" s="6" t="s">
         <v>2098</v>
-      </c>
-      <c r="B1399" s="6" t="s">
-        <v>2099</v>
       </c>
       <c r="C1399" s="6" t="s">
         <v>17</v>
@@ -58077,21 +58076,21 @@
         <v>46209</v>
       </c>
       <c r="I1399" s="6" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J1399" s="6">
         <v>6427</v>
       </c>
       <c r="K1399" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1400" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1400" s="31" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1400" s="6" t="s">
         <v>2100</v>
-      </c>
-      <c r="B1400" s="6" t="s">
-        <v>2101</v>
       </c>
       <c r="C1400" s="6" t="s">
         <v>17</v>
@@ -58119,15 +58118,15 @@
         <v>6428</v>
       </c>
       <c r="K1400" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1401" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1401" s="31" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1401" s="6" t="s">
         <v>2102</v>
-      </c>
-      <c r="B1401" s="6" t="s">
-        <v>2103</v>
       </c>
       <c r="C1401" s="6" t="s">
         <v>17</v>
@@ -58149,21 +58148,21 @@
         <v>46240</v>
       </c>
       <c r="I1401" s="6" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="J1401" s="6">
         <v>6429</v>
       </c>
       <c r="K1401" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1402" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1402" s="31" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1402" s="6" t="s">
         <v>2105</v>
-      </c>
-      <c r="B1402" s="6" t="s">
-        <v>2106</v>
       </c>
       <c r="C1402" s="6" t="s">
         <v>17</v>
@@ -58185,13 +58184,13 @@
         <v>46240</v>
       </c>
       <c r="I1402" s="6" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="J1402" s="6">
         <v>6429</v>
       </c>
       <c r="K1402" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1403" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58199,7 +58198,7 @@
         <v>470</v>
       </c>
       <c r="B1403" s="6" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="C1403" s="6" t="s">
         <v>348</v>
@@ -58221,21 +58220,21 @@
         <v>46240</v>
       </c>
       <c r="I1403" s="6" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="J1403" s="6">
         <v>6429</v>
       </c>
       <c r="K1403" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1404" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1404" s="32" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1404" s="6" t="s">
         <v>2108</v>
-      </c>
-      <c r="B1404" s="6" t="s">
-        <v>2109</v>
       </c>
       <c r="C1404" s="6" t="s">
         <v>17</v>
@@ -58263,7 +58262,7 @@
         <v>6430</v>
       </c>
       <c r="K1404" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1405" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58271,7 +58270,7 @@
         <v>330</v>
       </c>
       <c r="B1405" s="6" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C1405" s="6" t="s">
         <v>40</v>
@@ -58299,15 +58298,15 @@
         <v>6431</v>
       </c>
       <c r="K1405" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1406" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1406" s="31" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1406" s="6" t="s">
         <v>2111</v>
-      </c>
-      <c r="B1406" s="6" t="s">
-        <v>2112</v>
       </c>
       <c r="C1406" s="6" t="s">
         <v>17</v>
@@ -58335,15 +58334,15 @@
         <v>6431</v>
       </c>
       <c r="K1406" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1407" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1407" s="31" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1407" s="6" t="s">
         <v>2113</v>
-      </c>
-      <c r="B1407" s="6" t="s">
-        <v>2114</v>
       </c>
       <c r="C1407" s="6" t="s">
         <v>17</v>
@@ -58371,15 +58370,15 @@
         <v>6431</v>
       </c>
       <c r="K1407" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1408" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1408" s="31" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1408" s="6" t="s">
         <v>2115</v>
-      </c>
-      <c r="B1408" s="6" t="s">
-        <v>2116</v>
       </c>
       <c r="C1408" s="6" t="s">
         <v>17</v>
@@ -58407,15 +58406,15 @@
         <v>6431</v>
       </c>
       <c r="K1408" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1409" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1409" s="31" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1409" s="6" t="s">
         <v>2117</v>
-      </c>
-      <c r="B1409" s="6" t="s">
-        <v>2118</v>
       </c>
       <c r="C1409" s="6" t="s">
         <v>17</v>
@@ -58443,7 +58442,7 @@
         <v>6431</v>
       </c>
       <c r="K1409" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1410" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58451,7 +58450,7 @@
         <v>253</v>
       </c>
       <c r="B1410" s="6" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="C1410" s="6" t="s">
         <v>17</v>
@@ -58479,7 +58478,7 @@
         <v>6431</v>
       </c>
       <c r="K1410" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1411" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58487,7 +58486,7 @@
         <v>254</v>
       </c>
       <c r="B1411" s="6" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="C1411" s="6" t="s">
         <v>17</v>
@@ -58515,7 +58514,7 @@
         <v>6431</v>
       </c>
       <c r="K1411" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1412" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58523,7 +58522,7 @@
         <v>495</v>
       </c>
       <c r="B1412" s="6" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="C1412" s="6" t="s">
         <v>17</v>
@@ -58551,15 +58550,15 @@
         <v>6431</v>
       </c>
       <c r="K1412" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1413" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1413" s="31" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B1413" s="6" t="s">
         <v>2122</v>
-      </c>
-      <c r="B1413" s="6" t="s">
-        <v>2123</v>
       </c>
       <c r="C1413" s="6" t="s">
         <v>17</v>
@@ -58587,15 +58586,15 @@
         <v>6431</v>
       </c>
       <c r="K1413" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1414" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1414" s="31" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1414" s="6" t="s">
         <v>2124</v>
-      </c>
-      <c r="B1414" s="6" t="s">
-        <v>2125</v>
       </c>
       <c r="C1414" s="6" t="s">
         <v>17</v>
@@ -58623,7 +58622,7 @@
         <v>6432</v>
       </c>
       <c r="K1414" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1415" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58631,7 +58630,7 @@
         <v>983</v>
       </c>
       <c r="B1415" s="6" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="C1415" s="6" t="s">
         <v>17</v>
@@ -58650,7 +58649,7 @@
         <v>718</v>
       </c>
       <c r="H1415" s="12" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1415" s="6" t="s">
         <v>37</v>
@@ -58659,15 +58658,15 @@
         <v>6433</v>
       </c>
       <c r="K1415" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1416" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1416" s="31" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1416" s="6" t="s">
         <v>2127</v>
-      </c>
-      <c r="B1416" s="6" t="s">
-        <v>2128</v>
       </c>
       <c r="C1416" s="6" t="s">
         <v>17</v>
@@ -58686,7 +58685,7 @@
         <v>34472</v>
       </c>
       <c r="H1416" s="12" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="I1416" s="6" t="s">
         <v>121</v>
@@ -58695,7 +58694,7 @@
         <v>6434</v>
       </c>
       <c r="K1416" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1417" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58703,7 +58702,7 @@
         <v>1631</v>
       </c>
       <c r="B1417" s="6" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C1417" s="6" t="s">
         <v>17</v>
@@ -58722,7 +58721,7 @@
         <v>34472</v>
       </c>
       <c r="H1417" s="12" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="I1417" s="6" t="s">
         <v>121</v>
@@ -58731,15 +58730,15 @@
         <v>6434</v>
       </c>
       <c r="K1417" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1418" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1418" s="31" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1418" s="6" t="s">
         <v>2130</v>
-      </c>
-      <c r="B1418" s="6" t="s">
-        <v>2131</v>
       </c>
       <c r="C1418" s="6" t="s">
         <v>40</v>
@@ -58758,7 +58757,7 @@
         <v>717</v>
       </c>
       <c r="H1418" s="12" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="I1418" s="6" t="s">
         <v>37</v>
@@ -58767,7 +58766,7 @@
         <v>6435</v>
       </c>
       <c r="K1418" s="12" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1419" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58775,7 +58774,7 @@
         <v>515</v>
       </c>
       <c r="B1419" s="6" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C1419" s="6" t="s">
         <v>17</v>
@@ -58794,7 +58793,7 @@
         <v>10609</v>
       </c>
       <c r="H1419" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1419" s="6" t="s">
         <v>517</v>
@@ -58803,7 +58802,7 @@
         <v>6436</v>
       </c>
       <c r="K1419" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1420" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58811,7 +58810,7 @@
         <v>518</v>
       </c>
       <c r="B1420" s="6" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="C1420" s="6" t="s">
         <v>17</v>
@@ -58830,7 +58829,7 @@
         <v>10609</v>
       </c>
       <c r="H1420" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1420" s="6" t="s">
         <v>517</v>
@@ -58839,7 +58838,7 @@
         <v>6436</v>
       </c>
       <c r="K1420" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1421" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58847,7 +58846,7 @@
         <v>520</v>
       </c>
       <c r="B1421" s="6" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C1421" s="6" t="s">
         <v>17</v>
@@ -58866,7 +58865,7 @@
         <v>10609</v>
       </c>
       <c r="H1421" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1421" s="6" t="s">
         <v>517</v>
@@ -58875,7 +58874,7 @@
         <v>6436</v>
       </c>
       <c r="K1421" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1422" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58902,7 +58901,7 @@
         <v>13910</v>
       </c>
       <c r="H1422" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1422" s="6" t="s">
         <v>116</v>
@@ -58911,7 +58910,7 @@
         <v>6437</v>
       </c>
       <c r="K1422" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1423" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58938,7 +58937,7 @@
         <v>13910</v>
       </c>
       <c r="H1423" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1423" s="6" t="s">
         <v>116</v>
@@ -58947,7 +58946,7 @@
         <v>6437</v>
       </c>
       <c r="K1423" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1424" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58974,7 +58973,7 @@
         <v>13910</v>
       </c>
       <c r="H1424" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1424" s="6" t="s">
         <v>116</v>
@@ -58983,7 +58982,7 @@
         <v>6437</v>
       </c>
       <c r="K1424" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1425" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58991,7 +58990,7 @@
         <v>1030</v>
       </c>
       <c r="B1425" s="6" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="C1425" s="6" t="s">
         <v>17</v>
@@ -59010,7 +59009,7 @@
         <v>13910</v>
       </c>
       <c r="H1425" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1425" s="6" t="s">
         <v>116</v>
@@ -59019,15 +59018,15 @@
         <v>6437</v>
       </c>
       <c r="K1425" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1426" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1426" s="31" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B1426" s="6" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C1426" s="6" t="s">
         <v>17</v>
@@ -59046,7 +59045,7 @@
         <v>13902</v>
       </c>
       <c r="H1426" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1426" s="6" t="s">
         <v>116</v>
@@ -59055,15 +59054,15 @@
         <v>6438</v>
       </c>
       <c r="K1426" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1427" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1427" s="31" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1427" s="6" t="s">
         <v>2136</v>
-      </c>
-      <c r="B1427" s="6" t="s">
-        <v>2137</v>
       </c>
       <c r="C1427" s="6" t="s">
         <v>17</v>
@@ -59082,7 +59081,7 @@
         <v>13902</v>
       </c>
       <c r="H1427" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1427" s="6" t="s">
         <v>116</v>
@@ -59091,15 +59090,15 @@
         <v>6438</v>
       </c>
       <c r="K1427" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1428" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1428" s="31" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1428" s="6" t="s">
         <v>2138</v>
-      </c>
-      <c r="B1428" s="6" t="s">
-        <v>2139</v>
       </c>
       <c r="C1428" s="6" t="s">
         <v>17</v>
@@ -59118,7 +59117,7 @@
         <v>13902</v>
       </c>
       <c r="H1428" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1428" s="6" t="s">
         <v>116</v>
@@ -59127,15 +59126,15 @@
         <v>6438</v>
       </c>
       <c r="K1428" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1429" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1429" s="31" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B1429" s="6" t="s">
         <v>2140</v>
-      </c>
-      <c r="B1429" s="6" t="s">
-        <v>2141</v>
       </c>
       <c r="C1429" s="6" t="s">
         <v>17</v>
@@ -59154,7 +59153,7 @@
         <v>13902</v>
       </c>
       <c r="H1429" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1429" s="6" t="s">
         <v>116</v>
@@ -59163,15 +59162,15 @@
         <v>6438</v>
       </c>
       <c r="K1429" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1430" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1430" s="31" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1430" s="6" t="s">
         <v>2142</v>
-      </c>
-      <c r="B1430" s="6" t="s">
-        <v>2143</v>
       </c>
       <c r="C1430" s="6" t="s">
         <v>17</v>
@@ -59190,7 +59189,7 @@
         <v>13902</v>
       </c>
       <c r="H1430" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1430" s="6" t="s">
         <v>116</v>
@@ -59199,15 +59198,15 @@
         <v>6438</v>
       </c>
       <c r="K1430" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1431" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1431" s="31" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B1431" s="6" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C1431" s="6" t="s">
         <v>17</v>
@@ -59226,7 +59225,7 @@
         <v>13902</v>
       </c>
       <c r="H1431" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1431" s="6" t="s">
         <v>116</v>
@@ -59235,15 +59234,15 @@
         <v>6438</v>
       </c>
       <c r="K1431" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1432" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1432" s="31" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B1432" s="6" t="s">
         <v>2145</v>
-      </c>
-      <c r="B1432" s="6" t="s">
-        <v>2146</v>
       </c>
       <c r="C1432" s="6" t="s">
         <v>17</v>
@@ -59262,7 +59261,7 @@
         <v>13902</v>
       </c>
       <c r="H1432" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1432" s="6" t="s">
         <v>116</v>
@@ -59271,7 +59270,7 @@
         <v>6438</v>
       </c>
       <c r="K1432" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1433" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59298,7 +59297,7 @@
         <v>13902</v>
       </c>
       <c r="H1433" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1433" s="6" t="s">
         <v>116</v>
@@ -59307,15 +59306,15 @@
         <v>6438</v>
       </c>
       <c r="K1433" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1434" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1434" s="31" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B1434" s="17" t="s">
         <v>2147</v>
-      </c>
-      <c r="B1434" s="17" t="s">
-        <v>2148</v>
       </c>
       <c r="C1434" s="6" t="s">
         <v>17</v>
@@ -59334,7 +59333,7 @@
         <v>13902</v>
       </c>
       <c r="H1434" s="12" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1434" s="6" t="s">
         <v>116</v>
@@ -59343,7 +59342,7 @@
         <v>6438</v>
       </c>
       <c r="K1434" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1435" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59351,7 +59350,7 @@
         <v>289</v>
       </c>
       <c r="B1435" s="6" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="C1435" s="6" t="s">
         <v>17</v>
@@ -59370,7 +59369,7 @@
         <v>2474</v>
       </c>
       <c r="H1435" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1435" s="6" t="s">
         <v>799</v>
@@ -59379,15 +59378,15 @@
         <v>6439</v>
       </c>
       <c r="K1435" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1436" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1436" s="32" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1436" s="6" t="s">
         <v>2151</v>
-      </c>
-      <c r="B1436" s="6" t="s">
-        <v>2152</v>
       </c>
       <c r="C1436" s="6" t="s">
         <v>17</v>
@@ -59406,7 +59405,7 @@
         <v>2474</v>
       </c>
       <c r="H1436" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1436" s="6" t="s">
         <v>799</v>
@@ -59415,15 +59414,15 @@
         <v>6439</v>
       </c>
       <c r="K1436" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1437" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1437" s="32" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1437" s="6" t="s">
         <v>2153</v>
-      </c>
-      <c r="B1437" s="6" t="s">
-        <v>2154</v>
       </c>
       <c r="C1437" s="6" t="s">
         <v>17</v>
@@ -59442,7 +59441,7 @@
         <v>2474</v>
       </c>
       <c r="H1437" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1437" s="6" t="s">
         <v>799</v>
@@ -59451,7 +59450,7 @@
         <v>6439</v>
       </c>
       <c r="K1437" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1438" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59478,7 +59477,7 @@
         <v>2474</v>
       </c>
       <c r="H1438" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1438" s="6" t="s">
         <v>799</v>
@@ -59487,7 +59486,7 @@
         <v>6439</v>
       </c>
       <c r="K1438" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1439" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59495,7 +59494,7 @@
         <v>562</v>
       </c>
       <c r="B1439" s="6" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="C1439" s="6" t="s">
         <v>17</v>
@@ -59514,7 +59513,7 @@
         <v>2474</v>
       </c>
       <c r="H1439" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1439" s="6" t="s">
         <v>799</v>
@@ -59523,7 +59522,7 @@
         <v>6439</v>
       </c>
       <c r="K1439" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1440" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59531,7 +59530,7 @@
         <v>641</v>
       </c>
       <c r="B1440" s="6" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="C1440" s="6" t="s">
         <v>17</v>
@@ -59550,7 +59549,7 @@
         <v>2474</v>
       </c>
       <c r="H1440" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1440" s="6" t="s">
         <v>799</v>
@@ -59559,15 +59558,15 @@
         <v>6439</v>
       </c>
       <c r="K1440" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1441" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1441" s="32" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B1441" s="6" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C1441" s="6" t="s">
         <v>17</v>
@@ -59586,7 +59585,7 @@
         <v>2474</v>
       </c>
       <c r="H1441" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1441" s="6" t="s">
         <v>799</v>
@@ -59595,7 +59594,7 @@
         <v>6439</v>
       </c>
       <c r="K1441" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1442" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59622,7 +59621,7 @@
         <v>2474</v>
       </c>
       <c r="H1442" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1442" s="6" t="s">
         <v>799</v>
@@ -59631,7 +59630,7 @@
         <v>6439</v>
       </c>
       <c r="K1442" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1443" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59658,7 +59657,7 @@
         <v>2474</v>
       </c>
       <c r="H1443" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1443" s="6" t="s">
         <v>799</v>
@@ -59667,7 +59666,7 @@
         <v>6439</v>
       </c>
       <c r="K1443" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1444" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59694,7 +59693,7 @@
         <v>2474</v>
       </c>
       <c r="H1444" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1444" s="6" t="s">
         <v>799</v>
@@ -59703,7 +59702,7 @@
         <v>6439</v>
       </c>
       <c r="K1444" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1445" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59711,7 +59710,7 @@
         <v>301</v>
       </c>
       <c r="B1445" s="6" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="C1445" s="6" t="s">
         <v>17</v>
@@ -59730,7 +59729,7 @@
         <v>2474</v>
       </c>
       <c r="H1445" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1445" s="6" t="s">
         <v>799</v>
@@ -59739,7 +59738,7 @@
         <v>6439</v>
       </c>
       <c r="K1445" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1446" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59747,7 +59746,7 @@
         <v>286</v>
       </c>
       <c r="B1446" s="6" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="C1446" s="6" t="s">
         <v>17</v>
@@ -59766,7 +59765,7 @@
         <v>2474</v>
       </c>
       <c r="H1446" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1446" s="6" t="s">
         <v>799</v>
@@ -59775,7 +59774,7 @@
         <v>6439</v>
       </c>
       <c r="K1446" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1447" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59802,7 +59801,7 @@
         <v>2474</v>
       </c>
       <c r="H1447" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1447" s="6" t="s">
         <v>799</v>
@@ -59811,7 +59810,7 @@
         <v>6440</v>
       </c>
       <c r="K1447" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1448" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59838,7 +59837,7 @@
         <v>2474</v>
       </c>
       <c r="H1448" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1448" s="6" t="s">
         <v>799</v>
@@ -59847,7 +59846,7 @@
         <v>6440</v>
       </c>
       <c r="K1448" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1449" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59874,7 +59873,7 @@
         <v>2474</v>
       </c>
       <c r="H1449" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1449" s="6" t="s">
         <v>799</v>
@@ -59883,7 +59882,7 @@
         <v>6440</v>
       </c>
       <c r="K1449" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1450" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59891,7 +59890,7 @@
         <v>1565</v>
       </c>
       <c r="B1450" s="6" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="C1450" s="6" t="s">
         <v>17</v>
@@ -59910,7 +59909,7 @@
         <v>2474</v>
       </c>
       <c r="H1450" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1450" s="6" t="s">
         <v>799</v>
@@ -59919,13 +59918,13 @@
         <v>6440</v>
       </c>
       <c r="K1450" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1451" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1451" s="42"/>
       <c r="B1451" s="18" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C1451" s="18" t="s">
         <v>17</v>
@@ -59944,22 +59943,22 @@
         <v>133</v>
       </c>
       <c r="H1451" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1451" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1451" s="18">
         <v>6441</v>
       </c>
       <c r="K1451" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1452" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1452" s="42"/>
       <c r="B1452" s="18" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="C1452" s="18" t="s">
         <v>17</v>
@@ -59978,22 +59977,22 @@
         <v>133</v>
       </c>
       <c r="H1452" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1452" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1452" s="18">
         <v>6441</v>
       </c>
       <c r="K1452" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1453" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1453" s="42"/>
       <c r="B1453" s="18" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="C1453" s="18" t="s">
         <v>17</v>
@@ -60012,22 +60011,22 @@
         <v>133</v>
       </c>
       <c r="H1453" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1453" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1453" s="18">
         <v>6441</v>
       </c>
       <c r="K1453" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1454" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1454" s="42"/>
       <c r="B1454" s="18" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C1454" s="18" t="s">
         <v>17</v>
@@ -60046,22 +60045,22 @@
         <v>133</v>
       </c>
       <c r="H1454" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1454" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1454" s="18">
         <v>6441</v>
       </c>
       <c r="K1454" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1455" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1455" s="42"/>
       <c r="B1455" s="18" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="C1455" s="18" t="s">
         <v>17</v>
@@ -60080,22 +60079,22 @@
         <v>133</v>
       </c>
       <c r="H1455" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1455" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1455" s="18">
         <v>6441</v>
       </c>
       <c r="K1455" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1456" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1456" s="42"/>
       <c r="B1456" s="18" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="C1456" s="18" t="s">
         <v>17</v>
@@ -60114,22 +60113,22 @@
         <v>133</v>
       </c>
       <c r="H1456" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1456" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1456" s="18">
         <v>6441</v>
       </c>
       <c r="K1456" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1457" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1457" s="42"/>
       <c r="B1457" s="18" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C1457" s="18" t="s">
         <v>17</v>
@@ -60148,22 +60147,22 @@
         <v>133</v>
       </c>
       <c r="H1457" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1457" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1457" s="18">
         <v>6441</v>
       </c>
       <c r="K1457" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1458" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1458" s="42"/>
       <c r="B1458" s="18" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="C1458" s="18" t="s">
         <v>17</v>
@@ -60182,22 +60181,22 @@
         <v>133</v>
       </c>
       <c r="H1458" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1458" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1458" s="18">
         <v>6441</v>
       </c>
       <c r="K1458" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1459" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1459" s="42"/>
       <c r="B1459" s="18" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="C1459" s="18" t="s">
         <v>17</v>
@@ -60216,16 +60215,16 @@
         <v>133</v>
       </c>
       <c r="H1459" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1459" s="18" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J1459" s="18">
         <v>6441</v>
       </c>
       <c r="K1459" s="21" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1460" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60233,7 +60232,7 @@
         <v>687</v>
       </c>
       <c r="B1460" s="6" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C1460" s="6" t="s">
         <v>17</v>
@@ -60261,15 +60260,15 @@
         <v>6442</v>
       </c>
       <c r="K1460" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1461" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1461" s="31" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B1461" s="6" t="s">
         <v>2170</v>
-      </c>
-      <c r="B1461" s="6" t="s">
-        <v>2171</v>
       </c>
       <c r="C1461" s="6" t="s">
         <v>17</v>
@@ -60297,12 +60296,12 @@
         <v>6443</v>
       </c>
       <c r="K1461" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1462" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1462" s="31" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="B1462" s="6" t="s">
         <v>1135</v>
@@ -60333,15 +60332,15 @@
         <v>6443</v>
       </c>
       <c r="K1462" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1463" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1463" s="31" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1463" s="6" t="s">
         <v>2173</v>
-      </c>
-      <c r="B1463" s="6" t="s">
-        <v>2174</v>
       </c>
       <c r="C1463" s="6" t="s">
         <v>17</v>
@@ -60360,7 +60359,7 @@
         <v>129</v>
       </c>
       <c r="H1463" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1463" s="6" t="s">
         <v>346</v>
@@ -60369,15 +60368,15 @@
         <v>6444</v>
       </c>
       <c r="K1463" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1464" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1464" s="31" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B1464" s="6" t="s">
         <v>2175</v>
-      </c>
-      <c r="B1464" s="6" t="s">
-        <v>2176</v>
       </c>
       <c r="C1464" s="6" t="s">
         <v>17</v>
@@ -60396,7 +60395,7 @@
         <v>129</v>
       </c>
       <c r="H1464" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1464" s="6" t="s">
         <v>346</v>
@@ -60405,15 +60404,15 @@
         <v>6444</v>
       </c>
       <c r="K1464" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1465" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1465" s="31" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1465" s="6" t="s">
         <v>2177</v>
-      </c>
-      <c r="B1465" s="6" t="s">
-        <v>2178</v>
       </c>
       <c r="C1465" s="6" t="s">
         <v>17</v>
@@ -60432,7 +60431,7 @@
         <v>129</v>
       </c>
       <c r="H1465" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1465" s="6" t="s">
         <v>346</v>
@@ -60441,15 +60440,15 @@
         <v>6444</v>
       </c>
       <c r="K1465" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1466" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1466" s="31" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1466" s="6" t="s">
         <v>2179</v>
-      </c>
-      <c r="B1466" s="6" t="s">
-        <v>2180</v>
       </c>
       <c r="C1466" s="6" t="s">
         <v>17</v>
@@ -60468,7 +60467,7 @@
         <v>129</v>
       </c>
       <c r="H1466" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1466" s="6" t="s">
         <v>346</v>
@@ -60477,15 +60476,15 @@
         <v>6444</v>
       </c>
       <c r="K1466" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1467" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1467" s="31" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B1467" s="6" t="s">
         <v>2181</v>
-      </c>
-      <c r="B1467" s="6" t="s">
-        <v>2182</v>
       </c>
       <c r="C1467" s="6" t="s">
         <v>17</v>
@@ -60504,7 +60503,7 @@
         <v>129</v>
       </c>
       <c r="H1467" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1467" s="6" t="s">
         <v>346</v>
@@ -60513,15 +60512,15 @@
         <v>6444</v>
       </c>
       <c r="K1467" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1468" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1468" s="31" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B1468" s="6" t="s">
         <v>2183</v>
-      </c>
-      <c r="B1468" s="6" t="s">
-        <v>2184</v>
       </c>
       <c r="C1468" s="6" t="s">
         <v>17</v>
@@ -60540,7 +60539,7 @@
         <v>129</v>
       </c>
       <c r="H1468" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1468" s="6" t="s">
         <v>346</v>
@@ -60549,15 +60548,15 @@
         <v>6444</v>
       </c>
       <c r="K1468" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1469" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1469" s="31" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1469" s="6" t="s">
         <v>2185</v>
-      </c>
-      <c r="B1469" s="6" t="s">
-        <v>2186</v>
       </c>
       <c r="C1469" s="6" t="s">
         <v>17</v>
@@ -60576,7 +60575,7 @@
         <v>129</v>
       </c>
       <c r="H1469" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1469" s="6" t="s">
         <v>346</v>
@@ -60585,15 +60584,15 @@
         <v>6444</v>
       </c>
       <c r="K1469" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1470" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1470" s="31" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1470" s="6" t="s">
         <v>2187</v>
-      </c>
-      <c r="B1470" s="6" t="s">
-        <v>2188</v>
       </c>
       <c r="C1470" s="6" t="s">
         <v>40</v>
@@ -60612,24 +60611,24 @@
         <v>5</v>
       </c>
       <c r="H1470" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1470" s="6" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="J1470" s="6">
         <v>6445</v>
       </c>
       <c r="K1470" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1471" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1471" s="31" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1471" s="6" t="s">
         <v>2190</v>
-      </c>
-      <c r="B1471" s="6" t="s">
-        <v>2191</v>
       </c>
       <c r="C1471" s="6" t="s">
         <v>40</v>
@@ -60648,24 +60647,24 @@
         <v>5</v>
       </c>
       <c r="H1471" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1471" s="6" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="J1471" s="6">
         <v>6445</v>
       </c>
       <c r="K1471" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1472" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1472" s="31" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1472" s="6" t="s">
         <v>2192</v>
-      </c>
-      <c r="B1472" s="6" t="s">
-        <v>2193</v>
       </c>
       <c r="C1472" s="6" t="s">
         <v>40</v>
@@ -60684,24 +60683,24 @@
         <v>5</v>
       </c>
       <c r="H1472" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1472" s="6" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="J1472" s="6">
         <v>6445</v>
       </c>
       <c r="K1472" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1473" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1473" s="31" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1473" s="6" t="s">
         <v>2194</v>
-      </c>
-      <c r="B1473" s="6" t="s">
-        <v>2195</v>
       </c>
       <c r="C1473" s="6" t="s">
         <v>40</v>
@@ -60720,16 +60719,16 @@
         <v>5</v>
       </c>
       <c r="H1473" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1473" s="6" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="J1473" s="6">
         <v>6445</v>
       </c>
       <c r="K1473" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1474" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60737,7 +60736,7 @@
         <v>205</v>
       </c>
       <c r="B1474" s="6" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="C1474" s="6" t="s">
         <v>17</v>
@@ -60756,7 +60755,7 @@
         <v>131</v>
       </c>
       <c r="H1474" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1474" s="6" t="s">
         <v>346</v>
@@ -60765,15 +60764,15 @@
         <v>6446</v>
       </c>
       <c r="K1474" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1475" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1475" s="31" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1475" s="6" t="s">
         <v>2197</v>
-      </c>
-      <c r="B1475" s="6" t="s">
-        <v>2198</v>
       </c>
       <c r="C1475" s="6" t="s">
         <v>17</v>
@@ -60792,7 +60791,7 @@
         <v>131</v>
       </c>
       <c r="H1475" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1475" s="6" t="s">
         <v>346</v>
@@ -60801,15 +60800,15 @@
         <v>6446</v>
       </c>
       <c r="K1475" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1476" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1476" s="32" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1476" s="6" t="s">
         <v>2199</v>
-      </c>
-      <c r="B1476" s="6" t="s">
-        <v>2200</v>
       </c>
       <c r="C1476" s="6" t="s">
         <v>17</v>
@@ -60828,7 +60827,7 @@
         <v>131</v>
       </c>
       <c r="H1476" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1476" s="6" t="s">
         <v>346</v>
@@ -60837,7 +60836,7 @@
         <v>6446</v>
       </c>
       <c r="K1476" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1477" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60845,7 +60844,7 @@
         <v>233</v>
       </c>
       <c r="B1477" s="6" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="C1477" s="6" t="s">
         <v>17</v>
@@ -60864,7 +60863,7 @@
         <v>131</v>
       </c>
       <c r="H1477" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1477" s="6" t="s">
         <v>346</v>
@@ -60873,7 +60872,7 @@
         <v>6446</v>
       </c>
       <c r="K1477" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1478" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60881,7 +60880,7 @@
         <v>1370</v>
       </c>
       <c r="B1478" s="6" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C1478" s="6" t="s">
         <v>17</v>
@@ -60900,7 +60899,7 @@
         <v>131</v>
       </c>
       <c r="H1478" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1478" s="6" t="s">
         <v>346</v>
@@ -60909,15 +60908,15 @@
         <v>6446</v>
       </c>
       <c r="K1478" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1479" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1479" s="32" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1479" s="6" t="s">
         <v>2203</v>
-      </c>
-      <c r="B1479" s="6" t="s">
-        <v>2204</v>
       </c>
       <c r="C1479" s="6" t="s">
         <v>17</v>
@@ -60936,7 +60935,7 @@
         <v>131</v>
       </c>
       <c r="H1479" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1479" s="6" t="s">
         <v>346</v>
@@ -60945,15 +60944,15 @@
         <v>6446</v>
       </c>
       <c r="K1479" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1480" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1480" s="33" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1480" s="6" t="s">
         <v>2205</v>
-      </c>
-      <c r="B1480" s="6" t="s">
-        <v>2206</v>
       </c>
       <c r="C1480" s="6" t="s">
         <v>17</v>
@@ -60972,7 +60971,7 @@
         <v>131</v>
       </c>
       <c r="H1480" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1480" s="6" t="s">
         <v>346</v>
@@ -60981,15 +60980,15 @@
         <v>6446</v>
       </c>
       <c r="K1480" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1481" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1481" s="32" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B1481" s="6" t="s">
         <v>2207</v>
-      </c>
-      <c r="B1481" s="6" t="s">
-        <v>2208</v>
       </c>
       <c r="C1481" s="6" t="s">
         <v>17</v>
@@ -61008,7 +61007,7 @@
         <v>131</v>
       </c>
       <c r="H1481" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1481" s="6" t="s">
         <v>346</v>
@@ -61017,7 +61016,7 @@
         <v>6446</v>
       </c>
       <c r="K1481" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1482" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61025,7 +61024,7 @@
         <v>333</v>
       </c>
       <c r="B1482" s="6" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="C1482" s="6" t="s">
         <v>17</v>
@@ -61044,7 +61043,7 @@
         <v>131</v>
       </c>
       <c r="H1482" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1482" s="6" t="s">
         <v>346</v>
@@ -61053,7 +61052,7 @@
         <v>6446</v>
       </c>
       <c r="K1482" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1483" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61061,7 +61060,7 @@
         <v>303</v>
       </c>
       <c r="B1483" s="6" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C1483" s="6" t="s">
         <v>17</v>
@@ -61080,7 +61079,7 @@
         <v>131</v>
       </c>
       <c r="H1483" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1483" s="6" t="s">
         <v>346</v>
@@ -61089,7 +61088,7 @@
         <v>6446</v>
       </c>
       <c r="K1483" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1484" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61116,7 +61115,7 @@
         <v>131</v>
       </c>
       <c r="H1484" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1484" s="6" t="s">
         <v>346</v>
@@ -61125,7 +61124,7 @@
         <v>6446</v>
       </c>
       <c r="K1484" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1485" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61152,7 +61151,7 @@
         <v>5070</v>
       </c>
       <c r="H1485" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1485" s="6" t="s">
         <v>66</v>
@@ -61161,7 +61160,7 @@
         <v>6447</v>
       </c>
       <c r="K1485" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1486" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61188,7 +61187,7 @@
         <v>5070</v>
       </c>
       <c r="H1486" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1486" s="6" t="s">
         <v>66</v>
@@ -61197,15 +61196,15 @@
         <v>6447</v>
       </c>
       <c r="K1486" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1487" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1487" s="31" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B1487" s="6" t="s">
         <v>2209</v>
-      </c>
-      <c r="B1487" s="6" t="s">
-        <v>2210</v>
       </c>
       <c r="C1487" s="6" t="s">
         <v>17</v>
@@ -61224,7 +61223,7 @@
         <v>5070</v>
       </c>
       <c r="H1487" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1487" s="6" t="s">
         <v>66</v>
@@ -61233,7 +61232,7 @@
         <v>6447</v>
       </c>
       <c r="K1487" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1488" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61260,7 +61259,7 @@
         <v>5070</v>
       </c>
       <c r="H1488" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1488" s="6" t="s">
         <v>66</v>
@@ -61269,7 +61268,7 @@
         <v>6447</v>
       </c>
       <c r="K1488" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1489" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61296,7 +61295,7 @@
         <v>5070</v>
       </c>
       <c r="H1489" s="12" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I1489" s="6" t="s">
         <v>66</v>
@@ -61305,7 +61304,7 @@
         <v>6447</v>
       </c>
       <c r="K1489" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1490" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61313,7 +61312,7 @@
         <v>268</v>
       </c>
       <c r="B1490" s="6" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="C1490" s="6" t="s">
         <v>17</v>
@@ -61332,7 +61331,7 @@
         <v>135</v>
       </c>
       <c r="H1490" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1490" s="6" t="s">
         <v>346</v>
@@ -61341,15 +61340,15 @@
         <v>6448</v>
       </c>
       <c r="K1490" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1491" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1491" s="32" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1491" s="6" t="s">
         <v>2212</v>
-      </c>
-      <c r="B1491" s="6" t="s">
-        <v>2213</v>
       </c>
       <c r="C1491" s="6" t="s">
         <v>17</v>
@@ -61368,7 +61367,7 @@
         <v>135</v>
       </c>
       <c r="H1491" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1491" s="6" t="s">
         <v>346</v>
@@ -61377,15 +61376,15 @@
         <v>6448</v>
       </c>
       <c r="K1491" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1492" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1492" s="33" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1492" s="6" t="s">
         <v>2214</v>
-      </c>
-      <c r="B1492" s="6" t="s">
-        <v>2215</v>
       </c>
       <c r="C1492" s="6" t="s">
         <v>17</v>
@@ -61404,7 +61403,7 @@
         <v>135</v>
       </c>
       <c r="H1492" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1492" s="6" t="s">
         <v>346</v>
@@ -61413,15 +61412,15 @@
         <v>6448</v>
       </c>
       <c r="K1492" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1493" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1493" s="32" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1493" s="6" t="s">
         <v>2216</v>
-      </c>
-      <c r="B1493" s="6" t="s">
-        <v>2217</v>
       </c>
       <c r="C1493" s="6" t="s">
         <v>17</v>
@@ -61440,7 +61439,7 @@
         <v>135</v>
       </c>
       <c r="H1493" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1493" s="6" t="s">
         <v>346</v>
@@ -61449,15 +61448,15 @@
         <v>6448</v>
       </c>
       <c r="K1493" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1494" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1494" s="31" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1494" s="6" t="s">
         <v>2218</v>
-      </c>
-      <c r="B1494" s="6" t="s">
-        <v>2219</v>
       </c>
       <c r="C1494" s="6" t="s">
         <v>17</v>
@@ -61476,7 +61475,7 @@
         <v>135</v>
       </c>
       <c r="H1494" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1494" s="6" t="s">
         <v>346</v>
@@ -61485,15 +61484,15 @@
         <v>6448</v>
       </c>
       <c r="K1494" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1495" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1495" s="31" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1495" s="6" t="s">
         <v>2220</v>
-      </c>
-      <c r="B1495" s="6" t="s">
-        <v>2221</v>
       </c>
       <c r="C1495" s="6" t="s">
         <v>17</v>
@@ -61512,7 +61511,7 @@
         <v>135</v>
       </c>
       <c r="H1495" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1495" s="6" t="s">
         <v>346</v>
@@ -61521,15 +61520,15 @@
         <v>6448</v>
       </c>
       <c r="K1495" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1496" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1496" s="31" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1496" s="6" t="s">
         <v>2222</v>
-      </c>
-      <c r="B1496" s="6" t="s">
-        <v>2223</v>
       </c>
       <c r="C1496" s="6" t="s">
         <v>17</v>
@@ -61548,7 +61547,7 @@
         <v>135</v>
       </c>
       <c r="H1496" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1496" s="6" t="s">
         <v>346</v>
@@ -61557,7 +61556,7 @@
         <v>6448</v>
       </c>
       <c r="K1496" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1497" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61584,7 +61583,7 @@
         <v>14285</v>
       </c>
       <c r="H1497" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1497" s="6" t="s">
         <v>116</v>
@@ -61593,15 +61592,15 @@
         <v>6449</v>
       </c>
       <c r="K1497" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1498" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1498" s="31" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B1498" s="6" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="C1498" s="6" t="s">
         <v>17</v>
@@ -61620,7 +61619,7 @@
         <v>14285</v>
       </c>
       <c r="H1498" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1498" s="6" t="s">
         <v>116</v>
@@ -61629,7 +61628,7 @@
         <v>6449</v>
       </c>
       <c r="K1498" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1499" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61637,7 +61636,7 @@
         <v>323</v>
       </c>
       <c r="B1499" s="6" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="C1499" s="6" t="s">
         <v>17</v>
@@ -61656,7 +61655,7 @@
         <v>14285</v>
       </c>
       <c r="H1499" s="12" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1499" s="6" t="s">
         <v>116</v>
@@ -61665,7 +61664,7 @@
         <v>6449</v>
       </c>
       <c r="K1499" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1500" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61692,7 +61691,7 @@
         <v>5103</v>
       </c>
       <c r="H1500" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1500" s="6" t="s">
         <v>66</v>
@@ -61701,15 +61700,15 @@
         <v>6450</v>
       </c>
       <c r="K1500" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1501" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1501" s="31" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1501" s="6" t="s">
         <v>2226</v>
-      </c>
-      <c r="B1501" s="6" t="s">
-        <v>2227</v>
       </c>
       <c r="C1501" s="6" t="s">
         <v>17</v>
@@ -61728,7 +61727,7 @@
         <v>5103</v>
       </c>
       <c r="H1501" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1501" s="6" t="s">
         <v>66</v>
@@ -61737,15 +61736,15 @@
         <v>6450</v>
       </c>
       <c r="K1501" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1502" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1502" s="31" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1502" s="6" t="s">
         <v>2228</v>
-      </c>
-      <c r="B1502" s="6" t="s">
-        <v>2229</v>
       </c>
       <c r="C1502" s="6" t="s">
         <v>17</v>
@@ -61764,7 +61763,7 @@
         <v>5103</v>
       </c>
       <c r="H1502" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1502" s="6" t="s">
         <v>66</v>
@@ -61773,15 +61772,15 @@
         <v>6450</v>
       </c>
       <c r="K1502" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1503" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1503" s="31" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1503" s="6" t="s">
         <v>2230</v>
-      </c>
-      <c r="B1503" s="6" t="s">
-        <v>2231</v>
       </c>
       <c r="C1503" s="6" t="s">
         <v>17</v>
@@ -61800,7 +61799,7 @@
         <v>5103</v>
       </c>
       <c r="H1503" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1503" s="6" t="s">
         <v>66</v>
@@ -61809,15 +61808,15 @@
         <v>6450</v>
       </c>
       <c r="K1503" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1504" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1504" s="31" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B1504" s="6" t="s">
         <v>2232</v>
-      </c>
-      <c r="B1504" s="6" t="s">
-        <v>2233</v>
       </c>
       <c r="C1504" s="6" t="s">
         <v>17</v>
@@ -61836,7 +61835,7 @@
         <v>5103</v>
       </c>
       <c r="H1504" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1504" s="6" t="s">
         <v>66</v>
@@ -61845,7 +61844,7 @@
         <v>6450</v>
       </c>
       <c r="K1504" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1505" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61853,7 +61852,7 @@
         <v>338</v>
       </c>
       <c r="B1505" s="6" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="C1505" s="6" t="s">
         <v>17</v>
@@ -61872,7 +61871,7 @@
         <v>5103</v>
       </c>
       <c r="H1505" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1505" s="6" t="s">
         <v>66</v>
@@ -61881,7 +61880,7 @@
         <v>6450</v>
       </c>
       <c r="K1505" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1506" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61889,7 +61888,7 @@
         <v>295</v>
       </c>
       <c r="B1506" s="6" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="C1506" s="6" t="s">
         <v>17</v>
@@ -61908,24 +61907,24 @@
         <v>13</v>
       </c>
       <c r="H1506" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1506" s="6" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="J1506" s="6">
         <v>6451</v>
       </c>
       <c r="K1506" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1507" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1507" s="31" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B1507" s="6" t="s">
         <v>2237</v>
-      </c>
-      <c r="B1507" s="6" t="s">
-        <v>2238</v>
       </c>
       <c r="C1507" s="6" t="s">
         <v>17</v>
@@ -61944,7 +61943,7 @@
         <v>138</v>
       </c>
       <c r="H1507" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1507" s="6" t="s">
         <v>346</v>
@@ -61953,7 +61952,7 @@
         <v>6453</v>
       </c>
       <c r="K1507" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1508" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61961,7 +61960,7 @@
         <v>1038</v>
       </c>
       <c r="B1508" s="6" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="C1508" s="6" t="s">
         <v>40</v>
@@ -61980,7 +61979,7 @@
         <v>138</v>
       </c>
       <c r="H1508" s="12" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1508" s="6" t="s">
         <v>346</v>
@@ -61989,7 +61988,7 @@
         <v>6453</v>
       </c>
       <c r="K1508" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1509" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62016,7 +62015,7 @@
         <v>1504</v>
       </c>
       <c r="H1509" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1509" s="6" t="s">
         <v>1180</v>
@@ -62025,15 +62024,15 @@
         <v>6455</v>
       </c>
       <c r="K1509" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1510" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1510" s="32" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B1510" s="6" t="s">
         <v>2241</v>
-      </c>
-      <c r="B1510" s="6" t="s">
-        <v>2242</v>
       </c>
       <c r="C1510" s="6" t="s">
         <v>17</v>
@@ -62052,7 +62051,7 @@
         <v>1504</v>
       </c>
       <c r="H1510" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1510" s="6" t="s">
         <v>1180</v>
@@ -62061,15 +62060,15 @@
         <v>6455</v>
       </c>
       <c r="K1510" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1511" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1511" s="32" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B1511" s="6" t="s">
         <v>2243</v>
-      </c>
-      <c r="B1511" s="6" t="s">
-        <v>2244</v>
       </c>
       <c r="C1511" s="6" t="s">
         <v>17</v>
@@ -62088,7 +62087,7 @@
         <v>1504</v>
       </c>
       <c r="H1511" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1511" s="6" t="s">
         <v>1180</v>
@@ -62097,15 +62096,15 @@
         <v>6455</v>
       </c>
       <c r="K1511" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1512" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1512" s="32" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B1512" s="6" t="s">
         <v>2245</v>
-      </c>
-      <c r="B1512" s="6" t="s">
-        <v>2246</v>
       </c>
       <c r="C1512" s="6" t="s">
         <v>17</v>
@@ -62124,7 +62123,7 @@
         <v>1504</v>
       </c>
       <c r="H1512" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1512" s="6" t="s">
         <v>1180</v>
@@ -62133,7 +62132,7 @@
         <v>6455</v>
       </c>
       <c r="K1512" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1513" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62160,7 +62159,7 @@
         <v>1504</v>
       </c>
       <c r="H1513" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1513" s="6" t="s">
         <v>1180</v>
@@ -62169,7 +62168,7 @@
         <v>6455</v>
       </c>
       <c r="K1513" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1514" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62177,7 +62176,7 @@
         <v>1203</v>
       </c>
       <c r="B1514" s="6" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="C1514" s="6" t="s">
         <v>17</v>
@@ -62196,7 +62195,7 @@
         <v>1504</v>
       </c>
       <c r="H1514" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1514" s="6" t="s">
         <v>1180</v>
@@ -62205,7 +62204,7 @@
         <v>6455</v>
       </c>
       <c r="K1514" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1515" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62213,7 +62212,7 @@
         <v>1210</v>
       </c>
       <c r="B1515" s="6" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="C1515" s="6" t="s">
         <v>17</v>
@@ -62232,7 +62231,7 @@
         <v>1504</v>
       </c>
       <c r="H1515" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1515" s="6" t="s">
         <v>1180</v>
@@ -62241,7 +62240,7 @@
         <v>6455</v>
       </c>
       <c r="K1515" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1516" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62249,7 +62248,7 @@
         <v>1648</v>
       </c>
       <c r="B1516" s="6" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="C1516" s="6" t="s">
         <v>17</v>
@@ -62268,7 +62267,7 @@
         <v>1504</v>
       </c>
       <c r="H1516" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1516" s="6" t="s">
         <v>1180</v>
@@ -62277,7 +62276,7 @@
         <v>6455</v>
       </c>
       <c r="K1516" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1517" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62285,7 +62284,7 @@
         <v>1268</v>
       </c>
       <c r="B1517" s="6" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="C1517" s="6" t="s">
         <v>17</v>
@@ -62304,7 +62303,7 @@
         <v>1504</v>
       </c>
       <c r="H1517" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1517" s="6" t="s">
         <v>1180</v>
@@ -62313,15 +62312,15 @@
         <v>6455</v>
       </c>
       <c r="K1517" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1518" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1518" s="32" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B1518" s="6" t="s">
         <v>2251</v>
-      </c>
-      <c r="B1518" s="6" t="s">
-        <v>2252</v>
       </c>
       <c r="C1518" s="6" t="s">
         <v>17</v>
@@ -62340,7 +62339,7 @@
         <v>1504</v>
       </c>
       <c r="H1518" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1518" s="6" t="s">
         <v>1180</v>
@@ -62349,7 +62348,7 @@
         <v>6455</v>
       </c>
       <c r="K1518" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1519" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62357,7 +62356,7 @@
         <v>1272</v>
       </c>
       <c r="B1519" s="6" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="C1519" s="6" t="s">
         <v>17</v>
@@ -62376,7 +62375,7 @@
         <v>1504</v>
       </c>
       <c r="H1519" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1519" s="6" t="s">
         <v>1180</v>
@@ -62385,15 +62384,15 @@
         <v>6455</v>
       </c>
       <c r="K1519" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1520" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1520" s="32" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B1520" s="6" t="s">
         <v>2254</v>
-      </c>
-      <c r="B1520" s="6" t="s">
-        <v>2255</v>
       </c>
       <c r="C1520" s="6" t="s">
         <v>17</v>
@@ -62412,7 +62411,7 @@
         <v>1504</v>
       </c>
       <c r="H1520" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1520" s="6" t="s">
         <v>1180</v>
@@ -62421,15 +62420,15 @@
         <v>6455</v>
       </c>
       <c r="K1520" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1521" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1521" s="32" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B1521" s="6" t="s">
         <v>2256</v>
-      </c>
-      <c r="B1521" s="6" t="s">
-        <v>2257</v>
       </c>
       <c r="C1521" s="6" t="s">
         <v>17</v>
@@ -62448,7 +62447,7 @@
         <v>1504</v>
       </c>
       <c r="H1521" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1521" s="6" t="s">
         <v>1180</v>
@@ -62457,7 +62456,7 @@
         <v>6456</v>
       </c>
       <c r="K1521" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1522" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62484,7 +62483,7 @@
         <v>1504</v>
       </c>
       <c r="H1522" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1522" s="6" t="s">
         <v>1180</v>
@@ -62493,7 +62492,7 @@
         <v>6456</v>
       </c>
       <c r="K1522" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1523" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62520,7 +62519,7 @@
         <v>1504</v>
       </c>
       <c r="H1523" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1523" s="6" t="s">
         <v>1180</v>
@@ -62529,7 +62528,7 @@
         <v>6456</v>
       </c>
       <c r="K1523" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1524" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62537,7 +62536,7 @@
         <v>1229</v>
       </c>
       <c r="B1524" s="6" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="C1524" s="6" t="s">
         <v>17</v>
@@ -62556,7 +62555,7 @@
         <v>1504</v>
       </c>
       <c r="H1524" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1524" s="6" t="s">
         <v>1180</v>
@@ -62565,7 +62564,7 @@
         <v>6456</v>
       </c>
       <c r="K1524" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1525" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62573,7 +62572,7 @@
         <v>1424</v>
       </c>
       <c r="B1525" s="6" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="C1525" s="6" t="s">
         <v>17</v>
@@ -62592,7 +62591,7 @@
         <v>1504</v>
       </c>
       <c r="H1525" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1525" s="6" t="s">
         <v>1180</v>
@@ -62601,7 +62600,7 @@
         <v>6456</v>
       </c>
       <c r="K1525" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1526" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62609,7 +62608,7 @@
         <v>1422</v>
       </c>
       <c r="B1526" s="6" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="C1526" s="6" t="s">
         <v>17</v>
@@ -62628,7 +62627,7 @@
         <v>1504</v>
       </c>
       <c r="H1526" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1526" s="6" t="s">
         <v>1180</v>
@@ -62637,7 +62636,7 @@
         <v>6456</v>
       </c>
       <c r="K1526" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1527" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62645,7 +62644,7 @@
         <v>1252</v>
       </c>
       <c r="B1527" s="6" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="C1527" s="6" t="s">
         <v>17</v>
@@ -62664,7 +62663,7 @@
         <v>1504</v>
       </c>
       <c r="H1527" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1527" s="6" t="s">
         <v>1180</v>
@@ -62673,15 +62672,15 @@
         <v>6456</v>
       </c>
       <c r="K1527" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1528" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1528" s="32" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B1528" s="6" t="s">
         <v>2261</v>
-      </c>
-      <c r="B1528" s="6" t="s">
-        <v>2262</v>
       </c>
       <c r="C1528" s="6" t="s">
         <v>17</v>
@@ -62700,7 +62699,7 @@
         <v>1504</v>
       </c>
       <c r="H1528" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1528" s="6" t="s">
         <v>1180</v>
@@ -62709,7 +62708,7 @@
         <v>6456</v>
       </c>
       <c r="K1528" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1529" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62717,7 +62716,7 @@
         <v>1254</v>
       </c>
       <c r="B1529" s="6" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="C1529" s="6" t="s">
         <v>17</v>
@@ -62736,7 +62735,7 @@
         <v>1504</v>
       </c>
       <c r="H1529" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1529" s="6" t="s">
         <v>1180</v>
@@ -62745,15 +62744,15 @@
         <v>6456</v>
       </c>
       <c r="K1529" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1530" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1530" s="32" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B1530" s="6" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="C1530" s="6" t="s">
         <v>17</v>
@@ -62772,7 +62771,7 @@
         <v>1504</v>
       </c>
       <c r="H1530" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1530" s="6" t="s">
         <v>1180</v>
@@ -62781,7 +62780,7 @@
         <v>6456</v>
       </c>
       <c r="K1530" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1531" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62789,7 +62788,7 @@
         <v>1210</v>
       </c>
       <c r="B1531" s="6" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="C1531" s="6" t="s">
         <v>17</v>
@@ -62808,7 +62807,7 @@
         <v>1504</v>
       </c>
       <c r="H1531" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1531" s="6" t="s">
         <v>1180</v>
@@ -62817,7 +62816,7 @@
         <v>6457</v>
       </c>
       <c r="K1531" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1532" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62825,7 +62824,7 @@
         <v>1243</v>
       </c>
       <c r="B1532" s="6" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="C1532" s="6" t="s">
         <v>17</v>
@@ -62844,7 +62843,7 @@
         <v>1504</v>
       </c>
       <c r="H1532" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1532" s="6" t="s">
         <v>1180</v>
@@ -62853,7 +62852,7 @@
         <v>6457</v>
       </c>
       <c r="K1532" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1533" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62861,7 +62860,7 @@
         <v>1197</v>
       </c>
       <c r="B1533" s="6" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="C1533" s="6" t="s">
         <v>17</v>
@@ -62880,7 +62879,7 @@
         <v>1504</v>
       </c>
       <c r="H1533" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1533" s="6" t="s">
         <v>1180</v>
@@ -62889,15 +62888,15 @@
         <v>6457</v>
       </c>
       <c r="K1533" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1534" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1534" s="32" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B1534" s="6" t="s">
         <v>2268</v>
-      </c>
-      <c r="B1534" s="6" t="s">
-        <v>2269</v>
       </c>
       <c r="C1534" s="6" t="s">
         <v>17</v>
@@ -62916,7 +62915,7 @@
         <v>1504</v>
       </c>
       <c r="H1534" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1534" s="6" t="s">
         <v>1180</v>
@@ -62925,7 +62924,7 @@
         <v>6457</v>
       </c>
       <c r="K1534" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1535" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62933,7 +62932,7 @@
         <v>1218</v>
       </c>
       <c r="B1535" s="6" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="C1535" s="6" t="s">
         <v>17</v>
@@ -62952,7 +62951,7 @@
         <v>1504</v>
       </c>
       <c r="H1535" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1535" s="6" t="s">
         <v>1180</v>
@@ -62961,15 +62960,15 @@
         <v>6457</v>
       </c>
       <c r="K1535" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1536" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1536" s="32" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1536" s="6" t="s">
         <v>2271</v>
-      </c>
-      <c r="B1536" s="6" t="s">
-        <v>2272</v>
       </c>
       <c r="C1536" s="6" t="s">
         <v>348</v>
@@ -62988,7 +62987,7 @@
         <v>1504</v>
       </c>
       <c r="H1536" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1536" s="6" t="s">
         <v>1180</v>
@@ -62997,15 +62996,15 @@
         <v>6457</v>
       </c>
       <c r="K1536" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1537" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1537" s="31" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B1537" s="6" t="s">
         <v>2273</v>
-      </c>
-      <c r="B1537" s="6" t="s">
-        <v>2274</v>
       </c>
       <c r="C1537" s="6" t="s">
         <v>17</v>
@@ -63024,7 +63023,7 @@
         <v>1505</v>
       </c>
       <c r="H1537" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1537" s="6" t="s">
         <v>1180</v>
@@ -63033,15 +63032,15 @@
         <v>6458</v>
       </c>
       <c r="K1537" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1538" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1538" s="32" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="B1538" s="17" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="C1538" s="6" t="s">
         <v>17</v>
@@ -63060,7 +63059,7 @@
         <v>1505</v>
       </c>
       <c r="H1538" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1538" s="6" t="s">
         <v>1180</v>
@@ -63069,7 +63068,7 @@
         <v>6458</v>
       </c>
       <c r="K1538" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1539" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63077,7 +63076,7 @@
         <v>1268</v>
       </c>
       <c r="B1539" s="6" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="C1539" s="6" t="s">
         <v>17</v>
@@ -63096,7 +63095,7 @@
         <v>1505</v>
       </c>
       <c r="H1539" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1539" s="6" t="s">
         <v>1180</v>
@@ -63105,7 +63104,7 @@
         <v>6458</v>
       </c>
       <c r="K1539" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1540" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63113,7 +63112,7 @@
         <v>1272</v>
       </c>
       <c r="B1540" s="6" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="C1540" s="6" t="s">
         <v>17</v>
@@ -63132,7 +63131,7 @@
         <v>1505</v>
       </c>
       <c r="H1540" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1540" s="6" t="s">
         <v>1180</v>
@@ -63141,7 +63140,7 @@
         <v>6458</v>
       </c>
       <c r="K1540" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1541" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63149,7 +63148,7 @@
         <v>1648</v>
       </c>
       <c r="B1541" s="6" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="C1541" s="6" t="s">
         <v>17</v>
@@ -63168,7 +63167,7 @@
         <v>1505</v>
       </c>
       <c r="H1541" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1541" s="6" t="s">
         <v>1180</v>
@@ -63177,13 +63176,13 @@
         <v>6458</v>
       </c>
       <c r="K1541" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1542" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1542" s="43"/>
       <c r="B1542" s="18" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="C1542" s="18" t="s">
         <v>17</v>
@@ -63202,7 +63201,7 @@
         <v>1505</v>
       </c>
       <c r="H1542" s="21" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1542" s="18" t="s">
         <v>1180</v>
@@ -63211,15 +63210,15 @@
         <v>6458</v>
       </c>
       <c r="K1542" s="21" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1543" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1543" s="32" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="B1543" s="6" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="C1543" s="6" t="s">
         <v>17</v>
@@ -63238,7 +63237,7 @@
         <v>1505</v>
       </c>
       <c r="H1543" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1543" s="6" t="s">
         <v>1180</v>
@@ -63247,15 +63246,15 @@
         <v>6458</v>
       </c>
       <c r="K1543" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1544" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1544" s="32" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="B1544" s="6" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="C1544" s="6" t="s">
         <v>17</v>
@@ -63274,7 +63273,7 @@
         <v>1505</v>
       </c>
       <c r="H1544" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1544" s="6" t="s">
         <v>1180</v>
@@ -63283,7 +63282,7 @@
         <v>6458</v>
       </c>
       <c r="K1544" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1545" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63310,7 +63309,7 @@
         <v>1505</v>
       </c>
       <c r="H1545" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1545" s="6" t="s">
         <v>1180</v>
@@ -63319,7 +63318,7 @@
         <v>6458</v>
       </c>
       <c r="K1545" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1546" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63327,7 +63326,7 @@
         <v>1218</v>
       </c>
       <c r="B1546" s="6" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="C1546" s="6" t="s">
         <v>17</v>
@@ -63346,7 +63345,7 @@
         <v>1505</v>
       </c>
       <c r="H1546" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1546" s="6" t="s">
         <v>1180</v>
@@ -63355,7 +63354,7 @@
         <v>6458</v>
       </c>
       <c r="K1546" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1547" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63382,7 +63381,7 @@
         <v>1505</v>
       </c>
       <c r="H1547" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1547" s="6" t="s">
         <v>1180</v>
@@ -63391,7 +63390,7 @@
         <v>6458</v>
       </c>
       <c r="K1547" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1548" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63399,7 +63398,7 @@
         <v>1197</v>
       </c>
       <c r="B1548" s="6" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="C1548" s="6" t="s">
         <v>17</v>
@@ -63418,7 +63417,7 @@
         <v>1505</v>
       </c>
       <c r="H1548" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1548" s="6" t="s">
         <v>1180</v>
@@ -63427,7 +63426,7 @@
         <v>6458</v>
       </c>
       <c r="K1548" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1549" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63435,7 +63434,7 @@
         <v>1144</v>
       </c>
       <c r="B1549" s="6" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="C1549" s="6" t="s">
         <v>17</v>
@@ -63454,7 +63453,7 @@
         <v>1505</v>
       </c>
       <c r="H1549" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1549" s="6" t="s">
         <v>1180</v>
@@ -63463,7 +63462,7 @@
         <v>6459</v>
       </c>
       <c r="K1549" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1550" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63471,7 +63470,7 @@
         <v>1223</v>
       </c>
       <c r="B1550" s="6" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="C1550" s="6" t="s">
         <v>17</v>
@@ -63490,7 +63489,7 @@
         <v>1505</v>
       </c>
       <c r="H1550" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1550" s="6" t="s">
         <v>1180</v>
@@ -63499,7 +63498,7 @@
         <v>6459</v>
       </c>
       <c r="K1550" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1551" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63507,7 +63506,7 @@
         <v>1422</v>
       </c>
       <c r="B1551" s="6" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="C1551" s="6" t="s">
         <v>17</v>
@@ -63526,7 +63525,7 @@
         <v>1505</v>
       </c>
       <c r="H1551" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1551" s="6" t="s">
         <v>1180</v>
@@ -63535,7 +63534,7 @@
         <v>6459</v>
       </c>
       <c r="K1551" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1552" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63562,7 +63561,7 @@
         <v>1505</v>
       </c>
       <c r="H1552" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1552" s="6" t="s">
         <v>1180</v>
@@ -63571,7 +63570,7 @@
         <v>6459</v>
       </c>
       <c r="K1552" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1553" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63579,7 +63578,7 @@
         <v>1264</v>
       </c>
       <c r="B1553" s="6" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="C1553" s="6" t="s">
         <v>17</v>
@@ -63598,7 +63597,7 @@
         <v>1505</v>
       </c>
       <c r="H1553" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1553" s="6" t="s">
         <v>1180</v>
@@ -63607,15 +63606,15 @@
         <v>6459</v>
       </c>
       <c r="K1553" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1554" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1554" s="32" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B1554" s="6" t="s">
         <v>2284</v>
-      </c>
-      <c r="B1554" s="6" t="s">
-        <v>2285</v>
       </c>
       <c r="C1554" s="6" t="s">
         <v>348</v>
@@ -63634,7 +63633,7 @@
         <v>1505</v>
       </c>
       <c r="H1554" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1554" s="6" t="s">
         <v>1180</v>
@@ -63643,7 +63642,7 @@
         <v>6459</v>
       </c>
       <c r="K1554" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1555" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63670,7 +63669,7 @@
         <v>1505</v>
       </c>
       <c r="H1555" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1555" s="6" t="s">
         <v>1180</v>
@@ -63679,15 +63678,15 @@
         <v>6459</v>
       </c>
       <c r="K1555" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1556" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1556" s="32" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B1556" s="6" t="s">
         <v>2286</v>
-      </c>
-      <c r="B1556" s="6" t="s">
-        <v>2287</v>
       </c>
       <c r="C1556" s="6" t="s">
         <v>348</v>
@@ -63706,7 +63705,7 @@
         <v>1505</v>
       </c>
       <c r="H1556" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1556" s="6" t="s">
         <v>1180</v>
@@ -63715,7 +63714,7 @@
         <v>6459</v>
       </c>
       <c r="K1556" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1557" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63742,7 +63741,7 @@
         <v>1505</v>
       </c>
       <c r="H1557" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1557" s="6" t="s">
         <v>1180</v>
@@ -63751,7 +63750,7 @@
         <v>6459</v>
       </c>
       <c r="K1557" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1558" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63759,7 +63758,7 @@
         <v>344</v>
       </c>
       <c r="B1558" s="6" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="C1558" s="6" t="s">
         <v>17</v>
@@ -63778,7 +63777,7 @@
         <v>1505</v>
       </c>
       <c r="H1558" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1558" s="6" t="s">
         <v>1180</v>
@@ -63787,15 +63786,15 @@
         <v>6459</v>
       </c>
       <c r="K1558" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1559" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1559" s="32" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1559" s="6" t="s">
         <v>2289</v>
-      </c>
-      <c r="B1559" s="6" t="s">
-        <v>2290</v>
       </c>
       <c r="C1559" s="6" t="s">
         <v>348</v>
@@ -63814,7 +63813,7 @@
         <v>1505</v>
       </c>
       <c r="H1559" s="12" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1559" s="6" t="s">
         <v>1180</v>
@@ -63823,7 +63822,7 @@
         <v>6459</v>
       </c>
       <c r="K1559" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1560" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63831,7 +63830,7 @@
         <v>224</v>
       </c>
       <c r="B1560" s="6" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="C1560" s="6" t="s">
         <v>17</v>
@@ -63850,7 +63849,7 @@
         <v>1567</v>
       </c>
       <c r="H1560" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="I1560" s="6" t="s">
         <v>799</v>
@@ -63859,7 +63858,7 @@
         <v>6461</v>
       </c>
       <c r="K1560" s="12" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1561" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63867,7 +63866,7 @@
         <v>225</v>
       </c>
       <c r="B1561" s="6" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C1561" s="6" t="s">
         <v>17</v>
@@ -63886,7 +63885,7 @@
         <v>1567</v>
       </c>
       <c r="H1561" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="I1561" s="6" t="s">
         <v>799</v>
@@ -63895,7 +63894,7 @@
         <v>6461</v>
       </c>
       <c r="K1561" s="12" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1562" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63903,7 +63902,7 @@
         <v>723</v>
       </c>
       <c r="B1562" s="6" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C1562" s="6" t="s">
         <v>17</v>
@@ -63922,7 +63921,7 @@
         <v>2524</v>
       </c>
       <c r="H1562" s="12" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="I1562" s="6" t="s">
         <v>528</v>
@@ -63931,7 +63930,7 @@
         <v>6462</v>
       </c>
       <c r="K1562" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1563" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63958,7 +63957,7 @@
         <v>4665</v>
       </c>
       <c r="H1563" s="12" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1563" s="6" t="s">
         <v>1286</v>
@@ -63967,7 +63966,7 @@
         <v>6463</v>
       </c>
       <c r="K1563" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1564" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63994,7 +63993,7 @@
         <v>4665</v>
       </c>
       <c r="H1564" s="12" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1564" s="6" t="s">
         <v>1286</v>
@@ -64003,15 +64002,15 @@
         <v>6463</v>
       </c>
       <c r="K1564" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1565" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1565" s="32" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1565" s="6" t="s">
         <v>2297</v>
-      </c>
-      <c r="B1565" s="6" t="s">
-        <v>2298</v>
       </c>
       <c r="C1565" s="6" t="s">
         <v>17</v>
@@ -64030,7 +64029,7 @@
         <v>4665</v>
       </c>
       <c r="H1565" s="12" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1565" s="6" t="s">
         <v>1286</v>
@@ -64039,15 +64038,15 @@
         <v>6463</v>
       </c>
       <c r="K1565" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1566" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1566" s="32" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1566" s="6" t="s">
         <v>2299</v>
-      </c>
-      <c r="B1566" s="6" t="s">
-        <v>2300</v>
       </c>
       <c r="C1566" s="6" t="s">
         <v>17</v>
@@ -64066,7 +64065,7 @@
         <v>4665</v>
       </c>
       <c r="H1566" s="12" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1566" s="6" t="s">
         <v>1286</v>
@@ -64075,15 +64074,15 @@
         <v>6463</v>
       </c>
       <c r="K1566" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1567" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1567" s="31" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B1567" s="6" t="s">
         <v>2301</v>
-      </c>
-      <c r="B1567" s="6" t="s">
-        <v>2302</v>
       </c>
       <c r="C1567" s="6" t="s">
         <v>17</v>
@@ -64102,7 +64101,7 @@
         <v>4665</v>
       </c>
       <c r="H1567" s="12" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1567" s="6" t="s">
         <v>1286</v>
@@ -64111,15 +64110,15 @@
         <v>6463</v>
       </c>
       <c r="K1567" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1568" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1568" s="32" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B1568" s="6" t="s">
         <v>2303</v>
-      </c>
-      <c r="B1568" s="6" t="s">
-        <v>2304</v>
       </c>
       <c r="C1568" s="6" t="s">
         <v>17</v>
@@ -64138,7 +64137,7 @@
         <v>4665</v>
       </c>
       <c r="H1568" s="12" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1568" s="6" t="s">
         <v>1286</v>
@@ -64147,15 +64146,15 @@
         <v>6463</v>
       </c>
       <c r="K1568" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1569" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1569" s="34" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B1569" s="6" t="s">
         <v>2305</v>
-      </c>
-      <c r="B1569" s="6" t="s">
-        <v>2306</v>
       </c>
       <c r="C1569" s="6" t="s">
         <v>17</v>
@@ -64174,7 +64173,7 @@
         <v>4665</v>
       </c>
       <c r="H1569" s="12" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1569" s="6" t="s">
         <v>1286</v>
@@ -64183,15 +64182,15 @@
         <v>6463</v>
       </c>
       <c r="K1569" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1570" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1570" s="31" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B1570" s="6" t="s">
         <v>2307</v>
-      </c>
-      <c r="B1570" s="6" t="s">
-        <v>2308</v>
       </c>
       <c r="C1570" s="6" t="s">
         <v>17</v>
@@ -64219,13 +64218,13 @@
         <v>6463</v>
       </c>
       <c r="K1570" s="12" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1571" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1571" s="44"/>
       <c r="B1571" s="6" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="C1571" s="6" t="s">
         <v>348</v>
@@ -64244,22 +64243,22 @@
         <v>38</v>
       </c>
       <c r="H1571" s="12" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1571" s="6" t="s">
         <v>2310</v>
-      </c>
-      <c r="I1571" s="6" t="s">
-        <v>2311</v>
       </c>
       <c r="J1571" s="6">
         <v>6454</v>
       </c>
       <c r="K1571" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1572" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1572" s="44"/>
       <c r="B1572" s="6" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="C1572" s="6" t="s">
         <v>348</v>
@@ -64278,22 +64277,22 @@
         <v>38</v>
       </c>
       <c r="H1572" s="12" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1572" s="6" t="s">
         <v>2310</v>
-      </c>
-      <c r="I1572" s="6" t="s">
-        <v>2311</v>
       </c>
       <c r="J1572" s="6">
         <v>6454</v>
       </c>
       <c r="K1572" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1573" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1573" s="44"/>
       <c r="B1573" s="6" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="C1573" s="6" t="s">
         <v>348</v>
@@ -64312,22 +64311,22 @@
         <v>38</v>
       </c>
       <c r="H1573" s="12" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1573" s="6" t="s">
         <v>2310</v>
-      </c>
-      <c r="I1573" s="6" t="s">
-        <v>2311</v>
       </c>
       <c r="J1573" s="6">
         <v>6454</v>
       </c>
       <c r="K1573" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1574" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1574" s="44"/>
       <c r="B1574" s="6" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="C1574" s="6" t="s">
         <v>348</v>
@@ -64346,16 +64345,16 @@
         <v>38</v>
       </c>
       <c r="H1574" s="12" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1574" s="6" t="s">
         <v>2310</v>
-      </c>
-      <c r="I1574" s="6" t="s">
-        <v>2311</v>
       </c>
       <c r="J1574" s="6">
         <v>6454</v>
       </c>
       <c r="K1574" s="12" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1575" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB270BC9-40DD-4753-B416-B3B16DB8C069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2D1853-3B7C-43A0-A731-CD0296AF7D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8117" uniqueCount="2314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8117" uniqueCount="2309">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -5163,9 +5163,6 @@
     <t>لوح 1.5 مم SST لميع 1 × 2.5 م (430)</t>
   </si>
   <si>
-    <t>19-4-2029</t>
-  </si>
-  <si>
     <t>11301022</t>
   </si>
   <si>
@@ -5178,31 +5175,19 @@
     <t>لوح SST 1.5 مط 1×2</t>
   </si>
   <si>
-    <t>19-4-2027</t>
-  </si>
-  <si>
     <t>11301080</t>
   </si>
   <si>
     <t>لوح 1.8 مم SST مصنفر 125 ×200</t>
   </si>
   <si>
-    <t>19-4-2028</t>
-  </si>
-  <si>
     <t>لوح 1.8 مم SST مصنفر 125 ×250</t>
   </si>
   <si>
-    <t>19-4-2030</t>
-  </si>
-  <si>
     <t>11301081</t>
   </si>
   <si>
     <t>لوح 1.5 مم SST مصنفر مغلف 1.25 × 2 م</t>
-  </si>
-  <si>
-    <t>19-4-2031</t>
   </si>
   <si>
     <t>هيتر قلايه زيت 9ك</t>
@@ -46715,7 +46700,7 @@
         <v>59846</v>
       </c>
       <c r="H1083" s="27" t="s">
-        <v>1708</v>
+        <v>1637</v>
       </c>
       <c r="I1083" s="19" t="s">
         <v>602</v>
@@ -46729,10 +46714,10 @@
     </row>
     <row r="1084" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1084" s="35" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1084" s="18" t="s">
         <v>1709</v>
-      </c>
-      <c r="B1084" s="18" t="s">
-        <v>1710</v>
       </c>
       <c r="C1084" s="20" t="s">
         <v>40</v>
@@ -46768,7 +46753,7 @@
         <v>1600</v>
       </c>
       <c r="B1085" s="18" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C1085" s="19" t="s">
         <v>40</v>
@@ -46804,7 +46789,7 @@
         <v>201</v>
       </c>
       <c r="B1086" s="18" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C1086" s="19" t="s">
         <v>40</v>
@@ -46823,7 +46808,7 @@
         <v>59846</v>
       </c>
       <c r="H1086" s="27" t="s">
-        <v>1713</v>
+        <v>1637</v>
       </c>
       <c r="I1086" s="19" t="s">
         <v>602</v>
@@ -46837,10 +46822,10 @@
     </row>
     <row r="1087" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1087" s="35" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="B1087" s="18" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="C1087" s="19" t="s">
         <v>40</v>
@@ -46859,7 +46844,7 @@
         <v>59846</v>
       </c>
       <c r="H1087" s="27" t="s">
-        <v>1716</v>
+        <v>1637</v>
       </c>
       <c r="I1087" s="19" t="s">
         <v>602</v>
@@ -46876,7 +46861,7 @@
         <v>979</v>
       </c>
       <c r="B1088" s="18" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="C1088" s="19" t="s">
         <v>40</v>
@@ -46895,7 +46880,7 @@
         <v>59846</v>
       </c>
       <c r="H1088" s="27" t="s">
-        <v>1718</v>
+        <v>1637</v>
       </c>
       <c r="I1088" s="19" t="s">
         <v>602</v>
@@ -46909,10 +46894,10 @@
     </row>
     <row r="1089" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1089" s="35" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="B1089" s="18" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
       <c r="C1089" s="19" t="s">
         <v>40</v>
@@ -46931,7 +46916,7 @@
         <v>59846</v>
       </c>
       <c r="H1089" s="27" t="s">
-        <v>1721</v>
+        <v>1637</v>
       </c>
       <c r="I1089" s="19" t="s">
         <v>602</v>
@@ -46948,7 +46933,7 @@
         <v>427</v>
       </c>
       <c r="B1090" s="6" t="s">
-        <v>1722</v>
+        <v>1717</v>
       </c>
       <c r="C1090" s="6" t="s">
         <v>17</v>
@@ -46981,10 +46966,10 @@
     </row>
     <row r="1091" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1091" s="31" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
       <c r="B1091" s="17" t="s">
-        <v>1724</v>
+        <v>1719</v>
       </c>
       <c r="C1091" s="6" t="s">
         <v>17</v>
@@ -47020,7 +47005,7 @@
         <v>581</v>
       </c>
       <c r="B1092" s="6" t="s">
-        <v>1725</v>
+        <v>1720</v>
       </c>
       <c r="C1092" s="6" t="s">
         <v>17</v>
@@ -47053,10 +47038,10 @@
     </row>
     <row r="1093" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1093" s="31" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
       <c r="B1093" s="6" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
       <c r="C1093" s="6" t="s">
         <v>17</v>
@@ -47089,10 +47074,10 @@
     </row>
     <row r="1094" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1094" s="31" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="B1094" s="6" t="s">
-        <v>1729</v>
+        <v>1724</v>
       </c>
       <c r="C1094" s="6" t="s">
         <v>17</v>
@@ -47125,10 +47110,10 @@
     </row>
     <row r="1095" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1095" s="31" t="s">
-        <v>1730</v>
+        <v>1725</v>
       </c>
       <c r="B1095" s="6" t="s">
-        <v>1731</v>
+        <v>1726</v>
       </c>
       <c r="C1095" s="6" t="s">
         <v>17</v>
@@ -47162,7 +47147,7 @@
     <row r="1096" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1096" s="41"/>
       <c r="B1096" s="6" t="s">
-        <v>1732</v>
+        <v>1727</v>
       </c>
       <c r="C1096" s="6" t="s">
         <v>17</v>
@@ -47195,10 +47180,10 @@
     </row>
     <row r="1097" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1097" s="31" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="B1097" s="6" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="C1097" s="6" t="s">
         <v>17</v>
@@ -47231,10 +47216,10 @@
     </row>
     <row r="1098" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1098" s="31" t="s">
-        <v>1735</v>
+        <v>1730</v>
       </c>
       <c r="B1098" s="6" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="C1098" s="6" t="s">
         <v>17</v>
@@ -47303,10 +47288,10 @@
     </row>
     <row r="1100" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1100" s="31" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="B1100" s="6" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="C1100" s="6" t="s">
         <v>17</v>
@@ -47339,10 +47324,10 @@
     </row>
     <row r="1101" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1101" s="32" t="s">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="B1101" s="6" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="C1101" s="6" t="s">
         <v>17</v>
@@ -47375,10 +47360,10 @@
     </row>
     <row r="1102" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1102" s="32" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
       <c r="B1102" s="6" t="s">
-        <v>1742</v>
+        <v>1737</v>
       </c>
       <c r="C1102" s="6" t="s">
         <v>17</v>
@@ -47411,10 +47396,10 @@
     </row>
     <row r="1103" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1103" s="31" t="s">
-        <v>1743</v>
+        <v>1738</v>
       </c>
       <c r="B1103" s="6" t="s">
-        <v>1744</v>
+        <v>1739</v>
       </c>
       <c r="C1103" s="6" t="s">
         <v>17</v>
@@ -47447,10 +47432,10 @@
     </row>
     <row r="1104" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1104" s="31" t="s">
-        <v>1745</v>
+        <v>1740</v>
       </c>
       <c r="B1104" s="6" t="s">
-        <v>1746</v>
+        <v>1741</v>
       </c>
       <c r="C1104" s="6" t="s">
         <v>17</v>
@@ -47483,10 +47468,10 @@
     </row>
     <row r="1105" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1105" s="31" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="B1105" s="6" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="C1105" s="6" t="s">
         <v>17</v>
@@ -47522,7 +47507,7 @@
         <v>217</v>
       </c>
       <c r="B1106" s="6" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="C1106" s="6" t="s">
         <v>17</v>
@@ -47541,7 +47526,7 @@
         <v>93</v>
       </c>
       <c r="H1106" s="12" t="s">
-        <v>1750</v>
+        <v>1745</v>
       </c>
       <c r="I1106" s="6" t="s">
         <v>346</v>
@@ -47577,7 +47562,7 @@
         <v>93</v>
       </c>
       <c r="H1107" s="12" t="s">
-        <v>1750</v>
+        <v>1745</v>
       </c>
       <c r="I1107" s="6" t="s">
         <v>346</v>
@@ -47594,7 +47579,7 @@
         <v>443</v>
       </c>
       <c r="B1108" s="6" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="C1108" s="6" t="s">
         <v>17</v>
@@ -47613,7 +47598,7 @@
         <v>93</v>
       </c>
       <c r="H1108" s="12" t="s">
-        <v>1750</v>
+        <v>1745</v>
       </c>
       <c r="I1108" s="6" t="s">
         <v>346</v>
@@ -47630,7 +47615,7 @@
         <v>340</v>
       </c>
       <c r="B1109" s="6" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="C1109" s="6" t="s">
         <v>17</v>
@@ -47649,7 +47634,7 @@
         <v>93</v>
       </c>
       <c r="H1109" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1109" s="6" t="s">
         <v>346</v>
@@ -47663,10 +47648,10 @@
     </row>
     <row r="1110" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1110" s="32" t="s">
-        <v>1754</v>
+        <v>1749</v>
       </c>
       <c r="B1110" s="6" t="s">
-        <v>1755</v>
+        <v>1750</v>
       </c>
       <c r="C1110" s="6" t="s">
         <v>17</v>
@@ -47685,7 +47670,7 @@
         <v>93</v>
       </c>
       <c r="H1110" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1110" s="6" t="s">
         <v>346</v>
@@ -47699,10 +47684,10 @@
     </row>
     <row r="1111" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1111" s="31" t="s">
-        <v>1756</v>
+        <v>1751</v>
       </c>
       <c r="B1111" s="6" t="s">
-        <v>1757</v>
+        <v>1752</v>
       </c>
       <c r="C1111" s="6" t="s">
         <v>17</v>
@@ -47721,7 +47706,7 @@
         <v>713</v>
       </c>
       <c r="H1111" s="12" t="s">
-        <v>1758</v>
+        <v>1753</v>
       </c>
       <c r="I1111" s="6" t="s">
         <v>37</v>
@@ -47735,10 +47720,10 @@
     </row>
     <row r="1112" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1112" s="31" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
       <c r="B1112" s="6" t="s">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="C1112" s="6" t="s">
         <v>17</v>
@@ -47757,7 +47742,7 @@
         <v>713</v>
       </c>
       <c r="H1112" s="12" t="s">
-        <v>1758</v>
+        <v>1753</v>
       </c>
       <c r="I1112" s="6" t="s">
         <v>37</v>
@@ -47771,10 +47756,10 @@
     </row>
     <row r="1113" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1113" s="31" t="s">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="B1113" s="6" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
       <c r="C1113" s="6" t="s">
         <v>17</v>
@@ -47793,7 +47778,7 @@
         <v>6350</v>
       </c>
       <c r="H1113" s="12" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="I1113" s="6" t="s">
         <v>445</v>
@@ -47810,7 +47795,7 @@
         <v>286</v>
       </c>
       <c r="B1114" s="6" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="C1114" s="6" t="s">
         <v>17</v>
@@ -47829,16 +47814,16 @@
         <v>26</v>
       </c>
       <c r="H1114" s="12" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="I1114" s="6" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="J1114" s="6">
         <v>6351</v>
       </c>
       <c r="K1114" s="12" t="s">
-        <v>1766</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1115" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -47846,7 +47831,7 @@
         <v>286</v>
       </c>
       <c r="B1115" s="6" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="C1115" s="6" t="s">
         <v>17</v>
@@ -47874,15 +47859,15 @@
         <v>6358</v>
       </c>
       <c r="K1115" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1116" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1116" s="31" t="s">
-        <v>1768</v>
+        <v>1763</v>
       </c>
       <c r="B1116" s="6" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="C1116" s="6" t="s">
         <v>17</v>
@@ -47910,15 +47895,15 @@
         <v>6359</v>
       </c>
       <c r="K1116" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1117" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1117" s="31" t="s">
-        <v>1770</v>
+        <v>1765</v>
       </c>
       <c r="B1117" s="6" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="C1117" s="6" t="s">
         <v>17</v>
@@ -47946,15 +47931,15 @@
         <v>6359</v>
       </c>
       <c r="K1117" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1118" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1118" s="32" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
       <c r="B1118" s="6" t="s">
-        <v>1773</v>
+        <v>1768</v>
       </c>
       <c r="C1118" s="6" t="s">
         <v>17</v>
@@ -47973,7 +47958,7 @@
         <v>142</v>
       </c>
       <c r="H1118" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1118" s="6" t="s">
         <v>36</v>
@@ -47982,7 +47967,7 @@
         <v>6360</v>
       </c>
       <c r="K1118" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1119" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -47990,7 +47975,7 @@
         <v>321</v>
       </c>
       <c r="B1119" s="6" t="s">
-        <v>1774</v>
+        <v>1769</v>
       </c>
       <c r="C1119" s="6" t="s">
         <v>17</v>
@@ -48009,7 +47994,7 @@
         <v>142</v>
       </c>
       <c r="H1119" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1119" s="6" t="s">
         <v>36</v>
@@ -48018,15 +48003,15 @@
         <v>6360</v>
       </c>
       <c r="K1119" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1120" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1120" s="32" t="s">
-        <v>1775</v>
+        <v>1770</v>
       </c>
       <c r="B1120" s="6" t="s">
-        <v>1776</v>
+        <v>1771</v>
       </c>
       <c r="C1120" s="6" t="s">
         <v>17</v>
@@ -48045,7 +48030,7 @@
         <v>143</v>
       </c>
       <c r="H1120" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1120" s="6" t="s">
         <v>36</v>
@@ -48054,7 +48039,7 @@
         <v>6361</v>
       </c>
       <c r="K1120" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1121" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48062,7 +48047,7 @@
         <v>303</v>
       </c>
       <c r="B1121" s="6" t="s">
-        <v>1777</v>
+        <v>1772</v>
       </c>
       <c r="C1121" s="6" t="s">
         <v>17</v>
@@ -48081,7 +48066,7 @@
         <v>94</v>
       </c>
       <c r="H1121" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1121" s="6" t="s">
         <v>346</v>
@@ -48090,13 +48075,13 @@
         <v>6362</v>
       </c>
       <c r="K1121" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1122" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1122" s="31"/>
       <c r="B1122" s="6" t="s">
-        <v>1778</v>
+        <v>1773</v>
       </c>
       <c r="C1122" s="6" t="s">
         <v>17</v>
@@ -48115,7 +48100,7 @@
         <v>94</v>
       </c>
       <c r="H1122" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1122" s="6" t="s">
         <v>346</v>
@@ -48124,7 +48109,7 @@
         <v>6362</v>
       </c>
       <c r="K1122" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1123" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48132,7 +48117,7 @@
         <v>333</v>
       </c>
       <c r="B1123" s="6" t="s">
-        <v>1779</v>
+        <v>1774</v>
       </c>
       <c r="C1123" s="6" t="s">
         <v>17</v>
@@ -48151,7 +48136,7 @@
         <v>94</v>
       </c>
       <c r="H1123" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1123" s="6" t="s">
         <v>346</v>
@@ -48160,7 +48145,7 @@
         <v>6362</v>
       </c>
       <c r="K1123" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1124" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48168,7 +48153,7 @@
         <v>269</v>
       </c>
       <c r="B1124" s="6" t="s">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="C1124" s="6" t="s">
         <v>17</v>
@@ -48187,7 +48172,7 @@
         <v>94</v>
       </c>
       <c r="H1124" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1124" s="6" t="s">
         <v>346</v>
@@ -48196,7 +48181,7 @@
         <v>6362</v>
       </c>
       <c r="K1124" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1125" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48223,7 +48208,7 @@
         <v>94</v>
       </c>
       <c r="H1125" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1125" s="6" t="s">
         <v>346</v>
@@ -48232,7 +48217,7 @@
         <v>6362</v>
       </c>
       <c r="K1125" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1126" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48240,7 +48225,7 @@
         <v>323</v>
       </c>
       <c r="B1126" s="6" t="s">
-        <v>1781</v>
+        <v>1776</v>
       </c>
       <c r="C1126" s="6" t="s">
         <v>17</v>
@@ -48259,7 +48244,7 @@
         <v>14057</v>
       </c>
       <c r="H1126" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1126" s="6" t="s">
         <v>116</v>
@@ -48268,7 +48253,7 @@
         <v>6363</v>
       </c>
       <c r="K1126" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1127" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48295,7 +48280,7 @@
         <v>14057</v>
       </c>
       <c r="H1127" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1127" s="6" t="s">
         <v>116</v>
@@ -48304,7 +48289,7 @@
         <v>6363</v>
       </c>
       <c r="K1127" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1128" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48331,7 +48316,7 @@
         <v>14057</v>
       </c>
       <c r="H1128" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1128" s="6" t="s">
         <v>116</v>
@@ -48340,7 +48325,7 @@
         <v>6363</v>
       </c>
       <c r="K1128" s="12" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1129" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48348,7 +48333,7 @@
         <v>289</v>
       </c>
       <c r="B1129" s="6" t="s">
-        <v>1782</v>
+        <v>1777</v>
       </c>
       <c r="C1129" s="6" t="s">
         <v>17</v>
@@ -48367,7 +48352,7 @@
         <v>2464</v>
       </c>
       <c r="H1129" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1129" s="6" t="s">
         <v>799</v>
@@ -48376,7 +48361,7 @@
         <v>6364</v>
       </c>
       <c r="K1129" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1130" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48384,7 +48369,7 @@
         <v>560</v>
       </c>
       <c r="B1130" s="6" t="s">
-        <v>1784</v>
+        <v>1779</v>
       </c>
       <c r="C1130" s="6" t="s">
         <v>17</v>
@@ -48403,7 +48388,7 @@
         <v>2464</v>
       </c>
       <c r="H1130" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1130" s="6" t="s">
         <v>799</v>
@@ -48412,7 +48397,7 @@
         <v>6364</v>
       </c>
       <c r="K1130" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1131" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48420,7 +48405,7 @@
         <v>562</v>
       </c>
       <c r="B1131" s="6" t="s">
-        <v>1785</v>
+        <v>1780</v>
       </c>
       <c r="C1131" s="6" t="s">
         <v>17</v>
@@ -48439,7 +48424,7 @@
         <v>2464</v>
       </c>
       <c r="H1131" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1131" s="6" t="s">
         <v>799</v>
@@ -48448,15 +48433,15 @@
         <v>6364</v>
       </c>
       <c r="K1131" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1132" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1132" s="32" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="B1132" s="6" t="s">
-        <v>1787</v>
+        <v>1782</v>
       </c>
       <c r="C1132" s="6" t="s">
         <v>17</v>
@@ -48475,7 +48460,7 @@
         <v>2464</v>
       </c>
       <c r="H1132" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1132" s="6" t="s">
         <v>799</v>
@@ -48484,7 +48469,7 @@
         <v>6364</v>
       </c>
       <c r="K1132" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1133" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48492,7 +48477,7 @@
         <v>1437</v>
       </c>
       <c r="B1133" s="6" t="s">
-        <v>1788</v>
+        <v>1783</v>
       </c>
       <c r="C1133" s="6" t="s">
         <v>17</v>
@@ -48511,7 +48496,7 @@
         <v>2464</v>
       </c>
       <c r="H1133" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1133" s="6" t="s">
         <v>799</v>
@@ -48520,7 +48505,7 @@
         <v>6364</v>
       </c>
       <c r="K1133" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1134" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48528,7 +48513,7 @@
         <v>721</v>
       </c>
       <c r="B1134" s="6" t="s">
-        <v>1789</v>
+        <v>1784</v>
       </c>
       <c r="C1134" s="6" t="s">
         <v>17</v>
@@ -48547,7 +48532,7 @@
         <v>2464</v>
       </c>
       <c r="H1134" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1134" s="6" t="s">
         <v>799</v>
@@ -48556,15 +48541,15 @@
         <v>6364</v>
       </c>
       <c r="K1134" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1135" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1135" s="34" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
       <c r="B1135" s="6" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="C1135" s="6" t="s">
         <v>17</v>
@@ -48583,7 +48568,7 @@
         <v>2464</v>
       </c>
       <c r="H1135" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1135" s="6" t="s">
         <v>799</v>
@@ -48592,7 +48577,7 @@
         <v>6364</v>
       </c>
       <c r="K1135" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1136" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48619,7 +48604,7 @@
         <v>2464</v>
       </c>
       <c r="H1136" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1136" s="6" t="s">
         <v>799</v>
@@ -48628,7 +48613,7 @@
         <v>6364</v>
       </c>
       <c r="K1136" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1137" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48655,7 +48640,7 @@
         <v>2464</v>
       </c>
       <c r="H1137" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1137" s="6" t="s">
         <v>799</v>
@@ -48664,7 +48649,7 @@
         <v>6364</v>
       </c>
       <c r="K1137" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1138" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48691,7 +48676,7 @@
         <v>2464</v>
       </c>
       <c r="H1138" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1138" s="6" t="s">
         <v>799</v>
@@ -48700,7 +48685,7 @@
         <v>6364</v>
       </c>
       <c r="K1138" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1139" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48708,7 +48693,7 @@
         <v>287</v>
       </c>
       <c r="B1139" s="6" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="C1139" s="6" t="s">
         <v>17</v>
@@ -48727,7 +48712,7 @@
         <v>2464</v>
       </c>
       <c r="H1139" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1139" s="6" t="s">
         <v>799</v>
@@ -48736,7 +48721,7 @@
         <v>6364</v>
       </c>
       <c r="K1139" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1140" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48763,7 +48748,7 @@
         <v>2464</v>
       </c>
       <c r="H1140" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1140" s="6" t="s">
         <v>799</v>
@@ -48772,7 +48757,7 @@
         <v>6364</v>
       </c>
       <c r="K1140" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1141" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48799,7 +48784,7 @@
         <v>2464</v>
       </c>
       <c r="H1141" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1141" s="6" t="s">
         <v>799</v>
@@ -48808,7 +48793,7 @@
         <v>6365</v>
       </c>
       <c r="K1141" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1142" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48816,7 +48801,7 @@
         <v>1278</v>
       </c>
       <c r="B1142" s="6" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="C1142" s="6" t="s">
         <v>17</v>
@@ -48835,7 +48820,7 @@
         <v>2464</v>
       </c>
       <c r="H1142" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1142" s="6" t="s">
         <v>799</v>
@@ -48844,7 +48829,7 @@
         <v>6365</v>
       </c>
       <c r="K1142" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1143" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48852,7 +48837,7 @@
         <v>301</v>
       </c>
       <c r="B1143" s="6" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
       <c r="C1143" s="6" t="s">
         <v>17</v>
@@ -48871,7 +48856,7 @@
         <v>2464</v>
       </c>
       <c r="H1143" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1143" s="6" t="s">
         <v>799</v>
@@ -48880,7 +48865,7 @@
         <v>6365</v>
       </c>
       <c r="K1143" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1144" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48907,7 +48892,7 @@
         <v>2464</v>
       </c>
       <c r="H1144" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="I1144" s="6" t="s">
         <v>799</v>
@@ -48916,7 +48901,7 @@
         <v>6365</v>
       </c>
       <c r="K1144" s="12" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1145" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -48924,7 +48909,7 @@
         <v>723</v>
       </c>
       <c r="B1145" s="6" t="s">
-        <v>1795</v>
+        <v>1790</v>
       </c>
       <c r="C1145" s="6" t="s">
         <v>17</v>
@@ -48943,7 +48928,7 @@
         <v>2468</v>
       </c>
       <c r="H1145" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1145" s="6" t="s">
         <v>799</v>
@@ -48960,7 +48945,7 @@
         <v>286</v>
       </c>
       <c r="B1146" s="6" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="C1146" s="6" t="s">
         <v>17</v>
@@ -48979,7 +48964,7 @@
         <v>2468</v>
       </c>
       <c r="H1146" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1146" s="6" t="s">
         <v>799</v>
@@ -49015,7 +49000,7 @@
         <v>2468</v>
       </c>
       <c r="H1147" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1147" s="6" t="s">
         <v>799</v>
@@ -49029,10 +49014,10 @@
     </row>
     <row r="1148" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1148" s="31" t="s">
-        <v>1797</v>
+        <v>1792</v>
       </c>
       <c r="B1148" s="6" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="C1148" s="6" t="s">
         <v>17</v>
@@ -49051,7 +49036,7 @@
         <v>2468</v>
       </c>
       <c r="H1148" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1148" s="6" t="s">
         <v>799</v>
@@ -49065,10 +49050,10 @@
     </row>
     <row r="1149" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1149" s="32" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="B1149" s="6" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="C1149" s="6" t="s">
         <v>17</v>
@@ -49087,7 +49072,7 @@
         <v>2468</v>
       </c>
       <c r="H1149" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1149" s="6" t="s">
         <v>799</v>
@@ -49123,7 +49108,7 @@
         <v>2468</v>
       </c>
       <c r="H1150" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1150" s="6" t="s">
         <v>799</v>
@@ -49159,7 +49144,7 @@
         <v>2468</v>
       </c>
       <c r="H1151" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1151" s="6" t="s">
         <v>799</v>
@@ -49176,7 +49161,7 @@
         <v>907</v>
       </c>
       <c r="B1152" s="6" t="s">
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="C1152" s="6" t="s">
         <v>17</v>
@@ -49195,7 +49180,7 @@
         <v>2468</v>
       </c>
       <c r="H1152" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1152" s="6" t="s">
         <v>799</v>
@@ -49212,7 +49197,7 @@
         <v>295</v>
       </c>
       <c r="B1153" s="6" t="s">
-        <v>1802</v>
+        <v>1797</v>
       </c>
       <c r="C1153" s="6" t="s">
         <v>17</v>
@@ -49231,7 +49216,7 @@
         <v>2468</v>
       </c>
       <c r="H1153" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1153" s="6" t="s">
         <v>799</v>
@@ -49248,7 +49233,7 @@
         <v>1278</v>
       </c>
       <c r="B1154" s="6" t="s">
-        <v>1803</v>
+        <v>1798</v>
       </c>
       <c r="C1154" s="6" t="s">
         <v>17</v>
@@ -49267,7 +49252,7 @@
         <v>2472</v>
       </c>
       <c r="H1154" s="12" t="s">
-        <v>1804</v>
+        <v>1799</v>
       </c>
       <c r="I1154" s="6" t="s">
         <v>799</v>
@@ -49284,7 +49269,7 @@
         <v>372</v>
       </c>
       <c r="B1155" s="6" t="s">
-        <v>1805</v>
+        <v>1800</v>
       </c>
       <c r="C1155" s="6" t="s">
         <v>17</v>
@@ -49317,10 +49302,10 @@
     </row>
     <row r="1156" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1156" s="33" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="B1156" s="6" t="s">
-        <v>1807</v>
+        <v>1802</v>
       </c>
       <c r="C1156" s="6" t="s">
         <v>17</v>
@@ -49356,7 +49341,7 @@
         <v>405</v>
       </c>
       <c r="B1157" s="6" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="C1157" s="6" t="s">
         <v>17</v>
@@ -49500,7 +49485,7 @@
         <v>255</v>
       </c>
       <c r="B1161" s="6" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
       <c r="C1161" s="6" t="s">
         <v>17</v>
@@ -49536,7 +49521,7 @@
         <v>206</v>
       </c>
       <c r="B1162" s="6" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="C1162" s="6" t="s">
         <v>17</v>
@@ -49644,7 +49629,7 @@
         <v>355</v>
       </c>
       <c r="B1165" s="6" t="s">
-        <v>1811</v>
+        <v>1806</v>
       </c>
       <c r="C1165" s="6" t="s">
         <v>17</v>
@@ -49824,7 +49809,7 @@
         <v>756</v>
       </c>
       <c r="B1170" s="6" t="s">
-        <v>1812</v>
+        <v>1807</v>
       </c>
       <c r="C1170" s="6" t="s">
         <v>17</v>
@@ -49932,7 +49917,7 @@
         <v>401</v>
       </c>
       <c r="B1173" s="6" t="s">
-        <v>1813</v>
+        <v>1808</v>
       </c>
       <c r="C1173" s="6" t="s">
         <v>17</v>
@@ -50001,10 +49986,10 @@
     </row>
     <row r="1175" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1175" s="32" t="s">
-        <v>1814</v>
+        <v>1809</v>
       </c>
       <c r="B1175" s="6" t="s">
-        <v>1815</v>
+        <v>1810</v>
       </c>
       <c r="C1175" s="6" t="s">
         <v>17</v>
@@ -50076,7 +50061,7 @@
         <v>765</v>
       </c>
       <c r="B1177" s="6" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="C1177" s="6" t="s">
         <v>17</v>
@@ -50148,7 +50133,7 @@
         <v>421</v>
       </c>
       <c r="B1179" s="6" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="C1179" s="6" t="s">
         <v>17</v>
@@ -50184,7 +50169,7 @@
         <v>777</v>
       </c>
       <c r="B1180" s="6" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="C1180" s="6" t="s">
         <v>17</v>
@@ -50256,7 +50241,7 @@
         <v>395</v>
       </c>
       <c r="B1182" s="6" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="C1182" s="6" t="s">
         <v>17</v>
@@ -50289,10 +50274,10 @@
     </row>
     <row r="1183" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1183" s="34" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="B1183" s="6" t="s">
-        <v>1821</v>
+        <v>1816</v>
       </c>
       <c r="C1183" s="6" t="s">
         <v>17</v>
@@ -50325,10 +50310,10 @@
     </row>
     <row r="1184" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1184" s="34" t="s">
-        <v>1822</v>
+        <v>1817</v>
       </c>
       <c r="B1184" s="6" t="s">
-        <v>1823</v>
+        <v>1818</v>
       </c>
       <c r="C1184" s="6" t="s">
         <v>17</v>
@@ -50361,10 +50346,10 @@
     </row>
     <row r="1185" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1185" s="34" t="s">
-        <v>1824</v>
+        <v>1819</v>
       </c>
       <c r="B1185" s="6" t="s">
-        <v>1825</v>
+        <v>1820</v>
       </c>
       <c r="C1185" s="6" t="s">
         <v>17</v>
@@ -50397,10 +50382,10 @@
     </row>
     <row r="1186" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1186" s="34" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="B1186" s="6" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="C1186" s="6" t="s">
         <v>17</v>
@@ -50436,7 +50421,7 @@
         <v>210</v>
       </c>
       <c r="B1187" s="6" t="s">
-        <v>1828</v>
+        <v>1823</v>
       </c>
       <c r="C1187" s="6" t="s">
         <v>17</v>
@@ -50455,7 +50440,7 @@
         <v>5024</v>
       </c>
       <c r="H1187" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1187" s="6" t="s">
         <v>66</v>
@@ -50469,10 +50454,10 @@
     </row>
     <row r="1188" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1188" s="31" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
       <c r="B1188" s="6" t="s">
-        <v>1831</v>
+        <v>1826</v>
       </c>
       <c r="C1188" s="6" t="s">
         <v>17</v>
@@ -50491,7 +50476,7 @@
         <v>5024</v>
       </c>
       <c r="H1188" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1188" s="6" t="s">
         <v>66</v>
@@ -50527,7 +50512,7 @@
         <v>5024</v>
       </c>
       <c r="H1189" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1189" s="6" t="s">
         <v>66</v>
@@ -50563,7 +50548,7 @@
         <v>5024</v>
       </c>
       <c r="H1190" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1190" s="6" t="s">
         <v>66</v>
@@ -50580,7 +50565,7 @@
         <v>316</v>
       </c>
       <c r="B1191" s="6" t="s">
-        <v>1832</v>
+        <v>1827</v>
       </c>
       <c r="C1191" s="6" t="s">
         <v>17</v>
@@ -50599,7 +50584,7 @@
         <v>5024</v>
       </c>
       <c r="H1191" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1191" s="6" t="s">
         <v>66</v>
@@ -50613,10 +50598,10 @@
     </row>
     <row r="1192" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1192" s="31" t="s">
-        <v>1833</v>
+        <v>1828</v>
       </c>
       <c r="B1192" s="6" t="s">
-        <v>1834</v>
+        <v>1829</v>
       </c>
       <c r="C1192" s="6" t="s">
         <v>17</v>
@@ -50635,7 +50620,7 @@
         <v>5024</v>
       </c>
       <c r="H1192" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1192" s="6" t="s">
         <v>66</v>
@@ -50649,10 +50634,10 @@
     </row>
     <row r="1193" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1193" s="31" t="s">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="B1193" s="6" t="s">
-        <v>1836</v>
+        <v>1831</v>
       </c>
       <c r="C1193" s="6" t="s">
         <v>17</v>
@@ -50671,7 +50656,7 @@
         <v>5024</v>
       </c>
       <c r="H1193" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1193" s="6" t="s">
         <v>66</v>
@@ -50707,7 +50692,7 @@
         <v>5024</v>
       </c>
       <c r="H1194" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1194" s="6" t="s">
         <v>66</v>
@@ -50724,7 +50709,7 @@
         <v>962</v>
       </c>
       <c r="B1195" s="6" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="C1195" s="6" t="s">
         <v>17</v>
@@ -50743,7 +50728,7 @@
         <v>5024</v>
       </c>
       <c r="H1195" s="12" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="I1195" s="6" t="s">
         <v>66</v>
@@ -50796,7 +50781,7 @@
         <v>641</v>
       </c>
       <c r="B1197" s="6" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
       <c r="C1197" s="6" t="s">
         <v>17</v>
@@ -50829,10 +50814,10 @@
     </row>
     <row r="1198" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1198" s="31" t="s">
-        <v>1839</v>
+        <v>1834</v>
       </c>
       <c r="B1198" s="6" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="C1198" s="6" t="s">
         <v>17</v>
@@ -50868,7 +50853,7 @@
         <v>342</v>
       </c>
       <c r="B1199" s="6" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="C1199" s="6" t="s">
         <v>17</v>
@@ -50904,7 +50889,7 @@
         <v>209</v>
       </c>
       <c r="B1200" s="6" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="C1200" s="6" t="s">
         <v>17</v>
@@ -50940,7 +50925,7 @@
         <v>194</v>
       </c>
       <c r="B1201" s="6" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="C1201" s="6" t="s">
         <v>17</v>
@@ -50973,10 +50958,10 @@
     </row>
     <row r="1202" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1202" s="31" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="B1202" s="6" t="s">
-        <v>1845</v>
+        <v>1840</v>
       </c>
       <c r="C1202" s="6" t="s">
         <v>17</v>
@@ -51012,7 +50997,7 @@
         <v>1048</v>
       </c>
       <c r="B1203" s="6" t="s">
-        <v>1846</v>
+        <v>1841</v>
       </c>
       <c r="C1203" s="6" t="s">
         <v>17</v>
@@ -51048,7 +51033,7 @@
         <v>217</v>
       </c>
       <c r="B1204" s="6" t="s">
-        <v>1847</v>
+        <v>1842</v>
       </c>
       <c r="C1204" s="6" t="s">
         <v>17</v>
@@ -51081,10 +51066,10 @@
     </row>
     <row r="1205" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1205" s="32" t="s">
-        <v>1848</v>
+        <v>1843</v>
       </c>
       <c r="B1205" s="6" t="s">
-        <v>1849</v>
+        <v>1844</v>
       </c>
       <c r="C1205" s="6" t="s">
         <v>17</v>
@@ -51120,7 +51105,7 @@
         <v>204</v>
       </c>
       <c r="B1206" s="6" t="s">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="C1206" s="6" t="s">
         <v>17</v>
@@ -51156,7 +51141,7 @@
         <v>259</v>
       </c>
       <c r="B1207" s="6" t="s">
-        <v>1851</v>
+        <v>1846</v>
       </c>
       <c r="C1207" s="6" t="s">
         <v>17</v>
@@ -51175,7 +51160,7 @@
         <v>24592</v>
       </c>
       <c r="H1207" s="12" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="I1207" s="6" t="s">
         <v>75</v>
@@ -51192,7 +51177,7 @@
         <v>264</v>
       </c>
       <c r="B1208" s="6" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="C1208" s="6" t="s">
         <v>17</v>
@@ -51211,7 +51196,7 @@
         <v>829</v>
       </c>
       <c r="H1208" s="12" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I1208" s="6" t="s">
         <v>83</v>
@@ -51225,10 +51210,10 @@
     </row>
     <row r="1209" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1209" s="31" t="s">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="B1209" s="6" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="C1209" s="6" t="s">
         <v>17</v>
@@ -51247,10 +51232,10 @@
         <v>31</v>
       </c>
       <c r="H1209" s="12" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I1209" s="6" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
       <c r="J1209" s="6">
         <v>6382</v>
@@ -51264,7 +51249,7 @@
         <v>1532</v>
       </c>
       <c r="B1210" s="6" t="s">
-        <v>1858</v>
+        <v>1853</v>
       </c>
       <c r="C1210" s="6" t="s">
         <v>17</v>
@@ -51283,10 +51268,10 @@
         <v>31</v>
       </c>
       <c r="H1210" s="12" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I1210" s="6" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
       <c r="J1210" s="6">
         <v>6382</v>
@@ -51300,7 +51285,7 @@
         <v>1534</v>
       </c>
       <c r="B1211" s="6" t="s">
-        <v>1859</v>
+        <v>1854</v>
       </c>
       <c r="C1211" s="6" t="s">
         <v>17</v>
@@ -51319,10 +51304,10 @@
         <v>31</v>
       </c>
       <c r="H1211" s="12" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="I1211" s="6" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
       <c r="J1211" s="6">
         <v>6382</v>
@@ -51333,10 +51318,10 @@
     </row>
     <row r="1212" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1212" s="31" t="s">
-        <v>1860</v>
+        <v>1855</v>
       </c>
       <c r="B1212" s="6" t="s">
-        <v>1861</v>
+        <v>1856</v>
       </c>
       <c r="C1212" s="6" t="s">
         <v>17</v>
@@ -51355,7 +51340,7 @@
         <v>24600</v>
       </c>
       <c r="H1212" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1212" s="6" t="s">
         <v>75</v>
@@ -51370,7 +51355,7 @@
     <row r="1213" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1213" s="42"/>
       <c r="B1213" s="18" t="s">
-        <v>1862</v>
+        <v>1857</v>
       </c>
       <c r="C1213" s="18" t="s">
         <v>17</v>
@@ -51389,7 +51374,7 @@
         <v>105</v>
       </c>
       <c r="H1213" s="21" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1213" s="18" t="s">
         <v>346</v>
@@ -51403,10 +51388,10 @@
     </row>
     <row r="1214" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1214" s="32" t="s">
-        <v>1863</v>
+        <v>1858</v>
       </c>
       <c r="B1214" s="6" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="C1214" s="6" t="s">
         <v>17</v>
@@ -51425,7 +51410,7 @@
         <v>106</v>
       </c>
       <c r="H1214" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1214" s="6" t="s">
         <v>346</v>
@@ -51439,10 +51424,10 @@
     </row>
     <row r="1215" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1215" s="31" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
       <c r="B1215" s="6" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
       <c r="C1215" s="6" t="s">
         <v>17</v>
@@ -51461,7 +51446,7 @@
         <v>106</v>
       </c>
       <c r="H1215" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1215" s="6" t="s">
         <v>346</v>
@@ -51475,10 +51460,10 @@
     </row>
     <row r="1216" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1216" s="33" t="s">
-        <v>1867</v>
+        <v>1862</v>
       </c>
       <c r="B1216" s="6" t="s">
-        <v>1868</v>
+        <v>1863</v>
       </c>
       <c r="C1216" s="6" t="s">
         <v>17</v>
@@ -51497,7 +51482,7 @@
         <v>106</v>
       </c>
       <c r="H1216" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1216" s="6" t="s">
         <v>346</v>
@@ -51511,10 +51496,10 @@
     </row>
     <row r="1217" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1217" s="33" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="B1217" s="6" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="C1217" s="6" t="s">
         <v>17</v>
@@ -51533,7 +51518,7 @@
         <v>106</v>
       </c>
       <c r="H1217" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1217" s="6" t="s">
         <v>346</v>
@@ -51547,10 +51532,10 @@
     </row>
     <row r="1218" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1218" s="33" t="s">
-        <v>1871</v>
+        <v>1866</v>
       </c>
       <c r="B1218" s="6" t="s">
-        <v>1872</v>
+        <v>1867</v>
       </c>
       <c r="C1218" s="6" t="s">
         <v>17</v>
@@ -51569,7 +51554,7 @@
         <v>106</v>
       </c>
       <c r="H1218" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1218" s="6" t="s">
         <v>346</v>
@@ -51583,10 +51568,10 @@
     </row>
     <row r="1219" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1219" s="31" t="s">
-        <v>1873</v>
+        <v>1868</v>
       </c>
       <c r="B1219" s="6" t="s">
-        <v>1874</v>
+        <v>1869</v>
       </c>
       <c r="C1219" s="6" t="s">
         <v>17</v>
@@ -51605,7 +51590,7 @@
         <v>106</v>
       </c>
       <c r="H1219" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1219" s="6" t="s">
         <v>346</v>
@@ -51622,7 +51607,7 @@
         <v>269</v>
       </c>
       <c r="B1220" s="6" t="s">
-        <v>1875</v>
+        <v>1870</v>
       </c>
       <c r="C1220" s="6" t="s">
         <v>17</v>
@@ -51641,7 +51626,7 @@
         <v>106</v>
       </c>
       <c r="H1220" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1220" s="6" t="s">
         <v>346</v>
@@ -51658,7 +51643,7 @@
         <v>304</v>
       </c>
       <c r="B1221" s="6" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="C1221" s="6" t="s">
         <v>17</v>
@@ -51677,7 +51662,7 @@
         <v>106</v>
       </c>
       <c r="H1221" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1221" s="6" t="s">
         <v>346</v>
@@ -51694,7 +51679,7 @@
         <v>303</v>
       </c>
       <c r="B1222" s="6" t="s">
-        <v>1777</v>
+        <v>1772</v>
       </c>
       <c r="C1222" s="6" t="s">
         <v>17</v>
@@ -51713,7 +51698,7 @@
         <v>106</v>
       </c>
       <c r="H1222" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1222" s="6" t="s">
         <v>346</v>
@@ -51727,10 +51712,10 @@
     </row>
     <row r="1223" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1223" s="31" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="B1223" s="6" t="s">
-        <v>1878</v>
+        <v>1873</v>
       </c>
       <c r="C1223" s="6" t="s">
         <v>17</v>
@@ -51749,7 +51734,7 @@
         <v>106</v>
       </c>
       <c r="H1223" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1223" s="6" t="s">
         <v>346</v>
@@ -51766,7 +51751,7 @@
         <v>270</v>
       </c>
       <c r="B1224" s="6" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
       <c r="C1224" s="6" t="s">
         <v>17</v>
@@ -51785,7 +51770,7 @@
         <v>106</v>
       </c>
       <c r="H1224" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1224" s="6" t="s">
         <v>346</v>
@@ -51799,10 +51784,10 @@
     </row>
     <row r="1225" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1225" s="31" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="B1225" s="6" t="s">
-        <v>1881</v>
+        <v>1876</v>
       </c>
       <c r="C1225" s="6" t="s">
         <v>17</v>
@@ -51821,7 +51806,7 @@
         <v>14159</v>
       </c>
       <c r="H1225" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1225" s="6" t="s">
         <v>116</v>
@@ -51838,7 +51823,7 @@
         <v>220</v>
       </c>
       <c r="B1226" s="6" t="s">
-        <v>1883</v>
+        <v>1878</v>
       </c>
       <c r="C1226" s="6" t="s">
         <v>40</v>
@@ -51857,7 +51842,7 @@
         <v>14159</v>
       </c>
       <c r="H1226" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1226" s="6" t="s">
         <v>116</v>
@@ -51872,7 +51857,7 @@
     <row r="1227" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1227" s="31"/>
       <c r="B1227" s="17" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="C1227" s="6" t="s">
         <v>17</v>
@@ -51891,7 +51876,7 @@
         <v>14159</v>
       </c>
       <c r="H1227" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1227" s="6" t="s">
         <v>116</v>
@@ -51908,7 +51893,7 @@
         <v>292</v>
       </c>
       <c r="B1228" s="6" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="C1228" s="6" t="s">
         <v>40</v>
@@ -51927,7 +51912,7 @@
         <v>6002130</v>
       </c>
       <c r="H1228" s="12" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="I1228" s="6" t="s">
         <v>347</v>
@@ -51944,7 +51929,7 @@
         <v>291</v>
       </c>
       <c r="B1229" s="6" t="s">
-        <v>1887</v>
+        <v>1882</v>
       </c>
       <c r="C1229" s="6" t="s">
         <v>40</v>
@@ -51963,7 +51948,7 @@
         <v>6002130</v>
       </c>
       <c r="H1229" s="12" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="I1229" s="6" t="s">
         <v>347</v>
@@ -51980,7 +51965,7 @@
         <v>1264</v>
       </c>
       <c r="B1230" s="6" t="s">
-        <v>1888</v>
+        <v>1883</v>
       </c>
       <c r="C1230" s="6" t="s">
         <v>17</v>
@@ -51999,7 +51984,7 @@
         <v>1266</v>
       </c>
       <c r="H1230" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1230" s="6" t="s">
         <v>1180</v>
@@ -52035,7 +52020,7 @@
         <v>1266</v>
       </c>
       <c r="H1231" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1231" s="6" t="s">
         <v>1180</v>
@@ -52052,7 +52037,7 @@
         <v>1183</v>
       </c>
       <c r="B1232" s="6" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="C1232" s="6" t="s">
         <v>17</v>
@@ -52071,7 +52056,7 @@
         <v>1266</v>
       </c>
       <c r="H1232" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1232" s="6" t="s">
         <v>1180</v>
@@ -52107,7 +52092,7 @@
         <v>1266</v>
       </c>
       <c r="H1233" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1233" s="6" t="s">
         <v>1180</v>
@@ -52121,10 +52106,10 @@
     </row>
     <row r="1234" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1234" s="31" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
       <c r="B1234" s="6" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
       <c r="C1234" s="6" t="s">
         <v>40</v>
@@ -52143,7 +52128,7 @@
         <v>111</v>
       </c>
       <c r="H1234" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1234" s="6" t="s">
         <v>346</v>
@@ -52157,10 +52142,10 @@
     </row>
     <row r="1235" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1235" s="31" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
       <c r="B1235" s="6" t="s">
-        <v>1894</v>
+        <v>1889</v>
       </c>
       <c r="C1235" s="6" t="s">
         <v>17</v>
@@ -52179,7 +52164,7 @@
         <v>111</v>
       </c>
       <c r="H1235" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1235" s="6" t="s">
         <v>346</v>
@@ -52193,10 +52178,10 @@
     </row>
     <row r="1236" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1236" s="31" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="B1236" s="6" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="C1236" s="6" t="s">
         <v>17</v>
@@ -52215,7 +52200,7 @@
         <v>111</v>
       </c>
       <c r="H1236" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1236" s="6" t="s">
         <v>346</v>
@@ -52232,7 +52217,7 @@
         <v>912</v>
       </c>
       <c r="B1237" s="6" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
       <c r="C1237" s="6" t="s">
         <v>40</v>
@@ -52251,7 +52236,7 @@
         <v>111</v>
       </c>
       <c r="H1237" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1237" s="6" t="s">
         <v>346</v>
@@ -52268,7 +52253,7 @@
         <v>221</v>
       </c>
       <c r="B1238" s="6" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="C1238" s="6" t="s">
         <v>17</v>
@@ -52287,7 +52272,7 @@
         <v>14190</v>
       </c>
       <c r="H1238" s="12" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="I1238" s="6" t="s">
         <v>116</v>
@@ -52323,7 +52308,7 @@
         <v>14190</v>
       </c>
       <c r="H1239" s="12" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="I1239" s="6" t="s">
         <v>116</v>
@@ -52340,7 +52325,7 @@
         <v>440</v>
       </c>
       <c r="B1240" s="6" t="s">
-        <v>1900</v>
+        <v>1895</v>
       </c>
       <c r="C1240" s="6" t="s">
         <v>17</v>
@@ -52359,7 +52344,7 @@
         <v>14190</v>
       </c>
       <c r="H1240" s="12" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="I1240" s="6" t="s">
         <v>116</v>
@@ -52376,7 +52361,7 @@
         <v>1030</v>
       </c>
       <c r="B1241" s="6" t="s">
-        <v>1901</v>
+        <v>1896</v>
       </c>
       <c r="C1241" s="6" t="s">
         <v>17</v>
@@ -52395,7 +52380,7 @@
         <v>14190</v>
       </c>
       <c r="H1241" s="12" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="I1241" s="6" t="s">
         <v>116</v>
@@ -52409,10 +52394,10 @@
     </row>
     <row r="1242" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1242" s="31" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="B1242" s="6" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="C1242" s="6" t="s">
         <v>17</v>
@@ -52434,7 +52419,7 @@
         <v>1549</v>
       </c>
       <c r="I1242" s="6" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="J1242" s="6">
         <v>6395</v>
@@ -52445,10 +52430,10 @@
     </row>
     <row r="1243" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1243" s="31" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="B1243" s="6" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="C1243" s="6" t="s">
         <v>17</v>
@@ -52470,7 +52455,7 @@
         <v>1549</v>
       </c>
       <c r="I1243" s="6" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="J1243" s="6">
         <v>6395</v>
@@ -52481,10 +52466,10 @@
     </row>
     <row r="1244" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1244" s="31" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
       <c r="B1244" s="6" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="C1244" s="6" t="s">
         <v>40</v>
@@ -52503,7 +52488,7 @@
         <v>140</v>
       </c>
       <c r="H1244" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1244" s="6" t="s">
         <v>112</v>
@@ -52517,10 +52502,10 @@
     </row>
     <row r="1245" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1245" s="31" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
       <c r="B1245" s="6" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="C1245" s="6" t="s">
         <v>40</v>
@@ -52539,7 +52524,7 @@
         <v>140</v>
       </c>
       <c r="H1245" s="12" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="I1245" s="6" t="s">
         <v>112</v>
@@ -52575,7 +52560,7 @@
         <v>4953</v>
       </c>
       <c r="H1246" s="12" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="I1246" s="6" t="s">
         <v>66</v>
@@ -52611,7 +52596,7 @@
         <v>4953</v>
       </c>
       <c r="H1247" s="12" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="I1247" s="6" t="s">
         <v>66</v>
@@ -52628,7 +52613,7 @@
         <v>235</v>
       </c>
       <c r="B1248" s="6" t="s">
-        <v>1912</v>
+        <v>1907</v>
       </c>
       <c r="C1248" s="6" t="s">
         <v>17</v>
@@ -52661,10 +52646,10 @@
     </row>
     <row r="1249" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1249" s="31" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="B1249" s="6" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="C1249" s="6" t="s">
         <v>17</v>
@@ -52700,7 +52685,7 @@
         <v>338</v>
       </c>
       <c r="B1250" s="6" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
       <c r="C1250" s="6" t="s">
         <v>17</v>
@@ -52733,10 +52718,10 @@
     </row>
     <row r="1251" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1251" s="31" t="s">
-        <v>1916</v>
+        <v>1911</v>
       </c>
       <c r="B1251" s="6" t="s">
-        <v>1917</v>
+        <v>1912</v>
       </c>
       <c r="C1251" s="6" t="s">
         <v>17</v>
@@ -52772,7 +52757,7 @@
         <v>341</v>
       </c>
       <c r="B1252" s="6" t="s">
-        <v>1918</v>
+        <v>1913</v>
       </c>
       <c r="C1252" s="6" t="s">
         <v>17</v>
@@ -52805,10 +52790,10 @@
     </row>
     <row r="1253" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1253" s="31" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
       <c r="B1253" s="6" t="s">
-        <v>1831</v>
+        <v>1826</v>
       </c>
       <c r="C1253" s="6" t="s">
         <v>17</v>
@@ -52844,7 +52829,7 @@
         <v>960</v>
       </c>
       <c r="B1254" s="17" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="C1254" s="6" t="s">
         <v>17</v>
@@ -52880,7 +52865,7 @@
         <v>310</v>
       </c>
       <c r="B1255" s="6" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C1255" s="6" t="s">
         <v>17</v>
@@ -52916,7 +52901,7 @@
         <v>316</v>
       </c>
       <c r="B1256" s="6" t="s">
-        <v>1832</v>
+        <v>1827</v>
       </c>
       <c r="C1256" s="6" t="s">
         <v>17</v>
@@ -52949,10 +52934,10 @@
     </row>
     <row r="1257" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1257" s="31" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
       <c r="B1257" s="6" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="C1257" s="6" t="s">
         <v>17</v>
@@ -53007,7 +52992,7 @@
         <v>12686</v>
       </c>
       <c r="H1258" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1258" s="6" t="s">
         <v>497</v>
@@ -53021,10 +53006,10 @@
     </row>
     <row r="1259" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1259" s="31" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="B1259" s="6" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
       <c r="C1259" s="6" t="s">
         <v>17</v>
@@ -53043,7 +53028,7 @@
         <v>12686</v>
       </c>
       <c r="H1259" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1259" s="6" t="s">
         <v>497</v>
@@ -53057,10 +53042,10 @@
     </row>
     <row r="1260" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1260" s="31" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
       <c r="B1260" s="6" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="C1260" s="6" t="s">
         <v>17</v>
@@ -53079,7 +53064,7 @@
         <v>12686</v>
       </c>
       <c r="H1260" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1260" s="6" t="s">
         <v>497</v>
@@ -53096,7 +53081,7 @@
         <v>195</v>
       </c>
       <c r="B1261" s="6" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
       <c r="C1261" s="6" t="s">
         <v>17</v>
@@ -53115,7 +53100,7 @@
         <v>12686</v>
       </c>
       <c r="H1261" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1261" s="6" t="s">
         <v>497</v>
@@ -53132,7 +53117,7 @@
         <v>712</v>
       </c>
       <c r="B1262" s="6" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="C1262" s="6" t="s">
         <v>17</v>
@@ -53151,7 +53136,7 @@
         <v>12686</v>
       </c>
       <c r="H1262" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1262" s="6" t="s">
         <v>497</v>
@@ -53168,7 +53153,7 @@
         <v>1411</v>
       </c>
       <c r="B1263" s="6" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="C1263" s="6" t="s">
         <v>17</v>
@@ -53187,7 +53172,7 @@
         <v>12686</v>
       </c>
       <c r="H1263" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1263" s="6" t="s">
         <v>497</v>
@@ -53201,10 +53186,10 @@
     </row>
     <row r="1264" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1264" s="31" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="B1264" s="6" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="C1264" s="6" t="s">
         <v>17</v>
@@ -53223,7 +53208,7 @@
         <v>12686</v>
       </c>
       <c r="H1264" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1264" s="6" t="s">
         <v>497</v>
@@ -53237,10 +53222,10 @@
     </row>
     <row r="1265" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1265" s="31" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="B1265" s="6" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="C1265" s="6" t="s">
         <v>17</v>
@@ -53259,7 +53244,7 @@
         <v>12686</v>
       </c>
       <c r="H1265" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1265" s="6" t="s">
         <v>497</v>
@@ -53276,7 +53261,7 @@
         <v>594</v>
       </c>
       <c r="B1266" s="6" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="C1266" s="6" t="s">
         <v>17</v>
@@ -53295,7 +53280,7 @@
         <v>12686</v>
       </c>
       <c r="H1266" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1266" s="6" t="s">
         <v>497</v>
@@ -53312,7 +53297,7 @@
         <v>1183</v>
       </c>
       <c r="B1267" s="6" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="C1267" s="6" t="s">
         <v>17</v>
@@ -53331,7 +53316,7 @@
         <v>1267</v>
       </c>
       <c r="H1267" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1267" s="6" t="s">
         <v>1180</v>
@@ -53345,10 +53330,10 @@
     </row>
     <row r="1268" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1268" s="32" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="B1268" s="6" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="C1268" s="6" t="s">
         <v>17</v>
@@ -53367,7 +53352,7 @@
         <v>1267</v>
       </c>
       <c r="H1268" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1268" s="6" t="s">
         <v>1180</v>
@@ -53403,7 +53388,7 @@
         <v>1267</v>
       </c>
       <c r="H1269" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1269" s="6" t="s">
         <v>1180</v>
@@ -53439,7 +53424,7 @@
         <v>1267</v>
       </c>
       <c r="H1270" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1270" s="6" t="s">
         <v>1180</v>
@@ -53453,10 +53438,10 @@
     </row>
     <row r="1271" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1271" s="32" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="B1271" s="6" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="C1271" s="6" t="s">
         <v>17</v>
@@ -53475,7 +53460,7 @@
         <v>1267</v>
       </c>
       <c r="H1271" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1271" s="6" t="s">
         <v>1180</v>
@@ -53492,7 +53477,7 @@
         <v>436</v>
       </c>
       <c r="B1272" s="6" t="s">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="C1272" s="6" t="s">
         <v>17</v>
@@ -53511,7 +53496,7 @@
         <v>1267</v>
       </c>
       <c r="H1272" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1272" s="6" t="s">
         <v>1180</v>
@@ -53525,10 +53510,10 @@
     </row>
     <row r="1273" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1273" s="32" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="B1273" s="6" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="C1273" s="6" t="s">
         <v>17</v>
@@ -53547,7 +53532,7 @@
         <v>1267</v>
       </c>
       <c r="H1273" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1273" s="6" t="s">
         <v>1180</v>
@@ -53561,10 +53546,10 @@
     </row>
     <row r="1274" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1274" s="32" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="B1274" s="6" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="C1274" s="6" t="s">
         <v>17</v>
@@ -53583,7 +53568,7 @@
         <v>1267</v>
       </c>
       <c r="H1274" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1274" s="6" t="s">
         <v>1180</v>
@@ -53597,10 +53582,10 @@
     </row>
     <row r="1275" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1275" s="32" t="s">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="B1275" s="6" t="s">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="C1275" s="6" t="s">
         <v>17</v>
@@ -53619,7 +53604,7 @@
         <v>1267</v>
       </c>
       <c r="H1275" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1275" s="6" t="s">
         <v>1180</v>
@@ -53636,7 +53621,7 @@
         <v>1247</v>
       </c>
       <c r="B1276" s="6" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
       <c r="C1276" s="6" t="s">
         <v>17</v>
@@ -53655,7 +53640,7 @@
         <v>1267</v>
       </c>
       <c r="H1276" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1276" s="6" t="s">
         <v>1180</v>
@@ -53672,7 +53657,7 @@
         <v>1229</v>
       </c>
       <c r="B1277" s="6" t="s">
-        <v>1947</v>
+        <v>1942</v>
       </c>
       <c r="C1277" s="6" t="s">
         <v>17</v>
@@ -53691,7 +53676,7 @@
         <v>1265</v>
       </c>
       <c r="H1277" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1277" s="6" t="s">
         <v>1180</v>
@@ -53705,10 +53690,10 @@
     </row>
     <row r="1278" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1278" s="32" t="s">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="B1278" s="6" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="C1278" s="6" t="s">
         <v>17</v>
@@ -53727,7 +53712,7 @@
         <v>1265</v>
       </c>
       <c r="H1278" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1278" s="6" t="s">
         <v>1180</v>
@@ -53741,10 +53726,10 @@
     </row>
     <row r="1279" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1279" s="32" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="B1279" s="6" t="s">
-        <v>1951</v>
+        <v>1946</v>
       </c>
       <c r="C1279" s="6" t="s">
         <v>17</v>
@@ -53763,7 +53748,7 @@
         <v>1265</v>
       </c>
       <c r="H1279" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1279" s="6" t="s">
         <v>1180</v>
@@ -53780,7 +53765,7 @@
         <v>1424</v>
       </c>
       <c r="B1280" s="6" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
       <c r="C1280" s="6" t="s">
         <v>17</v>
@@ -53799,7 +53784,7 @@
         <v>1265</v>
       </c>
       <c r="H1280" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1280" s="6" t="s">
         <v>1180</v>
@@ -53835,7 +53820,7 @@
         <v>1265</v>
       </c>
       <c r="H1281" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1281" s="6" t="s">
         <v>1180</v>
@@ -53871,7 +53856,7 @@
         <v>1265</v>
       </c>
       <c r="H1282" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1282" s="6" t="s">
         <v>1180</v>
@@ -53888,7 +53873,7 @@
         <v>1144</v>
       </c>
       <c r="B1283" s="6" t="s">
-        <v>1953</v>
+        <v>1948</v>
       </c>
       <c r="C1283" s="6" t="s">
         <v>17</v>
@@ -53907,7 +53892,7 @@
         <v>1265</v>
       </c>
       <c r="H1283" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1283" s="6" t="s">
         <v>1180</v>
@@ -53943,7 +53928,7 @@
         <v>1265</v>
       </c>
       <c r="H1284" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1284" s="6" t="s">
         <v>1180</v>
@@ -53979,7 +53964,7 @@
         <v>1265</v>
       </c>
       <c r="H1285" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1285" s="6" t="s">
         <v>1180</v>
@@ -53996,7 +53981,7 @@
         <v>1252</v>
       </c>
       <c r="B1286" s="6" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="C1286" s="6" t="s">
         <v>17</v>
@@ -54015,7 +54000,7 @@
         <v>1265</v>
       </c>
       <c r="H1286" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1286" s="6" t="s">
         <v>1180</v>
@@ -54032,7 +54017,7 @@
         <v>1201</v>
       </c>
       <c r="B1287" s="6" t="s">
-        <v>1955</v>
+        <v>1950</v>
       </c>
       <c r="C1287" s="6" t="s">
         <v>17</v>
@@ -54051,7 +54036,7 @@
         <v>1265</v>
       </c>
       <c r="H1287" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1287" s="6" t="s">
         <v>1180</v>
@@ -54065,10 +54050,10 @@
     </row>
     <row r="1288" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1288" s="32" t="s">
-        <v>1956</v>
+        <v>1951</v>
       </c>
       <c r="B1288" s="6" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="C1288" s="6" t="s">
         <v>17</v>
@@ -54087,7 +54072,7 @@
         <v>1265</v>
       </c>
       <c r="H1288" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1288" s="6" t="s">
         <v>1180</v>
@@ -54104,7 +54089,7 @@
         <v>1235</v>
       </c>
       <c r="B1289" s="6" t="s">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="C1289" s="6" t="s">
         <v>17</v>
@@ -54123,7 +54108,7 @@
         <v>1265</v>
       </c>
       <c r="H1289" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1289" s="6" t="s">
         <v>1180</v>
@@ -54159,7 +54144,7 @@
         <v>1265</v>
       </c>
       <c r="H1290" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1290" s="6" t="s">
         <v>1180</v>
@@ -54195,7 +54180,7 @@
         <v>1265</v>
       </c>
       <c r="H1291" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1291" s="6" t="s">
         <v>1180</v>
@@ -54212,7 +54197,7 @@
         <v>1197</v>
       </c>
       <c r="B1292" s="6" t="s">
-        <v>1959</v>
+        <v>1954</v>
       </c>
       <c r="C1292" s="6" t="s">
         <v>17</v>
@@ -54231,7 +54216,7 @@
         <v>1265</v>
       </c>
       <c r="H1292" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1292" s="6" t="s">
         <v>1180</v>
@@ -54267,7 +54252,7 @@
         <v>1265</v>
       </c>
       <c r="H1293" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1293" s="6" t="s">
         <v>1180</v>
@@ -54303,7 +54288,7 @@
         <v>1265</v>
       </c>
       <c r="H1294" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1294" s="6" t="s">
         <v>1180</v>
@@ -54320,7 +54305,7 @@
         <v>515</v>
       </c>
       <c r="B1295" s="6" t="s">
-        <v>1960</v>
+        <v>1955</v>
       </c>
       <c r="C1295" s="6" t="s">
         <v>17</v>
@@ -54348,7 +54333,7 @@
         <v>6403</v>
       </c>
       <c r="K1295" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1296" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54356,7 +54341,7 @@
         <v>518</v>
       </c>
       <c r="B1296" s="6" t="s">
-        <v>1962</v>
+        <v>1957</v>
       </c>
       <c r="C1296" s="6" t="s">
         <v>17</v>
@@ -54384,7 +54369,7 @@
         <v>6403</v>
       </c>
       <c r="K1296" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1297" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54392,7 +54377,7 @@
         <v>520</v>
       </c>
       <c r="B1297" s="6" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="C1297" s="6" t="s">
         <v>17</v>
@@ -54420,7 +54405,7 @@
         <v>6403</v>
       </c>
       <c r="K1297" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1298" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54428,7 +54413,7 @@
         <v>495</v>
       </c>
       <c r="B1298" s="6" t="s">
-        <v>1964</v>
+        <v>1959</v>
       </c>
       <c r="C1298" s="6" t="s">
         <v>17</v>
@@ -54456,7 +54441,7 @@
         <v>6404</v>
       </c>
       <c r="K1298" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1299" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54492,15 +54477,15 @@
         <v>6404</v>
       </c>
       <c r="K1299" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1300" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1300" s="31" t="s">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="B1300" s="6" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="C1300" s="6" t="s">
         <v>17</v>
@@ -54528,7 +54513,7 @@
         <v>6404</v>
       </c>
       <c r="K1300" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1301" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54536,7 +54521,7 @@
         <v>590</v>
       </c>
       <c r="B1301" s="6" t="s">
-        <v>1967</v>
+        <v>1962</v>
       </c>
       <c r="C1301" s="6" t="s">
         <v>17</v>
@@ -54564,15 +54549,15 @@
         <v>6404</v>
       </c>
       <c r="K1301" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1302" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1302" s="31" t="s">
-        <v>1968</v>
+        <v>1963</v>
       </c>
       <c r="B1302" s="6" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="C1302" s="6" t="s">
         <v>17</v>
@@ -54600,7 +54585,7 @@
         <v>6404</v>
       </c>
       <c r="K1302" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1303" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54608,7 +54593,7 @@
         <v>194</v>
       </c>
       <c r="B1303" s="6" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="C1303" s="6" t="s">
         <v>17</v>
@@ -54636,15 +54621,15 @@
         <v>6404</v>
       </c>
       <c r="K1303" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1304" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1304" s="31" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="B1304" s="6" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="C1304" s="6" t="s">
         <v>17</v>
@@ -54672,7 +54657,7 @@
         <v>6404</v>
       </c>
       <c r="K1304" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1305" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54708,7 +54693,7 @@
         <v>6404</v>
       </c>
       <c r="K1305" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1306" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54716,7 +54701,7 @@
         <v>1488</v>
       </c>
       <c r="B1306" s="6" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
       <c r="C1306" s="6" t="s">
         <v>17</v>
@@ -54744,7 +54729,7 @@
         <v>6405</v>
       </c>
       <c r="K1306" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1307" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54752,7 +54737,7 @@
         <v>1038</v>
       </c>
       <c r="B1307" s="6" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="C1307" s="6" t="s">
         <v>40</v>
@@ -54780,7 +54765,7 @@
         <v>6405</v>
       </c>
       <c r="K1307" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1308" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54788,7 +54773,7 @@
         <v>308</v>
       </c>
       <c r="B1308" s="17" t="s">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="C1308" s="6" t="s">
         <v>17</v>
@@ -54816,15 +54801,15 @@
         <v>6405</v>
       </c>
       <c r="K1308" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1309" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1309" s="31" t="s">
-        <v>1976</v>
+        <v>1971</v>
       </c>
       <c r="B1309" s="6" t="s">
-        <v>1977</v>
+        <v>1972</v>
       </c>
       <c r="C1309" s="6" t="s">
         <v>17</v>
@@ -54846,21 +54831,21 @@
         <v>46147</v>
       </c>
       <c r="I1309" s="6" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="J1309" s="6">
         <v>6406</v>
       </c>
       <c r="K1309" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1310" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1310" s="31" t="s">
-        <v>1979</v>
+        <v>1974</v>
       </c>
       <c r="B1310" s="6" t="s">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="C1310" s="6" t="s">
         <v>17</v>
@@ -54882,13 +54867,13 @@
         <v>46147</v>
       </c>
       <c r="I1310" s="6" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="J1310" s="6">
         <v>6406</v>
       </c>
       <c r="K1310" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1311" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -54896,7 +54881,7 @@
         <v>1069</v>
       </c>
       <c r="B1311" s="6" t="s">
-        <v>1981</v>
+        <v>1976</v>
       </c>
       <c r="C1311" s="6" t="s">
         <v>17</v>
@@ -54924,15 +54909,15 @@
         <v>6407</v>
       </c>
       <c r="K1311" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1312" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1312" s="31" t="s">
-        <v>1982</v>
+        <v>1977</v>
       </c>
       <c r="B1312" s="6" t="s">
-        <v>1983</v>
+        <v>1978</v>
       </c>
       <c r="C1312" s="6" t="s">
         <v>17</v>
@@ -54960,15 +54945,15 @@
         <v>6408</v>
       </c>
       <c r="K1312" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1313" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1313" s="34" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="B1313" s="6" t="s">
-        <v>1985</v>
+        <v>1980</v>
       </c>
       <c r="C1313" s="6" t="s">
         <v>17</v>
@@ -54996,7 +54981,7 @@
         <v>6408</v>
       </c>
       <c r="K1313" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1314" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55004,7 +54989,7 @@
         <v>723</v>
       </c>
       <c r="B1314" s="6" t="s">
-        <v>1795</v>
+        <v>1790</v>
       </c>
       <c r="C1314" s="6" t="s">
         <v>17</v>
@@ -55032,7 +55017,7 @@
         <v>6408</v>
       </c>
       <c r="K1314" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1315" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55040,7 +55025,7 @@
         <v>333</v>
       </c>
       <c r="B1315" s="6" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="C1315" s="6" t="s">
         <v>17</v>
@@ -55068,15 +55053,15 @@
         <v>6408</v>
       </c>
       <c r="K1315" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1316" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1316" s="31" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="B1316" s="6" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
       <c r="C1316" s="6" t="s">
         <v>17</v>
@@ -55104,15 +55089,15 @@
         <v>6408</v>
       </c>
       <c r="K1316" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1317" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1317" s="31" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
       <c r="B1317" s="6" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="C1317" s="6" t="s">
         <v>17</v>
@@ -55140,15 +55125,15 @@
         <v>6408</v>
       </c>
       <c r="K1317" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1318" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1318" s="31" t="s">
-        <v>1991</v>
+        <v>1986</v>
       </c>
       <c r="B1318" s="6" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="C1318" s="6" t="s">
         <v>17</v>
@@ -55176,7 +55161,7 @@
         <v>6408</v>
       </c>
       <c r="K1318" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1319" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55184,7 +55169,7 @@
         <v>291</v>
       </c>
       <c r="B1319" s="6" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
       <c r="C1319" s="6" t="s">
         <v>40</v>
@@ -55212,7 +55197,7 @@
         <v>6409</v>
       </c>
       <c r="K1319" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1320" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55220,7 +55205,7 @@
         <v>292</v>
       </c>
       <c r="B1320" s="6" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="C1320" s="6" t="s">
         <v>40</v>
@@ -55248,7 +55233,7 @@
         <v>6409</v>
       </c>
       <c r="K1320" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1321" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55256,7 +55241,7 @@
         <v>687</v>
       </c>
       <c r="B1321" s="6" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="C1321" s="6" t="s">
         <v>17</v>
@@ -55284,12 +55269,12 @@
         <v>6410</v>
       </c>
       <c r="K1321" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1322" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1322" s="31" t="s">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="B1322" s="6" t="s">
         <v>512</v>
@@ -55320,7 +55305,7 @@
         <v>6411</v>
       </c>
       <c r="K1322" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1323" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55356,7 +55341,7 @@
         <v>6411</v>
       </c>
       <c r="K1323" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1324" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55392,15 +55377,15 @@
         <v>6411</v>
       </c>
       <c r="K1324" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1325" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1325" s="35" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="B1325" s="18" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="C1325" s="19" t="s">
         <v>40</v>
@@ -55428,15 +55413,15 @@
         <v>6412</v>
       </c>
       <c r="K1325" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1326" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1326" s="35" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
       <c r="B1326" s="18" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="C1326" s="19" t="s">
         <v>40</v>
@@ -55464,15 +55449,15 @@
         <v>6412</v>
       </c>
       <c r="K1326" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1327" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1327" s="35" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="B1327" s="18" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="C1327" s="19" t="s">
         <v>40</v>
@@ -55500,15 +55485,15 @@
         <v>6412</v>
       </c>
       <c r="K1327" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1328" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1328" s="35" t="s">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="B1328" s="18" t="s">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="C1328" s="19" t="s">
         <v>40</v>
@@ -55536,15 +55521,15 @@
         <v>6412</v>
       </c>
       <c r="K1328" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1329" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1329" s="35" t="s">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="B1329" s="18" t="s">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="C1329" s="19" t="s">
         <v>40</v>
@@ -55572,7 +55557,7 @@
         <v>6412</v>
       </c>
       <c r="K1329" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1330" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55599,24 +55584,24 @@
         <v>1717</v>
       </c>
       <c r="H1330" s="12" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="I1330" s="6" t="s">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="J1330" s="6">
         <v>6413</v>
       </c>
       <c r="K1330" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1331" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1331" s="31" t="s">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B1331" s="6" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="C1331" s="6" t="s">
         <v>40</v>
@@ -55638,21 +55623,21 @@
         <v>46028</v>
       </c>
       <c r="I1331" s="6" t="s">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="J1331" s="6">
         <v>6414</v>
       </c>
       <c r="K1331" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1332" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1332" s="31" t="s">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="B1332" s="6" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="C1332" s="6" t="s">
         <v>40</v>
@@ -55674,13 +55659,13 @@
         <v>46028</v>
       </c>
       <c r="I1332" s="6" t="s">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="J1332" s="6">
         <v>6414</v>
       </c>
       <c r="K1332" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1333" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55688,7 +55673,7 @@
         <v>1243</v>
       </c>
       <c r="B1333" s="6" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C1333" s="6" t="s">
         <v>17</v>
@@ -55707,7 +55692,7 @@
         <v>112</v>
       </c>
       <c r="H1333" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1333" s="6" t="s">
         <v>346</v>
@@ -55716,7 +55701,7 @@
         <v>6415</v>
       </c>
       <c r="K1333" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1334" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55724,7 +55709,7 @@
         <v>284</v>
       </c>
       <c r="B1334" s="6" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C1334" s="6" t="s">
         <v>17</v>
@@ -55743,7 +55728,7 @@
         <v>112</v>
       </c>
       <c r="H1334" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1334" s="6" t="s">
         <v>346</v>
@@ -55752,7 +55737,7 @@
         <v>6415</v>
       </c>
       <c r="K1334" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1335" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55760,7 +55745,7 @@
         <v>273</v>
       </c>
       <c r="B1335" s="6" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="C1335" s="6" t="s">
         <v>17</v>
@@ -55779,7 +55764,7 @@
         <v>112</v>
       </c>
       <c r="H1335" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1335" s="6" t="s">
         <v>346</v>
@@ -55788,7 +55773,7 @@
         <v>6415</v>
       </c>
       <c r="K1335" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1336" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55796,7 +55781,7 @@
         <v>1077</v>
       </c>
       <c r="B1336" s="6" t="s">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C1336" s="6" t="s">
         <v>17</v>
@@ -55815,7 +55800,7 @@
         <v>112</v>
       </c>
       <c r="H1336" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1336" s="6" t="s">
         <v>346</v>
@@ -55824,7 +55809,7 @@
         <v>6415</v>
       </c>
       <c r="K1336" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1337" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55832,7 +55817,7 @@
         <v>1268</v>
       </c>
       <c r="B1337" s="6" t="s">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C1337" s="6" t="s">
         <v>17</v>
@@ -55851,7 +55836,7 @@
         <v>112</v>
       </c>
       <c r="H1337" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1337" s="6" t="s">
         <v>346</v>
@@ -55860,7 +55845,7 @@
         <v>6415</v>
       </c>
       <c r="K1337" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1338" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55868,7 +55853,7 @@
         <v>1079</v>
       </c>
       <c r="B1338" s="6" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C1338" s="6" t="s">
         <v>17</v>
@@ -55887,7 +55872,7 @@
         <v>112</v>
       </c>
       <c r="H1338" s="12" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I1338" s="6" t="s">
         <v>346</v>
@@ -55896,7 +55881,7 @@
         <v>6415</v>
       </c>
       <c r="K1338" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1339" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -55904,7 +55889,7 @@
         <v>813</v>
       </c>
       <c r="B1339" s="6" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C1339" s="6" t="s">
         <v>17</v>
@@ -55932,15 +55917,15 @@
         <v>6416</v>
       </c>
       <c r="K1339" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1340" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1340" s="31" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B1340" s="6" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C1340" s="6" t="s">
         <v>17</v>
@@ -55968,15 +55953,15 @@
         <v>6416</v>
       </c>
       <c r="K1340" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1341" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1341" s="31" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B1341" s="6" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C1341" s="6" t="s">
         <v>17</v>
@@ -56004,15 +55989,15 @@
         <v>6416</v>
       </c>
       <c r="K1341" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1342" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1342" s="31" t="s">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B1342" s="6" t="s">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C1342" s="6" t="s">
         <v>17</v>
@@ -56040,7 +56025,7 @@
         <v>6416</v>
       </c>
       <c r="K1342" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1343" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56048,7 +56033,7 @@
         <v>809</v>
       </c>
       <c r="B1343" s="6" t="s">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="C1343" s="6" t="s">
         <v>17</v>
@@ -56076,15 +56061,15 @@
         <v>6416</v>
       </c>
       <c r="K1343" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1344" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1344" s="31" t="s">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="B1344" s="6" t="s">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="C1344" s="6" t="s">
         <v>17</v>
@@ -56112,7 +56097,7 @@
         <v>6416</v>
       </c>
       <c r="K1344" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1345" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56148,15 +56133,15 @@
         <v>6416</v>
       </c>
       <c r="K1345" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1346" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1346" s="31" t="s">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="B1346" s="6" t="s">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="C1346" s="6" t="s">
         <v>17</v>
@@ -56184,7 +56169,7 @@
         <v>6416</v>
       </c>
       <c r="K1346" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1347" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56192,7 +56177,7 @@
         <v>841</v>
       </c>
       <c r="B1347" s="6" t="s">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="C1347" s="6" t="s">
         <v>17</v>
@@ -56220,15 +56205,15 @@
         <v>6417</v>
       </c>
       <c r="K1347" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1348" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1348" s="31" t="s">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B1348" s="6" t="s">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="C1348" s="6" t="s">
         <v>17</v>
@@ -56256,15 +56241,15 @@
         <v>6417</v>
       </c>
       <c r="K1348" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1349" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1349" s="31" t="s">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B1349" s="6" t="s">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="C1349" s="6" t="s">
         <v>17</v>
@@ -56292,15 +56277,15 @@
         <v>6417</v>
       </c>
       <c r="K1349" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1350" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1350" s="31" t="s">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B1350" s="6" t="s">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="C1350" s="6" t="s">
         <v>17</v>
@@ -56328,15 +56313,15 @@
         <v>6417</v>
       </c>
       <c r="K1350" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1351" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1351" s="31" t="s">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B1351" s="6" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="C1351" s="6" t="s">
         <v>17</v>
@@ -56364,12 +56349,12 @@
         <v>6417</v>
       </c>
       <c r="K1351" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1352" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1352" s="31" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="B1352" s="6" t="s">
         <v>836</v>
@@ -56400,15 +56385,15 @@
         <v>6417</v>
       </c>
       <c r="K1352" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1353" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1353" s="31" t="s">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B1353" s="6" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="C1353" s="6" t="s">
         <v>17</v>
@@ -56436,15 +56421,15 @@
         <v>6417</v>
       </c>
       <c r="K1353" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1354" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1354" s="31" t="s">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B1354" s="6" t="s">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="C1354" s="6" t="s">
         <v>17</v>
@@ -56472,7 +56457,7 @@
         <v>6417</v>
       </c>
       <c r="K1354" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1355" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56480,7 +56465,7 @@
         <v>1463</v>
       </c>
       <c r="B1355" s="6" t="s">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="C1355" s="6" t="s">
         <v>17</v>
@@ -56508,7 +56493,7 @@
         <v>6417</v>
       </c>
       <c r="K1355" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1356" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56516,7 +56501,7 @@
         <v>853</v>
       </c>
       <c r="B1356" s="6" t="s">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="C1356" s="6" t="s">
         <v>17</v>
@@ -56544,7 +56529,7 @@
         <v>6417</v>
       </c>
       <c r="K1356" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1357" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56552,7 +56537,7 @@
         <v>13101019</v>
       </c>
       <c r="B1357" s="18" t="s">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="C1357" s="18" t="s">
         <v>17</v>
@@ -56580,7 +56565,7 @@
         <v>6417</v>
       </c>
       <c r="K1357" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1358" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56588,7 +56573,7 @@
         <v>819</v>
       </c>
       <c r="B1358" s="6" t="s">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="C1358" s="6" t="s">
         <v>17</v>
@@ -56616,7 +56601,7 @@
         <v>6418</v>
       </c>
       <c r="K1358" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1359" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56624,7 +56609,7 @@
         <v>809</v>
       </c>
       <c r="B1359" s="6" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="C1359" s="6" t="s">
         <v>17</v>
@@ -56652,15 +56637,15 @@
         <v>6418</v>
       </c>
       <c r="K1359" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1360" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1360" s="31" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B1360" s="6" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="C1360" s="6" t="s">
         <v>17</v>
@@ -56688,15 +56673,15 @@
         <v>6418</v>
       </c>
       <c r="K1360" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1361" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1361" s="31" t="s">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="B1361" s="6" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="C1361" s="6" t="s">
         <v>17</v>
@@ -56724,15 +56709,15 @@
         <v>6418</v>
       </c>
       <c r="K1361" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1362" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1362" s="31" t="s">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="B1362" s="6" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="C1362" s="6" t="s">
         <v>17</v>
@@ -56760,15 +56745,15 @@
         <v>6418</v>
       </c>
       <c r="K1362" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1363" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1363" s="31" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="B1363" s="6" t="s">
-        <v>2056</v>
+        <v>2051</v>
       </c>
       <c r="C1363" s="6" t="s">
         <v>17</v>
@@ -56796,15 +56781,15 @@
         <v>6418</v>
       </c>
       <c r="K1363" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1364" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1364" s="31" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="B1364" s="6" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="C1364" s="6" t="s">
         <v>17</v>
@@ -56832,15 +56817,15 @@
         <v>6418</v>
       </c>
       <c r="K1364" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1365" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1365" s="31" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="B1365" s="6" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="C1365" s="6" t="s">
         <v>17</v>
@@ -56868,15 +56853,15 @@
         <v>6418</v>
       </c>
       <c r="K1365" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1366" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1366" s="31" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="B1366" s="6" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="C1366" s="6" t="s">
         <v>17</v>
@@ -56904,7 +56889,7 @@
         <v>6418</v>
       </c>
       <c r="K1366" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1367" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56940,13 +56925,13 @@
         <v>6418</v>
       </c>
       <c r="K1367" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1368" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1368" s="42"/>
       <c r="B1368" s="18" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="C1368" s="18" t="s">
         <v>348</v>
@@ -56974,7 +56959,7 @@
         <v>6418</v>
       </c>
       <c r="K1368" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1369" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -56982,7 +56967,7 @@
         <v>815</v>
       </c>
       <c r="B1369" s="6" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="C1369" s="6" t="s">
         <v>17</v>
@@ -57010,7 +56995,7 @@
         <v>6419</v>
       </c>
       <c r="K1369" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1370" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57018,7 +57003,7 @@
         <v>13101032</v>
       </c>
       <c r="B1370" s="18" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="C1370" s="18" t="s">
         <v>17</v>
@@ -57046,15 +57031,15 @@
         <v>6419</v>
       </c>
       <c r="K1370" s="21" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1371" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1371" s="31" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="B1371" s="6" t="s">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="C1371" s="6" t="s">
         <v>17</v>
@@ -57082,15 +57067,15 @@
         <v>6419</v>
       </c>
       <c r="K1371" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1372" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1372" s="31" t="s">
-        <v>2068</v>
+        <v>2063</v>
       </c>
       <c r="B1372" s="6" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="C1372" s="6" t="s">
         <v>707</v>
@@ -57118,15 +57103,15 @@
         <v>6419</v>
       </c>
       <c r="K1372" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1373" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1373" s="31" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
       <c r="B1373" s="6" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="C1373" s="6" t="s">
         <v>348</v>
@@ -57154,7 +57139,7 @@
         <v>6419</v>
       </c>
       <c r="K1373" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1374" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57162,7 +57147,7 @@
         <v>515</v>
       </c>
       <c r="B1374" s="6" t="s">
-        <v>1960</v>
+        <v>1955</v>
       </c>
       <c r="C1374" s="6" t="s">
         <v>17</v>
@@ -57190,7 +57175,7 @@
         <v>6420</v>
       </c>
       <c r="K1374" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1375" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57198,7 +57183,7 @@
         <v>518</v>
       </c>
       <c r="B1375" s="6" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="C1375" s="6" t="s">
         <v>17</v>
@@ -57226,7 +57211,7 @@
         <v>6420</v>
       </c>
       <c r="K1375" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1376" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57234,7 +57219,7 @@
         <v>520</v>
       </c>
       <c r="B1376" s="6" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="C1376" s="6" t="s">
         <v>17</v>
@@ -57262,7 +57247,7 @@
         <v>6420</v>
       </c>
       <c r="K1376" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1377" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57298,7 +57283,7 @@
         <v>6421</v>
       </c>
       <c r="K1377" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1378" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57334,7 +57319,7 @@
         <v>6421</v>
       </c>
       <c r="K1378" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1379" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57342,7 +57327,7 @@
         <v>454</v>
       </c>
       <c r="B1379" s="6" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="C1379" s="6" t="s">
         <v>17</v>
@@ -57370,7 +57355,7 @@
         <v>6421</v>
       </c>
       <c r="K1379" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1380" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57378,7 +57363,7 @@
         <v>1309</v>
       </c>
       <c r="B1380" s="6" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="C1380" s="6" t="s">
         <v>17</v>
@@ -57406,7 +57391,7 @@
         <v>6421</v>
       </c>
       <c r="K1380" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1381" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57414,7 +57399,7 @@
         <v>1307</v>
       </c>
       <c r="B1381" s="6" t="s">
-        <v>2076</v>
+        <v>2071</v>
       </c>
       <c r="C1381" s="6" t="s">
         <v>17</v>
@@ -57442,7 +57427,7 @@
         <v>6421</v>
       </c>
       <c r="K1381" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1382" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57478,7 +57463,7 @@
         <v>6421</v>
       </c>
       <c r="K1382" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1383" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57486,7 +57471,7 @@
         <v>914</v>
       </c>
       <c r="B1383" s="6" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
       <c r="C1383" s="6" t="s">
         <v>17</v>
@@ -57514,7 +57499,7 @@
         <v>6422</v>
       </c>
       <c r="K1383" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1384" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57522,7 +57507,7 @@
         <v>1071</v>
       </c>
       <c r="B1384" s="6" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C1384" s="6" t="s">
         <v>17</v>
@@ -57550,7 +57535,7 @@
         <v>6423</v>
       </c>
       <c r="K1384" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1385" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57586,7 +57571,7 @@
         <v>6423</v>
       </c>
       <c r="K1385" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1386" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57594,7 +57579,7 @@
         <v>1307</v>
       </c>
       <c r="B1386" s="6" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
       <c r="C1386" s="6" t="s">
         <v>17</v>
@@ -57622,15 +57607,15 @@
         <v>6423</v>
       </c>
       <c r="K1386" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1387" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1387" s="31" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="B1387" s="6" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="C1387" s="6" t="s">
         <v>17</v>
@@ -57658,15 +57643,15 @@
         <v>6423</v>
       </c>
       <c r="K1387" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1388" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1388" s="32" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
       <c r="B1388" s="6" t="s">
-        <v>2083</v>
+        <v>2078</v>
       </c>
       <c r="C1388" s="6" t="s">
         <v>17</v>
@@ -57694,13 +57679,13 @@
         <v>6423</v>
       </c>
       <c r="K1388" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1389" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1389" s="42"/>
       <c r="B1389" s="18" t="s">
-        <v>2084</v>
+        <v>2079</v>
       </c>
       <c r="C1389" s="18" t="s">
         <v>17</v>
@@ -57728,13 +57713,13 @@
         <v>6424</v>
       </c>
       <c r="K1389" s="21" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1390" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1390" s="42"/>
       <c r="B1390" s="18" t="s">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="C1390" s="18" t="s">
         <v>17</v>
@@ -57762,13 +57747,13 @@
         <v>6424</v>
       </c>
       <c r="K1390" s="21" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1391" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1391" s="42"/>
       <c r="B1391" s="18" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="C1391" s="18" t="s">
         <v>17</v>
@@ -57796,7 +57781,7 @@
         <v>6424</v>
       </c>
       <c r="K1391" s="21" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1392" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57832,15 +57817,15 @@
         <v>6424</v>
       </c>
       <c r="K1392" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1393" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1393" s="31" t="s">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="B1393" s="6" t="s">
-        <v>2088</v>
+        <v>2083</v>
       </c>
       <c r="C1393" s="6" t="s">
         <v>17</v>
@@ -57868,15 +57853,15 @@
         <v>6425</v>
       </c>
       <c r="K1393" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1394" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1394" s="31" t="s">
-        <v>2089</v>
+        <v>2084</v>
       </c>
       <c r="B1394" s="6" t="s">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="C1394" s="6" t="s">
         <v>17</v>
@@ -57904,7 +57889,7 @@
         <v>6425</v>
       </c>
       <c r="K1394" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1395" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -57912,7 +57897,7 @@
         <v>1673</v>
       </c>
       <c r="B1395" s="6" t="s">
-        <v>2091</v>
+        <v>2086</v>
       </c>
       <c r="C1395" s="6" t="s">
         <v>17</v>
@@ -57940,15 +57925,15 @@
         <v>6425</v>
       </c>
       <c r="K1395" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1396" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1396" s="31" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
       <c r="B1396" s="6" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
       <c r="C1396" s="6" t="s">
         <v>17</v>
@@ -57976,13 +57961,13 @@
         <v>6425</v>
       </c>
       <c r="K1396" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1397" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1397" s="42"/>
       <c r="B1397" s="18" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="C1397" s="18" t="s">
         <v>40</v>
@@ -58010,15 +57995,15 @@
         <v>6426</v>
       </c>
       <c r="K1397" s="21" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1398" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1398" s="31" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
       <c r="B1398" s="6" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="C1398" s="6" t="s">
         <v>17</v>
@@ -58046,15 +58031,15 @@
         <v>6426</v>
       </c>
       <c r="K1398" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1399" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1399" s="31" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
       <c r="B1399" s="6" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
       <c r="C1399" s="6" t="s">
         <v>17</v>
@@ -58076,21 +58061,21 @@
         <v>46209</v>
       </c>
       <c r="I1399" s="6" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="J1399" s="6">
         <v>6427</v>
       </c>
       <c r="K1399" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1400" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1400" s="31" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
       <c r="B1400" s="6" t="s">
-        <v>2100</v>
+        <v>2095</v>
       </c>
       <c r="C1400" s="6" t="s">
         <v>17</v>
@@ -58118,15 +58103,15 @@
         <v>6428</v>
       </c>
       <c r="K1400" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1401" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1401" s="31" t="s">
-        <v>2101</v>
+        <v>2096</v>
       </c>
       <c r="B1401" s="6" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="C1401" s="6" t="s">
         <v>17</v>
@@ -58148,21 +58133,21 @@
         <v>46240</v>
       </c>
       <c r="I1401" s="6" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="J1401" s="6">
         <v>6429</v>
       </c>
       <c r="K1401" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1402" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1402" s="31" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
       <c r="B1402" s="6" t="s">
-        <v>2105</v>
+        <v>2100</v>
       </c>
       <c r="C1402" s="6" t="s">
         <v>17</v>
@@ -58184,13 +58169,13 @@
         <v>46240</v>
       </c>
       <c r="I1402" s="6" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="J1402" s="6">
         <v>6429</v>
       </c>
       <c r="K1402" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1403" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58198,7 +58183,7 @@
         <v>470</v>
       </c>
       <c r="B1403" s="6" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="C1403" s="6" t="s">
         <v>348</v>
@@ -58220,21 +58205,21 @@
         <v>46240</v>
       </c>
       <c r="I1403" s="6" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="J1403" s="6">
         <v>6429</v>
       </c>
       <c r="K1403" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1404" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1404" s="32" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="B1404" s="6" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
       <c r="C1404" s="6" t="s">
         <v>17</v>
@@ -58262,7 +58247,7 @@
         <v>6430</v>
       </c>
       <c r="K1404" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1405" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58270,7 +58255,7 @@
         <v>330</v>
       </c>
       <c r="B1405" s="6" t="s">
-        <v>2109</v>
+        <v>2104</v>
       </c>
       <c r="C1405" s="6" t="s">
         <v>40</v>
@@ -58298,15 +58283,15 @@
         <v>6431</v>
       </c>
       <c r="K1405" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1406" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1406" s="31" t="s">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="B1406" s="6" t="s">
-        <v>2111</v>
+        <v>2106</v>
       </c>
       <c r="C1406" s="6" t="s">
         <v>17</v>
@@ -58334,15 +58319,15 @@
         <v>6431</v>
       </c>
       <c r="K1406" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1407" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1407" s="31" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="B1407" s="6" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
       <c r="C1407" s="6" t="s">
         <v>17</v>
@@ -58370,15 +58355,15 @@
         <v>6431</v>
       </c>
       <c r="K1407" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1408" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1408" s="31" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
       <c r="B1408" s="6" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="C1408" s="6" t="s">
         <v>17</v>
@@ -58406,15 +58391,15 @@
         <v>6431</v>
       </c>
       <c r="K1408" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1409" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1409" s="31" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
       <c r="B1409" s="6" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
       <c r="C1409" s="6" t="s">
         <v>17</v>
@@ -58442,7 +58427,7 @@
         <v>6431</v>
       </c>
       <c r="K1409" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1410" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58450,7 +58435,7 @@
         <v>253</v>
       </c>
       <c r="B1410" s="6" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="C1410" s="6" t="s">
         <v>17</v>
@@ -58478,7 +58463,7 @@
         <v>6431</v>
       </c>
       <c r="K1410" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1411" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58486,7 +58471,7 @@
         <v>254</v>
       </c>
       <c r="B1411" s="6" t="s">
-        <v>2119</v>
+        <v>2114</v>
       </c>
       <c r="C1411" s="6" t="s">
         <v>17</v>
@@ -58514,7 +58499,7 @@
         <v>6431</v>
       </c>
       <c r="K1411" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1412" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58522,7 +58507,7 @@
         <v>495</v>
       </c>
       <c r="B1412" s="6" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
       <c r="C1412" s="6" t="s">
         <v>17</v>
@@ -58550,15 +58535,15 @@
         <v>6431</v>
       </c>
       <c r="K1412" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1413" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1413" s="31" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="B1413" s="6" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
       <c r="C1413" s="6" t="s">
         <v>17</v>
@@ -58586,15 +58571,15 @@
         <v>6431</v>
       </c>
       <c r="K1413" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1414" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1414" s="31" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
       <c r="B1414" s="6" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
       <c r="C1414" s="6" t="s">
         <v>17</v>
@@ -58622,7 +58607,7 @@
         <v>6432</v>
       </c>
       <c r="K1414" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1415" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58630,7 +58615,7 @@
         <v>983</v>
       </c>
       <c r="B1415" s="6" t="s">
-        <v>2125</v>
+        <v>2120</v>
       </c>
       <c r="C1415" s="6" t="s">
         <v>17</v>
@@ -58649,7 +58634,7 @@
         <v>718</v>
       </c>
       <c r="H1415" s="12" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="I1415" s="6" t="s">
         <v>37</v>
@@ -58658,15 +58643,15 @@
         <v>6433</v>
       </c>
       <c r="K1415" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1416" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1416" s="31" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="B1416" s="6" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="C1416" s="6" t="s">
         <v>17</v>
@@ -58685,7 +58670,7 @@
         <v>34472</v>
       </c>
       <c r="H1416" s="12" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="I1416" s="6" t="s">
         <v>121</v>
@@ -58694,7 +58679,7 @@
         <v>6434</v>
       </c>
       <c r="K1416" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1417" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58702,7 +58687,7 @@
         <v>1631</v>
       </c>
       <c r="B1417" s="6" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
       <c r="C1417" s="6" t="s">
         <v>17</v>
@@ -58721,7 +58706,7 @@
         <v>34472</v>
       </c>
       <c r="H1417" s="12" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="I1417" s="6" t="s">
         <v>121</v>
@@ -58730,15 +58715,15 @@
         <v>6434</v>
       </c>
       <c r="K1417" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1418" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1418" s="31" t="s">
-        <v>2129</v>
+        <v>2124</v>
       </c>
       <c r="B1418" s="6" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="C1418" s="6" t="s">
         <v>40</v>
@@ -58757,7 +58742,7 @@
         <v>717</v>
       </c>
       <c r="H1418" s="12" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="I1418" s="6" t="s">
         <v>37</v>
@@ -58766,7 +58751,7 @@
         <v>6435</v>
       </c>
       <c r="K1418" s="12" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1419" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58774,7 +58759,7 @@
         <v>515</v>
       </c>
       <c r="B1419" s="6" t="s">
-        <v>1960</v>
+        <v>1955</v>
       </c>
       <c r="C1419" s="6" t="s">
         <v>17</v>
@@ -58793,7 +58778,7 @@
         <v>10609</v>
       </c>
       <c r="H1419" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1419" s="6" t="s">
         <v>517</v>
@@ -58802,7 +58787,7 @@
         <v>6436</v>
       </c>
       <c r="K1419" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1420" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58810,7 +58795,7 @@
         <v>518</v>
       </c>
       <c r="B1420" s="6" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="C1420" s="6" t="s">
         <v>17</v>
@@ -58829,7 +58814,7 @@
         <v>10609</v>
       </c>
       <c r="H1420" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1420" s="6" t="s">
         <v>517</v>
@@ -58838,7 +58823,7 @@
         <v>6436</v>
       </c>
       <c r="K1420" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1421" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58846,7 +58831,7 @@
         <v>520</v>
       </c>
       <c r="B1421" s="6" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="C1421" s="6" t="s">
         <v>17</v>
@@ -58865,7 +58850,7 @@
         <v>10609</v>
       </c>
       <c r="H1421" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1421" s="6" t="s">
         <v>517</v>
@@ -58874,7 +58859,7 @@
         <v>6436</v>
       </c>
       <c r="K1421" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1422" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58901,7 +58886,7 @@
         <v>13910</v>
       </c>
       <c r="H1422" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1422" s="6" t="s">
         <v>116</v>
@@ -58910,7 +58895,7 @@
         <v>6437</v>
       </c>
       <c r="K1422" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1423" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58937,7 +58922,7 @@
         <v>13910</v>
       </c>
       <c r="H1423" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1423" s="6" t="s">
         <v>116</v>
@@ -58946,7 +58931,7 @@
         <v>6437</v>
       </c>
       <c r="K1423" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1424" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58973,7 +58958,7 @@
         <v>13910</v>
       </c>
       <c r="H1424" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1424" s="6" t="s">
         <v>116</v>
@@ -58982,7 +58967,7 @@
         <v>6437</v>
       </c>
       <c r="K1424" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1425" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -58990,7 +58975,7 @@
         <v>1030</v>
       </c>
       <c r="B1425" s="6" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="C1425" s="6" t="s">
         <v>17</v>
@@ -59009,7 +58994,7 @@
         <v>13910</v>
       </c>
       <c r="H1425" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1425" s="6" t="s">
         <v>116</v>
@@ -59018,15 +59003,15 @@
         <v>6437</v>
       </c>
       <c r="K1425" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1426" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1426" s="31" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
       <c r="B1426" s="6" t="s">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="C1426" s="6" t="s">
         <v>17</v>
@@ -59045,7 +59030,7 @@
         <v>13902</v>
       </c>
       <c r="H1426" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1426" s="6" t="s">
         <v>116</v>
@@ -59054,15 +59039,15 @@
         <v>6438</v>
       </c>
       <c r="K1426" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1427" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1427" s="31" t="s">
-        <v>2135</v>
+        <v>2130</v>
       </c>
       <c r="B1427" s="6" t="s">
-        <v>2136</v>
+        <v>2131</v>
       </c>
       <c r="C1427" s="6" t="s">
         <v>17</v>
@@ -59081,7 +59066,7 @@
         <v>13902</v>
       </c>
       <c r="H1427" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1427" s="6" t="s">
         <v>116</v>
@@ -59090,15 +59075,15 @@
         <v>6438</v>
       </c>
       <c r="K1427" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1428" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1428" s="31" t="s">
-        <v>2137</v>
+        <v>2132</v>
       </c>
       <c r="B1428" s="6" t="s">
-        <v>2138</v>
+        <v>2133</v>
       </c>
       <c r="C1428" s="6" t="s">
         <v>17</v>
@@ -59117,7 +59102,7 @@
         <v>13902</v>
       </c>
       <c r="H1428" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1428" s="6" t="s">
         <v>116</v>
@@ -59126,15 +59111,15 @@
         <v>6438</v>
       </c>
       <c r="K1428" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1429" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1429" s="31" t="s">
-        <v>2139</v>
+        <v>2134</v>
       </c>
       <c r="B1429" s="6" t="s">
-        <v>2140</v>
+        <v>2135</v>
       </c>
       <c r="C1429" s="6" t="s">
         <v>17</v>
@@ -59153,7 +59138,7 @@
         <v>13902</v>
       </c>
       <c r="H1429" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1429" s="6" t="s">
         <v>116</v>
@@ -59162,15 +59147,15 @@
         <v>6438</v>
       </c>
       <c r="K1429" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1430" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1430" s="31" t="s">
-        <v>2141</v>
+        <v>2136</v>
       </c>
       <c r="B1430" s="6" t="s">
-        <v>2142</v>
+        <v>2137</v>
       </c>
       <c r="C1430" s="6" t="s">
         <v>17</v>
@@ -59189,7 +59174,7 @@
         <v>13902</v>
       </c>
       <c r="H1430" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1430" s="6" t="s">
         <v>116</v>
@@ -59198,15 +59183,15 @@
         <v>6438</v>
       </c>
       <c r="K1430" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1431" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1431" s="31" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="B1431" s="6" t="s">
-        <v>2143</v>
+        <v>2138</v>
       </c>
       <c r="C1431" s="6" t="s">
         <v>17</v>
@@ -59225,7 +59210,7 @@
         <v>13902</v>
       </c>
       <c r="H1431" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1431" s="6" t="s">
         <v>116</v>
@@ -59234,15 +59219,15 @@
         <v>6438</v>
       </c>
       <c r="K1431" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1432" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1432" s="31" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
       <c r="B1432" s="6" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="C1432" s="6" t="s">
         <v>17</v>
@@ -59261,7 +59246,7 @@
         <v>13902</v>
       </c>
       <c r="H1432" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1432" s="6" t="s">
         <v>116</v>
@@ -59270,7 +59255,7 @@
         <v>6438</v>
       </c>
       <c r="K1432" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1433" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59297,7 +59282,7 @@
         <v>13902</v>
       </c>
       <c r="H1433" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1433" s="6" t="s">
         <v>116</v>
@@ -59306,15 +59291,15 @@
         <v>6438</v>
       </c>
       <c r="K1433" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1434" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1434" s="31" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="B1434" s="17" t="s">
-        <v>2147</v>
+        <v>2142</v>
       </c>
       <c r="C1434" s="6" t="s">
         <v>17</v>
@@ -59333,7 +59318,7 @@
         <v>13902</v>
       </c>
       <c r="H1434" s="12" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="I1434" s="6" t="s">
         <v>116</v>
@@ -59342,7 +59327,7 @@
         <v>6438</v>
       </c>
       <c r="K1434" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1435" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59350,7 +59335,7 @@
         <v>289</v>
       </c>
       <c r="B1435" s="6" t="s">
-        <v>2148</v>
+        <v>2143</v>
       </c>
       <c r="C1435" s="6" t="s">
         <v>17</v>
@@ -59369,7 +59354,7 @@
         <v>2474</v>
       </c>
       <c r="H1435" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1435" s="6" t="s">
         <v>799</v>
@@ -59378,15 +59363,15 @@
         <v>6439</v>
       </c>
       <c r="K1435" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1436" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1436" s="32" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="B1436" s="6" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
       <c r="C1436" s="6" t="s">
         <v>17</v>
@@ -59405,7 +59390,7 @@
         <v>2474</v>
       </c>
       <c r="H1436" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1436" s="6" t="s">
         <v>799</v>
@@ -59414,15 +59399,15 @@
         <v>6439</v>
       </c>
       <c r="K1436" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1437" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1437" s="32" t="s">
-        <v>2152</v>
+        <v>2147</v>
       </c>
       <c r="B1437" s="6" t="s">
-        <v>2153</v>
+        <v>2148</v>
       </c>
       <c r="C1437" s="6" t="s">
         <v>17</v>
@@ -59441,7 +59426,7 @@
         <v>2474</v>
       </c>
       <c r="H1437" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1437" s="6" t="s">
         <v>799</v>
@@ -59450,7 +59435,7 @@
         <v>6439</v>
       </c>
       <c r="K1437" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1438" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59477,7 +59462,7 @@
         <v>2474</v>
       </c>
       <c r="H1438" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1438" s="6" t="s">
         <v>799</v>
@@ -59486,7 +59471,7 @@
         <v>6439</v>
       </c>
       <c r="K1438" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1439" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59494,7 +59479,7 @@
         <v>562</v>
       </c>
       <c r="B1439" s="6" t="s">
-        <v>1785</v>
+        <v>1780</v>
       </c>
       <c r="C1439" s="6" t="s">
         <v>17</v>
@@ -59513,7 +59498,7 @@
         <v>2474</v>
       </c>
       <c r="H1439" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1439" s="6" t="s">
         <v>799</v>
@@ -59522,7 +59507,7 @@
         <v>6439</v>
       </c>
       <c r="K1439" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1440" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59530,7 +59515,7 @@
         <v>641</v>
       </c>
       <c r="B1440" s="6" t="s">
-        <v>2154</v>
+        <v>2149</v>
       </c>
       <c r="C1440" s="6" t="s">
         <v>17</v>
@@ -59549,7 +59534,7 @@
         <v>2474</v>
       </c>
       <c r="H1440" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1440" s="6" t="s">
         <v>799</v>
@@ -59558,15 +59543,15 @@
         <v>6439</v>
       </c>
       <c r="K1440" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1441" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1441" s="32" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="B1441" s="6" t="s">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="C1441" s="6" t="s">
         <v>17</v>
@@ -59585,7 +59570,7 @@
         <v>2474</v>
       </c>
       <c r="H1441" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1441" s="6" t="s">
         <v>799</v>
@@ -59594,7 +59579,7 @@
         <v>6439</v>
       </c>
       <c r="K1441" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1442" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59621,7 +59606,7 @@
         <v>2474</v>
       </c>
       <c r="H1442" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1442" s="6" t="s">
         <v>799</v>
@@ -59630,7 +59615,7 @@
         <v>6439</v>
       </c>
       <c r="K1442" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1443" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59657,7 +59642,7 @@
         <v>2474</v>
       </c>
       <c r="H1443" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1443" s="6" t="s">
         <v>799</v>
@@ -59666,7 +59651,7 @@
         <v>6439</v>
       </c>
       <c r="K1443" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1444" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59693,7 +59678,7 @@
         <v>2474</v>
       </c>
       <c r="H1444" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1444" s="6" t="s">
         <v>799</v>
@@ -59702,7 +59687,7 @@
         <v>6439</v>
       </c>
       <c r="K1444" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1445" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59710,7 +59695,7 @@
         <v>301</v>
       </c>
       <c r="B1445" s="6" t="s">
-        <v>2156</v>
+        <v>2151</v>
       </c>
       <c r="C1445" s="6" t="s">
         <v>17</v>
@@ -59729,7 +59714,7 @@
         <v>2474</v>
       </c>
       <c r="H1445" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1445" s="6" t="s">
         <v>799</v>
@@ -59738,7 +59723,7 @@
         <v>6439</v>
       </c>
       <c r="K1445" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1446" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59746,7 +59731,7 @@
         <v>286</v>
       </c>
       <c r="B1446" s="6" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="C1446" s="6" t="s">
         <v>17</v>
@@ -59765,7 +59750,7 @@
         <v>2474</v>
       </c>
       <c r="H1446" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1446" s="6" t="s">
         <v>799</v>
@@ -59774,7 +59759,7 @@
         <v>6439</v>
       </c>
       <c r="K1446" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1447" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59801,7 +59786,7 @@
         <v>2474</v>
       </c>
       <c r="H1447" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1447" s="6" t="s">
         <v>799</v>
@@ -59810,7 +59795,7 @@
         <v>6440</v>
       </c>
       <c r="K1447" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1448" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59837,7 +59822,7 @@
         <v>2474</v>
       </c>
       <c r="H1448" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1448" s="6" t="s">
         <v>799</v>
@@ -59846,7 +59831,7 @@
         <v>6440</v>
       </c>
       <c r="K1448" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1449" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59873,7 +59858,7 @@
         <v>2474</v>
       </c>
       <c r="H1449" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1449" s="6" t="s">
         <v>799</v>
@@ -59882,7 +59867,7 @@
         <v>6440</v>
       </c>
       <c r="K1449" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1450" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -59890,7 +59875,7 @@
         <v>1565</v>
       </c>
       <c r="B1450" s="6" t="s">
-        <v>2157</v>
+        <v>2152</v>
       </c>
       <c r="C1450" s="6" t="s">
         <v>17</v>
@@ -59909,7 +59894,7 @@
         <v>2474</v>
       </c>
       <c r="H1450" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1450" s="6" t="s">
         <v>799</v>
@@ -59918,13 +59903,13 @@
         <v>6440</v>
       </c>
       <c r="K1450" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1451" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1451" s="42"/>
       <c r="B1451" s="18" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="C1451" s="18" t="s">
         <v>17</v>
@@ -59943,22 +59928,22 @@
         <v>133</v>
       </c>
       <c r="H1451" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1451" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1451" s="18">
         <v>6441</v>
       </c>
       <c r="K1451" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1452" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1452" s="42"/>
       <c r="B1452" s="18" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="C1452" s="18" t="s">
         <v>17</v>
@@ -59977,22 +59962,22 @@
         <v>133</v>
       </c>
       <c r="H1452" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1452" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1452" s="18">
         <v>6441</v>
       </c>
       <c r="K1452" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1453" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1453" s="42"/>
       <c r="B1453" s="18" t="s">
-        <v>2161</v>
+        <v>2156</v>
       </c>
       <c r="C1453" s="18" t="s">
         <v>17</v>
@@ -60011,22 +59996,22 @@
         <v>133</v>
       </c>
       <c r="H1453" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1453" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1453" s="18">
         <v>6441</v>
       </c>
       <c r="K1453" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1454" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1454" s="42"/>
       <c r="B1454" s="18" t="s">
-        <v>2162</v>
+        <v>2157</v>
       </c>
       <c r="C1454" s="18" t="s">
         <v>17</v>
@@ -60045,22 +60030,22 @@
         <v>133</v>
       </c>
       <c r="H1454" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1454" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1454" s="18">
         <v>6441</v>
       </c>
       <c r="K1454" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1455" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1455" s="42"/>
       <c r="B1455" s="18" t="s">
-        <v>2163</v>
+        <v>2158</v>
       </c>
       <c r="C1455" s="18" t="s">
         <v>17</v>
@@ -60079,22 +60064,22 @@
         <v>133</v>
       </c>
       <c r="H1455" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1455" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1455" s="18">
         <v>6441</v>
       </c>
       <c r="K1455" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1456" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1456" s="42"/>
       <c r="B1456" s="18" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="C1456" s="18" t="s">
         <v>17</v>
@@ -60113,22 +60098,22 @@
         <v>133</v>
       </c>
       <c r="H1456" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1456" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1456" s="18">
         <v>6441</v>
       </c>
       <c r="K1456" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1457" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1457" s="42"/>
       <c r="B1457" s="18" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
       <c r="C1457" s="18" t="s">
         <v>17</v>
@@ -60147,22 +60132,22 @@
         <v>133</v>
       </c>
       <c r="H1457" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1457" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1457" s="18">
         <v>6441</v>
       </c>
       <c r="K1457" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1458" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1458" s="42"/>
       <c r="B1458" s="18" t="s">
-        <v>2166</v>
+        <v>2161</v>
       </c>
       <c r="C1458" s="18" t="s">
         <v>17</v>
@@ -60181,22 +60166,22 @@
         <v>133</v>
       </c>
       <c r="H1458" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1458" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1458" s="18">
         <v>6441</v>
       </c>
       <c r="K1458" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1459" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1459" s="42"/>
       <c r="B1459" s="18" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="C1459" s="18" t="s">
         <v>17</v>
@@ -60215,16 +60200,16 @@
         <v>133</v>
       </c>
       <c r="H1459" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1459" s="18" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="J1459" s="18">
         <v>6441</v>
       </c>
       <c r="K1459" s="21" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1460" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60232,7 +60217,7 @@
         <v>687</v>
       </c>
       <c r="B1460" s="6" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="C1460" s="6" t="s">
         <v>17</v>
@@ -60260,15 +60245,15 @@
         <v>6442</v>
       </c>
       <c r="K1460" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1461" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1461" s="31" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="B1461" s="6" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
       <c r="C1461" s="6" t="s">
         <v>17</v>
@@ -60296,12 +60281,12 @@
         <v>6443</v>
       </c>
       <c r="K1461" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1462" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1462" s="31" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="B1462" s="6" t="s">
         <v>1135</v>
@@ -60332,15 +60317,15 @@
         <v>6443</v>
       </c>
       <c r="K1462" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1463" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1463" s="31" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="B1463" s="6" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
       <c r="C1463" s="6" t="s">
         <v>17</v>
@@ -60359,7 +60344,7 @@
         <v>129</v>
       </c>
       <c r="H1463" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1463" s="6" t="s">
         <v>346</v>
@@ -60368,15 +60353,15 @@
         <v>6444</v>
       </c>
       <c r="K1463" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1464" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1464" s="31" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="B1464" s="6" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="C1464" s="6" t="s">
         <v>17</v>
@@ -60395,7 +60380,7 @@
         <v>129</v>
       </c>
       <c r="H1464" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1464" s="6" t="s">
         <v>346</v>
@@ -60404,15 +60389,15 @@
         <v>6444</v>
       </c>
       <c r="K1464" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1465" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1465" s="31" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="B1465" s="6" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="C1465" s="6" t="s">
         <v>17</v>
@@ -60431,7 +60416,7 @@
         <v>129</v>
       </c>
       <c r="H1465" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1465" s="6" t="s">
         <v>346</v>
@@ -60440,15 +60425,15 @@
         <v>6444</v>
       </c>
       <c r="K1465" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1466" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1466" s="31" t="s">
-        <v>2178</v>
+        <v>2173</v>
       </c>
       <c r="B1466" s="6" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
       <c r="C1466" s="6" t="s">
         <v>17</v>
@@ -60467,7 +60452,7 @@
         <v>129</v>
       </c>
       <c r="H1466" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1466" s="6" t="s">
         <v>346</v>
@@ -60476,15 +60461,15 @@
         <v>6444</v>
       </c>
       <c r="K1466" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1467" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1467" s="31" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="B1467" s="6" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
       <c r="C1467" s="6" t="s">
         <v>17</v>
@@ -60503,7 +60488,7 @@
         <v>129</v>
       </c>
       <c r="H1467" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1467" s="6" t="s">
         <v>346</v>
@@ -60512,15 +60497,15 @@
         <v>6444</v>
       </c>
       <c r="K1467" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1468" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1468" s="31" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="B1468" s="6" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="C1468" s="6" t="s">
         <v>17</v>
@@ -60539,7 +60524,7 @@
         <v>129</v>
       </c>
       <c r="H1468" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1468" s="6" t="s">
         <v>346</v>
@@ -60548,15 +60533,15 @@
         <v>6444</v>
       </c>
       <c r="K1468" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1469" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1469" s="31" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="B1469" s="6" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
       <c r="C1469" s="6" t="s">
         <v>17</v>
@@ -60575,7 +60560,7 @@
         <v>129</v>
       </c>
       <c r="H1469" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1469" s="6" t="s">
         <v>346</v>
@@ -60584,15 +60569,15 @@
         <v>6444</v>
       </c>
       <c r="K1469" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1470" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1470" s="31" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
       <c r="B1470" s="6" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="C1470" s="6" t="s">
         <v>40</v>
@@ -60611,24 +60596,24 @@
         <v>5</v>
       </c>
       <c r="H1470" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1470" s="6" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="J1470" s="6">
         <v>6445</v>
       </c>
       <c r="K1470" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1471" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1471" s="31" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="B1471" s="6" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
       <c r="C1471" s="6" t="s">
         <v>40</v>
@@ -60647,24 +60632,24 @@
         <v>5</v>
       </c>
       <c r="H1471" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1471" s="6" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="J1471" s="6">
         <v>6445</v>
       </c>
       <c r="K1471" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1472" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1472" s="31" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="B1472" s="6" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="C1472" s="6" t="s">
         <v>40</v>
@@ -60683,24 +60668,24 @@
         <v>5</v>
       </c>
       <c r="H1472" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1472" s="6" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="J1472" s="6">
         <v>6445</v>
       </c>
       <c r="K1472" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1473" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1473" s="31" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
       <c r="B1473" s="6" t="s">
-        <v>2194</v>
+        <v>2189</v>
       </c>
       <c r="C1473" s="6" t="s">
         <v>40</v>
@@ -60719,16 +60704,16 @@
         <v>5</v>
       </c>
       <c r="H1473" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1473" s="6" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="J1473" s="6">
         <v>6445</v>
       </c>
       <c r="K1473" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1474" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60736,7 +60721,7 @@
         <v>205</v>
       </c>
       <c r="B1474" s="6" t="s">
-        <v>2195</v>
+        <v>2190</v>
       </c>
       <c r="C1474" s="6" t="s">
         <v>17</v>
@@ -60755,7 +60740,7 @@
         <v>131</v>
       </c>
       <c r="H1474" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1474" s="6" t="s">
         <v>346</v>
@@ -60764,15 +60749,15 @@
         <v>6446</v>
       </c>
       <c r="K1474" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1475" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1475" s="31" t="s">
-        <v>2196</v>
+        <v>2191</v>
       </c>
       <c r="B1475" s="6" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="C1475" s="6" t="s">
         <v>17</v>
@@ -60791,7 +60776,7 @@
         <v>131</v>
       </c>
       <c r="H1475" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1475" s="6" t="s">
         <v>346</v>
@@ -60800,15 +60785,15 @@
         <v>6446</v>
       </c>
       <c r="K1475" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1476" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1476" s="32" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="B1476" s="6" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
       <c r="C1476" s="6" t="s">
         <v>17</v>
@@ -60827,7 +60812,7 @@
         <v>131</v>
       </c>
       <c r="H1476" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1476" s="6" t="s">
         <v>346</v>
@@ -60836,7 +60821,7 @@
         <v>6446</v>
       </c>
       <c r="K1476" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1477" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60844,7 +60829,7 @@
         <v>233</v>
       </c>
       <c r="B1477" s="6" t="s">
-        <v>2200</v>
+        <v>2195</v>
       </c>
       <c r="C1477" s="6" t="s">
         <v>17</v>
@@ -60863,7 +60848,7 @@
         <v>131</v>
       </c>
       <c r="H1477" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1477" s="6" t="s">
         <v>346</v>
@@ -60872,7 +60857,7 @@
         <v>6446</v>
       </c>
       <c r="K1477" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1478" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -60880,7 +60865,7 @@
         <v>1370</v>
       </c>
       <c r="B1478" s="6" t="s">
-        <v>2201</v>
+        <v>2196</v>
       </c>
       <c r="C1478" s="6" t="s">
         <v>17</v>
@@ -60899,7 +60884,7 @@
         <v>131</v>
       </c>
       <c r="H1478" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1478" s="6" t="s">
         <v>346</v>
@@ -60908,15 +60893,15 @@
         <v>6446</v>
       </c>
       <c r="K1478" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1479" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1479" s="32" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="B1479" s="6" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="C1479" s="6" t="s">
         <v>17</v>
@@ -60935,7 +60920,7 @@
         <v>131</v>
       </c>
       <c r="H1479" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1479" s="6" t="s">
         <v>346</v>
@@ -60944,15 +60929,15 @@
         <v>6446</v>
       </c>
       <c r="K1479" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1480" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1480" s="33" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="B1480" s="6" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="C1480" s="6" t="s">
         <v>17</v>
@@ -60971,7 +60956,7 @@
         <v>131</v>
       </c>
       <c r="H1480" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1480" s="6" t="s">
         <v>346</v>
@@ -60980,15 +60965,15 @@
         <v>6446</v>
       </c>
       <c r="K1480" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1481" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1481" s="32" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
       <c r="B1481" s="6" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="C1481" s="6" t="s">
         <v>17</v>
@@ -61007,7 +60992,7 @@
         <v>131</v>
       </c>
       <c r="H1481" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1481" s="6" t="s">
         <v>346</v>
@@ -61016,7 +61001,7 @@
         <v>6446</v>
       </c>
       <c r="K1481" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1482" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61024,7 +61009,7 @@
         <v>333</v>
       </c>
       <c r="B1482" s="6" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="C1482" s="6" t="s">
         <v>17</v>
@@ -61043,7 +61028,7 @@
         <v>131</v>
       </c>
       <c r="H1482" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1482" s="6" t="s">
         <v>346</v>
@@ -61052,7 +61037,7 @@
         <v>6446</v>
       </c>
       <c r="K1482" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1483" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61060,7 +61045,7 @@
         <v>303</v>
       </c>
       <c r="B1483" s="6" t="s">
-        <v>1777</v>
+        <v>1772</v>
       </c>
       <c r="C1483" s="6" t="s">
         <v>17</v>
@@ -61079,7 +61064,7 @@
         <v>131</v>
       </c>
       <c r="H1483" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1483" s="6" t="s">
         <v>346</v>
@@ -61088,7 +61073,7 @@
         <v>6446</v>
       </c>
       <c r="K1483" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1484" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61115,7 +61100,7 @@
         <v>131</v>
       </c>
       <c r="H1484" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1484" s="6" t="s">
         <v>346</v>
@@ -61124,7 +61109,7 @@
         <v>6446</v>
       </c>
       <c r="K1484" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1485" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61151,7 +61136,7 @@
         <v>5070</v>
       </c>
       <c r="H1485" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1485" s="6" t="s">
         <v>66</v>
@@ -61160,7 +61145,7 @@
         <v>6447</v>
       </c>
       <c r="K1485" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1486" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61187,7 +61172,7 @@
         <v>5070</v>
       </c>
       <c r="H1486" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1486" s="6" t="s">
         <v>66</v>
@@ -61196,15 +61181,15 @@
         <v>6447</v>
       </c>
       <c r="K1486" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1487" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1487" s="31" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
       <c r="B1487" s="6" t="s">
-        <v>2209</v>
+        <v>2204</v>
       </c>
       <c r="C1487" s="6" t="s">
         <v>17</v>
@@ -61223,7 +61208,7 @@
         <v>5070</v>
       </c>
       <c r="H1487" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1487" s="6" t="s">
         <v>66</v>
@@ -61232,7 +61217,7 @@
         <v>6447</v>
       </c>
       <c r="K1487" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1488" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61259,7 +61244,7 @@
         <v>5070</v>
       </c>
       <c r="H1488" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1488" s="6" t="s">
         <v>66</v>
@@ -61268,7 +61253,7 @@
         <v>6447</v>
       </c>
       <c r="K1488" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1489" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61295,7 +61280,7 @@
         <v>5070</v>
       </c>
       <c r="H1489" s="12" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="I1489" s="6" t="s">
         <v>66</v>
@@ -61304,7 +61289,7 @@
         <v>6447</v>
       </c>
       <c r="K1489" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1490" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61312,7 +61297,7 @@
         <v>268</v>
       </c>
       <c r="B1490" s="6" t="s">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="C1490" s="6" t="s">
         <v>17</v>
@@ -61331,7 +61316,7 @@
         <v>135</v>
       </c>
       <c r="H1490" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1490" s="6" t="s">
         <v>346</v>
@@ -61340,15 +61325,15 @@
         <v>6448</v>
       </c>
       <c r="K1490" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1491" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1491" s="32" t="s">
-        <v>2211</v>
+        <v>2206</v>
       </c>
       <c r="B1491" s="6" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="C1491" s="6" t="s">
         <v>17</v>
@@ -61367,7 +61352,7 @@
         <v>135</v>
       </c>
       <c r="H1491" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1491" s="6" t="s">
         <v>346</v>
@@ -61376,15 +61361,15 @@
         <v>6448</v>
       </c>
       <c r="K1491" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1492" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1492" s="33" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
       <c r="B1492" s="6" t="s">
-        <v>2214</v>
+        <v>2209</v>
       </c>
       <c r="C1492" s="6" t="s">
         <v>17</v>
@@ -61403,7 +61388,7 @@
         <v>135</v>
       </c>
       <c r="H1492" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1492" s="6" t="s">
         <v>346</v>
@@ -61412,15 +61397,15 @@
         <v>6448</v>
       </c>
       <c r="K1492" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1493" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1493" s="32" t="s">
-        <v>2215</v>
+        <v>2210</v>
       </c>
       <c r="B1493" s="6" t="s">
-        <v>2216</v>
+        <v>2211</v>
       </c>
       <c r="C1493" s="6" t="s">
         <v>17</v>
@@ -61439,7 +61424,7 @@
         <v>135</v>
       </c>
       <c r="H1493" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1493" s="6" t="s">
         <v>346</v>
@@ -61448,15 +61433,15 @@
         <v>6448</v>
       </c>
       <c r="K1493" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1494" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1494" s="31" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="B1494" s="6" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
       <c r="C1494" s="6" t="s">
         <v>17</v>
@@ -61475,7 +61460,7 @@
         <v>135</v>
       </c>
       <c r="H1494" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1494" s="6" t="s">
         <v>346</v>
@@ -61484,15 +61469,15 @@
         <v>6448</v>
       </c>
       <c r="K1494" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1495" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1495" s="31" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="B1495" s="6" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
       <c r="C1495" s="6" t="s">
         <v>17</v>
@@ -61511,7 +61496,7 @@
         <v>135</v>
       </c>
       <c r="H1495" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1495" s="6" t="s">
         <v>346</v>
@@ -61520,15 +61505,15 @@
         <v>6448</v>
       </c>
       <c r="K1495" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1496" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1496" s="31" t="s">
-        <v>2221</v>
+        <v>2216</v>
       </c>
       <c r="B1496" s="6" t="s">
-        <v>2222</v>
+        <v>2217</v>
       </c>
       <c r="C1496" s="6" t="s">
         <v>17</v>
@@ -61547,7 +61532,7 @@
         <v>135</v>
       </c>
       <c r="H1496" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1496" s="6" t="s">
         <v>346</v>
@@ -61556,7 +61541,7 @@
         <v>6448</v>
       </c>
       <c r="K1496" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1497" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61583,7 +61568,7 @@
         <v>14285</v>
       </c>
       <c r="H1497" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1497" s="6" t="s">
         <v>116</v>
@@ -61592,15 +61577,15 @@
         <v>6449</v>
       </c>
       <c r="K1497" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1498" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1498" s="31" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="B1498" s="6" t="s">
-        <v>2223</v>
+        <v>2218</v>
       </c>
       <c r="C1498" s="6" t="s">
         <v>17</v>
@@ -61619,7 +61604,7 @@
         <v>14285</v>
       </c>
       <c r="H1498" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1498" s="6" t="s">
         <v>116</v>
@@ -61628,7 +61613,7 @@
         <v>6449</v>
       </c>
       <c r="K1498" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1499" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61636,7 +61621,7 @@
         <v>323</v>
       </c>
       <c r="B1499" s="6" t="s">
-        <v>2224</v>
+        <v>2219</v>
       </c>
       <c r="C1499" s="6" t="s">
         <v>17</v>
@@ -61655,7 +61640,7 @@
         <v>14285</v>
       </c>
       <c r="H1499" s="12" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I1499" s="6" t="s">
         <v>116</v>
@@ -61664,7 +61649,7 @@
         <v>6449</v>
       </c>
       <c r="K1499" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1500" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61691,7 +61676,7 @@
         <v>5103</v>
       </c>
       <c r="H1500" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1500" s="6" t="s">
         <v>66</v>
@@ -61700,15 +61685,15 @@
         <v>6450</v>
       </c>
       <c r="K1500" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1501" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1501" s="31" t="s">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="B1501" s="6" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="C1501" s="6" t="s">
         <v>17</v>
@@ -61727,7 +61712,7 @@
         <v>5103</v>
       </c>
       <c r="H1501" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1501" s="6" t="s">
         <v>66</v>
@@ -61736,15 +61721,15 @@
         <v>6450</v>
       </c>
       <c r="K1501" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1502" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1502" s="31" t="s">
-        <v>2227</v>
+        <v>2222</v>
       </c>
       <c r="B1502" s="6" t="s">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="C1502" s="6" t="s">
         <v>17</v>
@@ -61763,7 +61748,7 @@
         <v>5103</v>
       </c>
       <c r="H1502" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1502" s="6" t="s">
         <v>66</v>
@@ -61772,15 +61757,15 @@
         <v>6450</v>
       </c>
       <c r="K1502" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1503" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1503" s="31" t="s">
-        <v>2229</v>
+        <v>2224</v>
       </c>
       <c r="B1503" s="6" t="s">
-        <v>2230</v>
+        <v>2225</v>
       </c>
       <c r="C1503" s="6" t="s">
         <v>17</v>
@@ -61799,7 +61784,7 @@
         <v>5103</v>
       </c>
       <c r="H1503" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1503" s="6" t="s">
         <v>66</v>
@@ -61808,15 +61793,15 @@
         <v>6450</v>
       </c>
       <c r="K1503" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1504" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1504" s="31" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="B1504" s="6" t="s">
-        <v>2232</v>
+        <v>2227</v>
       </c>
       <c r="C1504" s="6" t="s">
         <v>17</v>
@@ -61835,7 +61820,7 @@
         <v>5103</v>
       </c>
       <c r="H1504" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1504" s="6" t="s">
         <v>66</v>
@@ -61844,7 +61829,7 @@
         <v>6450</v>
       </c>
       <c r="K1504" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1505" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61852,7 +61837,7 @@
         <v>338</v>
       </c>
       <c r="B1505" s="6" t="s">
-        <v>2233</v>
+        <v>2228</v>
       </c>
       <c r="C1505" s="6" t="s">
         <v>17</v>
@@ -61871,7 +61856,7 @@
         <v>5103</v>
       </c>
       <c r="H1505" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1505" s="6" t="s">
         <v>66</v>
@@ -61880,7 +61865,7 @@
         <v>6450</v>
       </c>
       <c r="K1505" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1506" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61888,7 +61873,7 @@
         <v>295</v>
       </c>
       <c r="B1506" s="6" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="C1506" s="6" t="s">
         <v>17</v>
@@ -61907,24 +61892,24 @@
         <v>13</v>
       </c>
       <c r="H1506" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1506" s="6" t="s">
-        <v>2235</v>
+        <v>2230</v>
       </c>
       <c r="J1506" s="6">
         <v>6451</v>
       </c>
       <c r="K1506" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1507" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1507" s="31" t="s">
-        <v>2236</v>
+        <v>2231</v>
       </c>
       <c r="B1507" s="6" t="s">
-        <v>2237</v>
+        <v>2232</v>
       </c>
       <c r="C1507" s="6" t="s">
         <v>17</v>
@@ -61943,7 +61928,7 @@
         <v>138</v>
       </c>
       <c r="H1507" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1507" s="6" t="s">
         <v>346</v>
@@ -61952,7 +61937,7 @@
         <v>6453</v>
       </c>
       <c r="K1507" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1508" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -61960,7 +61945,7 @@
         <v>1038</v>
       </c>
       <c r="B1508" s="6" t="s">
-        <v>2238</v>
+        <v>2233</v>
       </c>
       <c r="C1508" s="6" t="s">
         <v>40</v>
@@ -61979,7 +61964,7 @@
         <v>138</v>
       </c>
       <c r="H1508" s="12" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="I1508" s="6" t="s">
         <v>346</v>
@@ -61988,7 +61973,7 @@
         <v>6453</v>
       </c>
       <c r="K1508" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1509" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62015,7 +62000,7 @@
         <v>1504</v>
       </c>
       <c r="H1509" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1509" s="6" t="s">
         <v>1180</v>
@@ -62024,15 +62009,15 @@
         <v>6455</v>
       </c>
       <c r="K1509" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1510" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1510" s="32" t="s">
-        <v>2240</v>
+        <v>2235</v>
       </c>
       <c r="B1510" s="6" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="C1510" s="6" t="s">
         <v>17</v>
@@ -62051,7 +62036,7 @@
         <v>1504</v>
       </c>
       <c r="H1510" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1510" s="6" t="s">
         <v>1180</v>
@@ -62060,15 +62045,15 @@
         <v>6455</v>
       </c>
       <c r="K1510" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1511" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1511" s="32" t="s">
-        <v>2242</v>
+        <v>2237</v>
       </c>
       <c r="B1511" s="6" t="s">
-        <v>2243</v>
+        <v>2238</v>
       </c>
       <c r="C1511" s="6" t="s">
         <v>17</v>
@@ -62087,7 +62072,7 @@
         <v>1504</v>
       </c>
       <c r="H1511" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1511" s="6" t="s">
         <v>1180</v>
@@ -62096,15 +62081,15 @@
         <v>6455</v>
       </c>
       <c r="K1511" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1512" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1512" s="32" t="s">
-        <v>2244</v>
+        <v>2239</v>
       </c>
       <c r="B1512" s="6" t="s">
-        <v>2245</v>
+        <v>2240</v>
       </c>
       <c r="C1512" s="6" t="s">
         <v>17</v>
@@ -62123,7 +62108,7 @@
         <v>1504</v>
       </c>
       <c r="H1512" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1512" s="6" t="s">
         <v>1180</v>
@@ -62132,7 +62117,7 @@
         <v>6455</v>
       </c>
       <c r="K1512" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1513" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62159,7 +62144,7 @@
         <v>1504</v>
       </c>
       <c r="H1513" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1513" s="6" t="s">
         <v>1180</v>
@@ -62168,7 +62153,7 @@
         <v>6455</v>
       </c>
       <c r="K1513" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1514" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62176,7 +62161,7 @@
         <v>1203</v>
       </c>
       <c r="B1514" s="6" t="s">
-        <v>2246</v>
+        <v>2241</v>
       </c>
       <c r="C1514" s="6" t="s">
         <v>17</v>
@@ -62195,7 +62180,7 @@
         <v>1504</v>
       </c>
       <c r="H1514" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1514" s="6" t="s">
         <v>1180</v>
@@ -62204,7 +62189,7 @@
         <v>6455</v>
       </c>
       <c r="K1514" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1515" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62212,7 +62197,7 @@
         <v>1210</v>
       </c>
       <c r="B1515" s="6" t="s">
-        <v>2247</v>
+        <v>2242</v>
       </c>
       <c r="C1515" s="6" t="s">
         <v>17</v>
@@ -62231,7 +62216,7 @@
         <v>1504</v>
       </c>
       <c r="H1515" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1515" s="6" t="s">
         <v>1180</v>
@@ -62240,7 +62225,7 @@
         <v>6455</v>
       </c>
       <c r="K1515" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1516" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62248,7 +62233,7 @@
         <v>1648</v>
       </c>
       <c r="B1516" s="6" t="s">
-        <v>2248</v>
+        <v>2243</v>
       </c>
       <c r="C1516" s="6" t="s">
         <v>17</v>
@@ -62267,7 +62252,7 @@
         <v>1504</v>
       </c>
       <c r="H1516" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1516" s="6" t="s">
         <v>1180</v>
@@ -62276,7 +62261,7 @@
         <v>6455</v>
       </c>
       <c r="K1516" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1517" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62284,7 +62269,7 @@
         <v>1268</v>
       </c>
       <c r="B1517" s="6" t="s">
-        <v>2249</v>
+        <v>2244</v>
       </c>
       <c r="C1517" s="6" t="s">
         <v>17</v>
@@ -62303,7 +62288,7 @@
         <v>1504</v>
       </c>
       <c r="H1517" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1517" s="6" t="s">
         <v>1180</v>
@@ -62312,15 +62297,15 @@
         <v>6455</v>
       </c>
       <c r="K1517" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1518" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1518" s="32" t="s">
-        <v>2250</v>
+        <v>2245</v>
       </c>
       <c r="B1518" s="6" t="s">
-        <v>2251</v>
+        <v>2246</v>
       </c>
       <c r="C1518" s="6" t="s">
         <v>17</v>
@@ -62339,7 +62324,7 @@
         <v>1504</v>
       </c>
       <c r="H1518" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1518" s="6" t="s">
         <v>1180</v>
@@ -62348,7 +62333,7 @@
         <v>6455</v>
       </c>
       <c r="K1518" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1519" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62356,7 +62341,7 @@
         <v>1272</v>
       </c>
       <c r="B1519" s="6" t="s">
-        <v>2252</v>
+        <v>2247</v>
       </c>
       <c r="C1519" s="6" t="s">
         <v>17</v>
@@ -62375,7 +62360,7 @@
         <v>1504</v>
       </c>
       <c r="H1519" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1519" s="6" t="s">
         <v>1180</v>
@@ -62384,15 +62369,15 @@
         <v>6455</v>
       </c>
       <c r="K1519" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1520" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1520" s="32" t="s">
-        <v>2253</v>
+        <v>2248</v>
       </c>
       <c r="B1520" s="6" t="s">
-        <v>2254</v>
+        <v>2249</v>
       </c>
       <c r="C1520" s="6" t="s">
         <v>17</v>
@@ -62411,7 +62396,7 @@
         <v>1504</v>
       </c>
       <c r="H1520" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1520" s="6" t="s">
         <v>1180</v>
@@ -62420,15 +62405,15 @@
         <v>6455</v>
       </c>
       <c r="K1520" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1521" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1521" s="32" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="B1521" s="6" t="s">
-        <v>2256</v>
+        <v>2251</v>
       </c>
       <c r="C1521" s="6" t="s">
         <v>17</v>
@@ -62447,7 +62432,7 @@
         <v>1504</v>
       </c>
       <c r="H1521" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1521" s="6" t="s">
         <v>1180</v>
@@ -62456,7 +62441,7 @@
         <v>6456</v>
       </c>
       <c r="K1521" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1522" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62483,7 +62468,7 @@
         <v>1504</v>
       </c>
       <c r="H1522" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1522" s="6" t="s">
         <v>1180</v>
@@ -62492,7 +62477,7 @@
         <v>6456</v>
       </c>
       <c r="K1522" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1523" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62519,7 +62504,7 @@
         <v>1504</v>
       </c>
       <c r="H1523" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1523" s="6" t="s">
         <v>1180</v>
@@ -62528,7 +62513,7 @@
         <v>6456</v>
       </c>
       <c r="K1523" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1524" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62536,7 +62521,7 @@
         <v>1229</v>
       </c>
       <c r="B1524" s="6" t="s">
-        <v>1947</v>
+        <v>1942</v>
       </c>
       <c r="C1524" s="6" t="s">
         <v>17</v>
@@ -62555,7 +62540,7 @@
         <v>1504</v>
       </c>
       <c r="H1524" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1524" s="6" t="s">
         <v>1180</v>
@@ -62564,7 +62549,7 @@
         <v>6456</v>
       </c>
       <c r="K1524" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1525" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62572,7 +62557,7 @@
         <v>1424</v>
       </c>
       <c r="B1525" s="6" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
       <c r="C1525" s="6" t="s">
         <v>17</v>
@@ -62591,7 +62576,7 @@
         <v>1504</v>
       </c>
       <c r="H1525" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1525" s="6" t="s">
         <v>1180</v>
@@ -62600,7 +62585,7 @@
         <v>6456</v>
       </c>
       <c r="K1525" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1526" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62608,7 +62593,7 @@
         <v>1422</v>
       </c>
       <c r="B1526" s="6" t="s">
-        <v>2258</v>
+        <v>2253</v>
       </c>
       <c r="C1526" s="6" t="s">
         <v>17</v>
@@ -62627,7 +62612,7 @@
         <v>1504</v>
       </c>
       <c r="H1526" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1526" s="6" t="s">
         <v>1180</v>
@@ -62636,7 +62621,7 @@
         <v>6456</v>
       </c>
       <c r="K1526" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1527" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62644,7 +62629,7 @@
         <v>1252</v>
       </c>
       <c r="B1527" s="6" t="s">
-        <v>2259</v>
+        <v>2254</v>
       </c>
       <c r="C1527" s="6" t="s">
         <v>17</v>
@@ -62663,7 +62648,7 @@
         <v>1504</v>
       </c>
       <c r="H1527" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1527" s="6" t="s">
         <v>1180</v>
@@ -62672,15 +62657,15 @@
         <v>6456</v>
       </c>
       <c r="K1527" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1528" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1528" s="32" t="s">
-        <v>2260</v>
+        <v>2255</v>
       </c>
       <c r="B1528" s="6" t="s">
-        <v>2261</v>
+        <v>2256</v>
       </c>
       <c r="C1528" s="6" t="s">
         <v>17</v>
@@ -62699,7 +62684,7 @@
         <v>1504</v>
       </c>
       <c r="H1528" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1528" s="6" t="s">
         <v>1180</v>
@@ -62708,7 +62693,7 @@
         <v>6456</v>
       </c>
       <c r="K1528" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1529" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62716,7 +62701,7 @@
         <v>1254</v>
       </c>
       <c r="B1529" s="6" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="C1529" s="6" t="s">
         <v>17</v>
@@ -62735,7 +62720,7 @@
         <v>1504</v>
       </c>
       <c r="H1529" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1529" s="6" t="s">
         <v>1180</v>
@@ -62744,15 +62729,15 @@
         <v>6456</v>
       </c>
       <c r="K1529" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1530" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1530" s="32" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="B1530" s="6" t="s">
-        <v>2263</v>
+        <v>2258</v>
       </c>
       <c r="C1530" s="6" t="s">
         <v>17</v>
@@ -62771,7 +62756,7 @@
         <v>1504</v>
       </c>
       <c r="H1530" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1530" s="6" t="s">
         <v>1180</v>
@@ -62780,7 +62765,7 @@
         <v>6456</v>
       </c>
       <c r="K1530" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1531" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62788,7 +62773,7 @@
         <v>1210</v>
       </c>
       <c r="B1531" s="6" t="s">
-        <v>2264</v>
+        <v>2259</v>
       </c>
       <c r="C1531" s="6" t="s">
         <v>17</v>
@@ -62807,7 +62792,7 @@
         <v>1504</v>
       </c>
       <c r="H1531" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1531" s="6" t="s">
         <v>1180</v>
@@ -62816,7 +62801,7 @@
         <v>6457</v>
       </c>
       <c r="K1531" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1532" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62824,7 +62809,7 @@
         <v>1243</v>
       </c>
       <c r="B1532" s="6" t="s">
-        <v>2265</v>
+        <v>2260</v>
       </c>
       <c r="C1532" s="6" t="s">
         <v>17</v>
@@ -62843,7 +62828,7 @@
         <v>1504</v>
       </c>
       <c r="H1532" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1532" s="6" t="s">
         <v>1180</v>
@@ -62852,7 +62837,7 @@
         <v>6457</v>
       </c>
       <c r="K1532" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1533" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62860,7 +62845,7 @@
         <v>1197</v>
       </c>
       <c r="B1533" s="6" t="s">
-        <v>2266</v>
+        <v>2261</v>
       </c>
       <c r="C1533" s="6" t="s">
         <v>17</v>
@@ -62879,7 +62864,7 @@
         <v>1504</v>
       </c>
       <c r="H1533" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1533" s="6" t="s">
         <v>1180</v>
@@ -62888,15 +62873,15 @@
         <v>6457</v>
       </c>
       <c r="K1533" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1534" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1534" s="32" t="s">
-        <v>2267</v>
+        <v>2262</v>
       </c>
       <c r="B1534" s="6" t="s">
-        <v>2268</v>
+        <v>2263</v>
       </c>
       <c r="C1534" s="6" t="s">
         <v>17</v>
@@ -62915,7 +62900,7 @@
         <v>1504</v>
       </c>
       <c r="H1534" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1534" s="6" t="s">
         <v>1180</v>
@@ -62924,7 +62909,7 @@
         <v>6457</v>
       </c>
       <c r="K1534" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1535" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -62932,7 +62917,7 @@
         <v>1218</v>
       </c>
       <c r="B1535" s="6" t="s">
-        <v>2269</v>
+        <v>2264</v>
       </c>
       <c r="C1535" s="6" t="s">
         <v>17</v>
@@ -62951,7 +62936,7 @@
         <v>1504</v>
       </c>
       <c r="H1535" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1535" s="6" t="s">
         <v>1180</v>
@@ -62960,15 +62945,15 @@
         <v>6457</v>
       </c>
       <c r="K1535" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1536" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1536" s="32" t="s">
-        <v>2270</v>
+        <v>2265</v>
       </c>
       <c r="B1536" s="6" t="s">
-        <v>2271</v>
+        <v>2266</v>
       </c>
       <c r="C1536" s="6" t="s">
         <v>348</v>
@@ -62987,7 +62972,7 @@
         <v>1504</v>
       </c>
       <c r="H1536" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1536" s="6" t="s">
         <v>1180</v>
@@ -62996,15 +62981,15 @@
         <v>6457</v>
       </c>
       <c r="K1536" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1537" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1537" s="31" t="s">
-        <v>2272</v>
+        <v>2267</v>
       </c>
       <c r="B1537" s="6" t="s">
-        <v>2273</v>
+        <v>2268</v>
       </c>
       <c r="C1537" s="6" t="s">
         <v>17</v>
@@ -63023,7 +63008,7 @@
         <v>1505</v>
       </c>
       <c r="H1537" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1537" s="6" t="s">
         <v>1180</v>
@@ -63032,15 +63017,15 @@
         <v>6458</v>
       </c>
       <c r="K1537" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1538" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1538" s="32" t="s">
-        <v>2250</v>
+        <v>2245</v>
       </c>
       <c r="B1538" s="17" t="s">
-        <v>2274</v>
+        <v>2269</v>
       </c>
       <c r="C1538" s="6" t="s">
         <v>17</v>
@@ -63059,7 +63044,7 @@
         <v>1505</v>
       </c>
       <c r="H1538" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1538" s="6" t="s">
         <v>1180</v>
@@ -63068,7 +63053,7 @@
         <v>6458</v>
       </c>
       <c r="K1538" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1539" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63076,7 +63061,7 @@
         <v>1268</v>
       </c>
       <c r="B1539" s="6" t="s">
-        <v>2275</v>
+        <v>2270</v>
       </c>
       <c r="C1539" s="6" t="s">
         <v>17</v>
@@ -63095,7 +63080,7 @@
         <v>1505</v>
       </c>
       <c r="H1539" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1539" s="6" t="s">
         <v>1180</v>
@@ -63104,7 +63089,7 @@
         <v>6458</v>
       </c>
       <c r="K1539" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1540" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63112,7 +63097,7 @@
         <v>1272</v>
       </c>
       <c r="B1540" s="6" t="s">
-        <v>2276</v>
+        <v>2271</v>
       </c>
       <c r="C1540" s="6" t="s">
         <v>17</v>
@@ -63131,7 +63116,7 @@
         <v>1505</v>
       </c>
       <c r="H1540" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1540" s="6" t="s">
         <v>1180</v>
@@ -63140,7 +63125,7 @@
         <v>6458</v>
       </c>
       <c r="K1540" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1541" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63148,7 +63133,7 @@
         <v>1648</v>
       </c>
       <c r="B1541" s="6" t="s">
-        <v>2248</v>
+        <v>2243</v>
       </c>
       <c r="C1541" s="6" t="s">
         <v>17</v>
@@ -63167,7 +63152,7 @@
         <v>1505</v>
       </c>
       <c r="H1541" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1541" s="6" t="s">
         <v>1180</v>
@@ -63176,13 +63161,13 @@
         <v>6458</v>
       </c>
       <c r="K1541" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1542" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1542" s="43"/>
       <c r="B1542" s="18" t="s">
-        <v>2277</v>
+        <v>2272</v>
       </c>
       <c r="C1542" s="18" t="s">
         <v>17</v>
@@ -63201,7 +63186,7 @@
         <v>1505</v>
       </c>
       <c r="H1542" s="21" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1542" s="18" t="s">
         <v>1180</v>
@@ -63210,15 +63195,15 @@
         <v>6458</v>
       </c>
       <c r="K1542" s="21" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1543" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1543" s="32" t="s">
-        <v>2253</v>
+        <v>2248</v>
       </c>
       <c r="B1543" s="6" t="s">
-        <v>2278</v>
+        <v>2273</v>
       </c>
       <c r="C1543" s="6" t="s">
         <v>17</v>
@@ -63237,7 +63222,7 @@
         <v>1505</v>
       </c>
       <c r="H1543" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1543" s="6" t="s">
         <v>1180</v>
@@ -63246,15 +63231,15 @@
         <v>6458</v>
       </c>
       <c r="K1543" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1544" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1544" s="32" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="B1544" s="6" t="s">
-        <v>2279</v>
+        <v>2274</v>
       </c>
       <c r="C1544" s="6" t="s">
         <v>17</v>
@@ -63273,7 +63258,7 @@
         <v>1505</v>
       </c>
       <c r="H1544" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1544" s="6" t="s">
         <v>1180</v>
@@ -63282,7 +63267,7 @@
         <v>6458</v>
       </c>
       <c r="K1544" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1545" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63309,7 +63294,7 @@
         <v>1505</v>
       </c>
       <c r="H1545" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1545" s="6" t="s">
         <v>1180</v>
@@ -63318,7 +63303,7 @@
         <v>6458</v>
       </c>
       <c r="K1545" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1546" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63326,7 +63311,7 @@
         <v>1218</v>
       </c>
       <c r="B1546" s="6" t="s">
-        <v>2280</v>
+        <v>2275</v>
       </c>
       <c r="C1546" s="6" t="s">
         <v>17</v>
@@ -63345,7 +63330,7 @@
         <v>1505</v>
       </c>
       <c r="H1546" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1546" s="6" t="s">
         <v>1180</v>
@@ -63354,7 +63339,7 @@
         <v>6458</v>
       </c>
       <c r="K1546" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1547" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63381,7 +63366,7 @@
         <v>1505</v>
       </c>
       <c r="H1547" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1547" s="6" t="s">
         <v>1180</v>
@@ -63390,7 +63375,7 @@
         <v>6458</v>
       </c>
       <c r="K1547" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1548" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63398,7 +63383,7 @@
         <v>1197</v>
       </c>
       <c r="B1548" s="6" t="s">
-        <v>2266</v>
+        <v>2261</v>
       </c>
       <c r="C1548" s="6" t="s">
         <v>17</v>
@@ -63417,7 +63402,7 @@
         <v>1505</v>
       </c>
       <c r="H1548" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1548" s="6" t="s">
         <v>1180</v>
@@ -63426,7 +63411,7 @@
         <v>6458</v>
       </c>
       <c r="K1548" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1549" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63434,7 +63419,7 @@
         <v>1144</v>
       </c>
       <c r="B1549" s="6" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
       <c r="C1549" s="6" t="s">
         <v>17</v>
@@ -63453,7 +63438,7 @@
         <v>1505</v>
       </c>
       <c r="H1549" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1549" s="6" t="s">
         <v>1180</v>
@@ -63462,7 +63447,7 @@
         <v>6459</v>
       </c>
       <c r="K1549" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1550" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63470,7 +63455,7 @@
         <v>1223</v>
       </c>
       <c r="B1550" s="6" t="s">
-        <v>2268</v>
+        <v>2263</v>
       </c>
       <c r="C1550" s="6" t="s">
         <v>17</v>
@@ -63489,7 +63474,7 @@
         <v>1505</v>
       </c>
       <c r="H1550" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1550" s="6" t="s">
         <v>1180</v>
@@ -63498,7 +63483,7 @@
         <v>6459</v>
       </c>
       <c r="K1550" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1551" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63506,7 +63491,7 @@
         <v>1422</v>
       </c>
       <c r="B1551" s="6" t="s">
-        <v>2258</v>
+        <v>2253</v>
       </c>
       <c r="C1551" s="6" t="s">
         <v>17</v>
@@ -63525,7 +63510,7 @@
         <v>1505</v>
       </c>
       <c r="H1551" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1551" s="6" t="s">
         <v>1180</v>
@@ -63534,7 +63519,7 @@
         <v>6459</v>
       </c>
       <c r="K1551" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1552" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63561,7 +63546,7 @@
         <v>1505</v>
       </c>
       <c r="H1552" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1552" s="6" t="s">
         <v>1180</v>
@@ -63570,7 +63555,7 @@
         <v>6459</v>
       </c>
       <c r="K1552" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1553" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63578,7 +63563,7 @@
         <v>1264</v>
       </c>
       <c r="B1553" s="6" t="s">
-        <v>2282</v>
+        <v>2277</v>
       </c>
       <c r="C1553" s="6" t="s">
         <v>17</v>
@@ -63597,7 +63582,7 @@
         <v>1505</v>
       </c>
       <c r="H1553" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1553" s="6" t="s">
         <v>1180</v>
@@ -63606,15 +63591,15 @@
         <v>6459</v>
       </c>
       <c r="K1553" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1554" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1554" s="32" t="s">
-        <v>2283</v>
+        <v>2278</v>
       </c>
       <c r="B1554" s="6" t="s">
-        <v>2284</v>
+        <v>2279</v>
       </c>
       <c r="C1554" s="6" t="s">
         <v>348</v>
@@ -63633,7 +63618,7 @@
         <v>1505</v>
       </c>
       <c r="H1554" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1554" s="6" t="s">
         <v>1180</v>
@@ -63642,7 +63627,7 @@
         <v>6459</v>
       </c>
       <c r="K1554" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1555" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63669,7 +63654,7 @@
         <v>1505</v>
       </c>
       <c r="H1555" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1555" s="6" t="s">
         <v>1180</v>
@@ -63678,15 +63663,15 @@
         <v>6459</v>
       </c>
       <c r="K1555" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1556" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1556" s="32" t="s">
-        <v>2285</v>
+        <v>2280</v>
       </c>
       <c r="B1556" s="6" t="s">
-        <v>2286</v>
+        <v>2281</v>
       </c>
       <c r="C1556" s="6" t="s">
         <v>348</v>
@@ -63705,7 +63690,7 @@
         <v>1505</v>
       </c>
       <c r="H1556" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1556" s="6" t="s">
         <v>1180</v>
@@ -63714,7 +63699,7 @@
         <v>6459</v>
       </c>
       <c r="K1556" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1557" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63741,7 +63726,7 @@
         <v>1505</v>
       </c>
       <c r="H1557" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1557" s="6" t="s">
         <v>1180</v>
@@ -63750,7 +63735,7 @@
         <v>6459</v>
       </c>
       <c r="K1557" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1558" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63758,7 +63743,7 @@
         <v>344</v>
       </c>
       <c r="B1558" s="6" t="s">
-        <v>2287</v>
+        <v>2282</v>
       </c>
       <c r="C1558" s="6" t="s">
         <v>17</v>
@@ -63777,7 +63762,7 @@
         <v>1505</v>
       </c>
       <c r="H1558" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1558" s="6" t="s">
         <v>1180</v>
@@ -63786,15 +63771,15 @@
         <v>6459</v>
       </c>
       <c r="K1558" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1559" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1559" s="32" t="s">
-        <v>2288</v>
+        <v>2283</v>
       </c>
       <c r="B1559" s="6" t="s">
-        <v>2289</v>
+        <v>2284</v>
       </c>
       <c r="C1559" s="6" t="s">
         <v>348</v>
@@ -63813,7 +63798,7 @@
         <v>1505</v>
       </c>
       <c r="H1559" s="12" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="I1559" s="6" t="s">
         <v>1180</v>
@@ -63822,7 +63807,7 @@
         <v>6459</v>
       </c>
       <c r="K1559" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1560" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63830,7 +63815,7 @@
         <v>224</v>
       </c>
       <c r="B1560" s="6" t="s">
-        <v>2290</v>
+        <v>2285</v>
       </c>
       <c r="C1560" s="6" t="s">
         <v>17</v>
@@ -63849,7 +63834,7 @@
         <v>1567</v>
       </c>
       <c r="H1560" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="I1560" s="6" t="s">
         <v>799</v>
@@ -63858,7 +63843,7 @@
         <v>6461</v>
       </c>
       <c r="K1560" s="12" t="s">
-        <v>2291</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1561" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63866,7 +63851,7 @@
         <v>225</v>
       </c>
       <c r="B1561" s="6" t="s">
-        <v>2292</v>
+        <v>2287</v>
       </c>
       <c r="C1561" s="6" t="s">
         <v>17</v>
@@ -63885,7 +63870,7 @@
         <v>1567</v>
       </c>
       <c r="H1561" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="I1561" s="6" t="s">
         <v>799</v>
@@ -63894,7 +63879,7 @@
         <v>6461</v>
       </c>
       <c r="K1561" s="12" t="s">
-        <v>2291</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1562" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63902,7 +63887,7 @@
         <v>723</v>
       </c>
       <c r="B1562" s="6" t="s">
-        <v>1795</v>
+        <v>1790</v>
       </c>
       <c r="C1562" s="6" t="s">
         <v>17</v>
@@ -63921,7 +63906,7 @@
         <v>2524</v>
       </c>
       <c r="H1562" s="12" t="s">
-        <v>2293</v>
+        <v>2288</v>
       </c>
       <c r="I1562" s="6" t="s">
         <v>528</v>
@@ -63930,7 +63915,7 @@
         <v>6462</v>
       </c>
       <c r="K1562" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1563" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63957,7 +63942,7 @@
         <v>4665</v>
       </c>
       <c r="H1563" s="12" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="I1563" s="6" t="s">
         <v>1286</v>
@@ -63966,7 +63951,7 @@
         <v>6463</v>
       </c>
       <c r="K1563" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1564" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -63993,7 +63978,7 @@
         <v>4665</v>
       </c>
       <c r="H1564" s="12" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="I1564" s="6" t="s">
         <v>1286</v>
@@ -64002,15 +63987,15 @@
         <v>6463</v>
       </c>
       <c r="K1564" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1565" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1565" s="32" t="s">
-        <v>2296</v>
+        <v>2291</v>
       </c>
       <c r="B1565" s="6" t="s">
-        <v>2297</v>
+        <v>2292</v>
       </c>
       <c r="C1565" s="6" t="s">
         <v>17</v>
@@ -64029,7 +64014,7 @@
         <v>4665</v>
       </c>
       <c r="H1565" s="12" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="I1565" s="6" t="s">
         <v>1286</v>
@@ -64038,15 +64023,15 @@
         <v>6463</v>
       </c>
       <c r="K1565" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1566" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1566" s="32" t="s">
-        <v>2298</v>
+        <v>2293</v>
       </c>
       <c r="B1566" s="6" t="s">
-        <v>2299</v>
+        <v>2294</v>
       </c>
       <c r="C1566" s="6" t="s">
         <v>17</v>
@@ -64065,7 +64050,7 @@
         <v>4665</v>
       </c>
       <c r="H1566" s="12" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="I1566" s="6" t="s">
         <v>1286</v>
@@ -64074,15 +64059,15 @@
         <v>6463</v>
       </c>
       <c r="K1566" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1567" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1567" s="31" t="s">
-        <v>2300</v>
+        <v>2295</v>
       </c>
       <c r="B1567" s="6" t="s">
-        <v>2301</v>
+        <v>2296</v>
       </c>
       <c r="C1567" s="6" t="s">
         <v>17</v>
@@ -64101,7 +64086,7 @@
         <v>4665</v>
       </c>
       <c r="H1567" s="12" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="I1567" s="6" t="s">
         <v>1286</v>
@@ -64110,15 +64095,15 @@
         <v>6463</v>
       </c>
       <c r="K1567" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1568" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1568" s="32" t="s">
-        <v>2302</v>
+        <v>2297</v>
       </c>
       <c r="B1568" s="6" t="s">
-        <v>2303</v>
+        <v>2298</v>
       </c>
       <c r="C1568" s="6" t="s">
         <v>17</v>
@@ -64137,7 +64122,7 @@
         <v>4665</v>
       </c>
       <c r="H1568" s="12" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="I1568" s="6" t="s">
         <v>1286</v>
@@ -64146,15 +64131,15 @@
         <v>6463</v>
       </c>
       <c r="K1568" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1569" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1569" s="34" t="s">
-        <v>2304</v>
+        <v>2299</v>
       </c>
       <c r="B1569" s="6" t="s">
-        <v>2305</v>
+        <v>2300</v>
       </c>
       <c r="C1569" s="6" t="s">
         <v>17</v>
@@ -64173,7 +64158,7 @@
         <v>4665</v>
       </c>
       <c r="H1569" s="12" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="I1569" s="6" t="s">
         <v>1286</v>
@@ -64182,15 +64167,15 @@
         <v>6463</v>
       </c>
       <c r="K1569" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1570" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1570" s="31" t="s">
-        <v>2306</v>
+        <v>2301</v>
       </c>
       <c r="B1570" s="6" t="s">
-        <v>2307</v>
+        <v>2302</v>
       </c>
       <c r="C1570" s="6" t="s">
         <v>17</v>
@@ -64218,13 +64203,13 @@
         <v>6463</v>
       </c>
       <c r="K1570" s="12" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1571" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1571" s="44"/>
       <c r="B1571" s="6" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="C1571" s="6" t="s">
         <v>348</v>
@@ -64243,22 +64228,22 @@
         <v>38</v>
       </c>
       <c r="H1571" s="12" t="s">
-        <v>2309</v>
+        <v>2304</v>
       </c>
       <c r="I1571" s="6" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="J1571" s="6">
         <v>6454</v>
       </c>
       <c r="K1571" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1572" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1572" s="44"/>
       <c r="B1572" s="6" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
       <c r="C1572" s="6" t="s">
         <v>348</v>
@@ -64277,22 +64262,22 @@
         <v>38</v>
       </c>
       <c r="H1572" s="12" t="s">
-        <v>2309</v>
+        <v>2304</v>
       </c>
       <c r="I1572" s="6" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="J1572" s="6">
         <v>6454</v>
       </c>
       <c r="K1572" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1573" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1573" s="44"/>
       <c r="B1573" s="6" t="s">
-        <v>2312</v>
+        <v>2307</v>
       </c>
       <c r="C1573" s="6" t="s">
         <v>348</v>
@@ -64311,22 +64296,22 @@
         <v>38</v>
       </c>
       <c r="H1573" s="12" t="s">
-        <v>2309</v>
+        <v>2304</v>
       </c>
       <c r="I1573" s="6" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="J1573" s="6">
         <v>6454</v>
       </c>
       <c r="K1573" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1574" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1574" s="44"/>
       <c r="B1574" s="6" t="s">
-        <v>2313</v>
+        <v>2308</v>
       </c>
       <c r="C1574" s="6" t="s">
         <v>348</v>
@@ -64345,16 +64330,16 @@
         <v>38</v>
       </c>
       <c r="H1574" s="12" t="s">
-        <v>2309</v>
+        <v>2304</v>
       </c>
       <c r="I1574" s="6" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="J1574" s="6">
         <v>6454</v>
       </c>
       <c r="K1574" s="12" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1575" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A447340E-66E0-4B74-A4F3-CD1B2BF3AB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76032464-E053-4BC7-9329-7AE4BCCB2EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8376" uniqueCount="2343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8378" uniqueCount="2344">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -7066,6 +7066,9 @@
   </si>
   <si>
     <t>SALINV-01-01-26250</t>
+  </si>
+  <si>
+    <t>4667</t>
   </si>
 </sst>
 </file>
@@ -12738,8 +12741,8 @@
         <f t="shared" si="2"/>
         <v>6900</v>
       </c>
-      <c r="G134" s="42">
-        <v>40667</v>
+      <c r="G134" s="42" t="s">
+        <v>2343</v>
       </c>
       <c r="H134" s="11" t="s">
         <v>152</v>
@@ -12774,8 +12777,8 @@
         <f t="shared" si="2"/>
         <v>1350</v>
       </c>
-      <c r="G135" s="42">
-        <v>40667</v>
+      <c r="G135" s="42" t="s">
+        <v>2343</v>
       </c>
       <c r="H135" s="11" t="s">
         <v>152</v>
@@ -62146,14 +62149,14 @@
         <v>17</v>
       </c>
       <c r="D1508" s="6">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="E1508" s="6">
         <v>936</v>
       </c>
       <c r="F1508" s="63">
         <f t="shared" si="23"/>
-        <v>76752</v>
+        <v>26208</v>
       </c>
       <c r="G1508" s="42">
         <v>138</v>
@@ -64576,7 +64579,7 @@
     <row r="1576" spans="1:11" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F1576" s="67">
         <f>SUM(F2:F1575)</f>
-        <v>31323125.786196016</v>
+        <v>31272581.786196016</v>
       </c>
     </row>
   </sheetData>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76032464-E053-4BC7-9329-7AE4BCCB2EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10065211-AC79-4B08-9724-B58FD3835F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59107,14 +59107,14 @@
         <v>40</v>
       </c>
       <c r="D1423" s="6">
-        <v>52400</v>
+        <v>52.4</v>
       </c>
       <c r="E1423" s="6">
         <v>90</v>
       </c>
       <c r="F1423" s="63">
         <f t="shared" si="22"/>
-        <v>4716000</v>
+        <v>4716</v>
       </c>
       <c r="G1423" s="42">
         <v>13910</v>
@@ -64579,7 +64579,7 @@
     <row r="1576" spans="1:11" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F1576" s="67">
         <f>SUM(F2:F1575)</f>
-        <v>31272581.786196016</v>
+        <v>26561297.786196016</v>
       </c>
     </row>
   </sheetData>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590BD02C-2945-4DE5-892A-58A80FA2AC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56A6023-71DF-4007-9AE5-C1A077E83A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7083,9 +7083,6 @@
     <t>DH004497-26</t>
   </si>
   <si>
-    <t>RAW-M-2026-0001755</t>
-  </si>
-  <si>
     <t>ES001379-26</t>
   </si>
   <si>
@@ -7098,7 +7095,10 @@
     <t>6263</t>
   </si>
   <si>
-    <t>RAW-S-2026-000080</t>
+    <t>RAW/S/2026/000080</t>
+  </si>
+  <si>
+    <t>RAW/M/2026/0001755</t>
   </si>
 </sst>
 </file>
@@ -7955,7 +7955,7 @@
     <col min="4" max="4" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" style="66" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.85546875" style="49" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="49" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" style="60" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30.42578125" style="49" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" style="49" bestFit="1" customWidth="1"/>
@@ -35361,7 +35361,7 @@
     <row r="762" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A762" s="25"/>
       <c r="B762" s="42" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="C762" s="42" t="s">
         <v>17</v>
@@ -35377,7 +35377,7 @@
         <v>12631.6</v>
       </c>
       <c r="G762" s="42" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H762" s="11" t="s">
         <v>1284</v>
@@ -35395,7 +35395,7 @@
     <row r="763" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A763" s="25"/>
       <c r="B763" s="42" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="C763" s="42" t="s">
         <v>17</v>
@@ -35411,7 +35411,7 @@
         <v>965</v>
       </c>
       <c r="G763" s="42" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H763" s="11">
         <v>46297</v>
@@ -35420,7 +35420,7 @@
         <v>1285</v>
       </c>
       <c r="J763" s="42" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="K763" s="11" t="s">
         <v>1286</v>
@@ -35447,7 +35447,7 @@
         <v>41650</v>
       </c>
       <c r="G764" s="42" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H764" s="11" t="s">
         <v>1284</v>
@@ -35483,7 +35483,7 @@
         <v>960</v>
       </c>
       <c r="G765" s="42" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H765" s="11" t="s">
         <v>1284</v>
@@ -35519,7 +35519,7 @@
         <v>49980</v>
       </c>
       <c r="G766" s="42" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H766" s="11" t="s">
         <v>1284</v>
@@ -35555,7 +35555,7 @@
         <v>58100</v>
       </c>
       <c r="G767" s="42" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H767" s="11" t="s">
         <v>1284</v>
@@ -35591,7 +35591,7 @@
         <v>14450</v>
       </c>
       <c r="G768" s="42" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H768" s="11" t="s">
         <v>1284</v>
@@ -42630,11 +42630,11 @@
         <v>5</v>
       </c>
       <c r="E964" s="6">
-        <v>26116.6</v>
+        <v>2476</v>
       </c>
       <c r="F964" s="63">
         <f t="shared" ref="F964:F1027" si="15">E964*D964</f>
-        <v>130583</v>
+        <v>12380</v>
       </c>
       <c r="G964" s="42">
         <v>2461</v>
@@ -46273,7 +46273,7 @@
         <v>1429</v>
       </c>
       <c r="G1065" s="48" t="s">
-        <v>2348</v>
+        <v>2353</v>
       </c>
       <c r="H1065" s="20" t="s">
         <v>1631</v>
@@ -46309,7 +46309,7 @@
         <v>3591</v>
       </c>
       <c r="G1066" s="48" t="s">
-        <v>2348</v>
+        <v>2353</v>
       </c>
       <c r="H1066" s="20" t="s">
         <v>1631</v>
@@ -46345,7 +46345,7 @@
         <v>24746</v>
       </c>
       <c r="G1067" s="48" t="s">
-        <v>2348</v>
+        <v>2353</v>
       </c>
       <c r="H1067" s="20" t="s">
         <v>1631</v>
@@ -46381,7 +46381,7 @@
         <v>856</v>
       </c>
       <c r="G1068" s="48" t="s">
-        <v>2348</v>
+        <v>2353</v>
       </c>
       <c r="H1068" s="20" t="s">
         <v>1631</v>
@@ -47603,7 +47603,7 @@
         <v>152775</v>
       </c>
       <c r="G1102" s="42" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="H1102" s="11">
         <v>46117</v>
@@ -47639,7 +47639,7 @@
         <v>43125</v>
       </c>
       <c r="G1103" s="42" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="H1103" s="11">
         <v>46117</v>
@@ -47675,7 +47675,7 @@
         <v>3300</v>
       </c>
       <c r="G1104" s="42" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="H1104" s="11">
         <v>46117</v>
@@ -47711,7 +47711,7 @@
         <v>580</v>
       </c>
       <c r="G1105" s="42" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="H1105" s="11">
         <v>46117</v>
@@ -47747,7 +47747,7 @@
         <v>220</v>
       </c>
       <c r="G1106" s="42" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="H1106" s="11">
         <v>46117</v>
@@ -64603,7 +64603,7 @@
     <row r="1576" spans="1:11" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F1576" s="67">
         <f>SUM(F2:F1575)</f>
-        <v>26124894.386196017</v>
+        <v>26006691.386196017</v>
       </c>
     </row>
   </sheetData>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56A6023-71DF-4007-9AE5-C1A077E83A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1404FAAB-8975-4C67-B2DE-EBA265FA7649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31455,7 +31455,7 @@
         <v>1990</v>
       </c>
       <c r="G653" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H653" s="11" t="s">
         <v>1148</v>
@@ -31491,7 +31491,7 @@
         <v>789.75</v>
       </c>
       <c r="G654" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H654" s="11" t="s">
         <v>1148</v>
@@ -31527,7 +31527,7 @@
         <v>526.5</v>
       </c>
       <c r="G655" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H655" s="11" t="s">
         <v>1148</v>
@@ -31563,7 +31563,7 @@
         <v>6142.5</v>
       </c>
       <c r="G656" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H656" s="11" t="s">
         <v>1148</v>
@@ -31599,7 +31599,7 @@
         <v>99.54</v>
       </c>
       <c r="G657" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H657" s="11" t="s">
         <v>1148</v>
@@ -31635,7 +31635,7 @@
         <v>10750.320000000002</v>
       </c>
       <c r="G658" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H658" s="11" t="s">
         <v>1148</v>
@@ -31671,7 +31671,7 @@
         <v>2340</v>
       </c>
       <c r="G659" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H659" s="11" t="s">
         <v>1148</v>
@@ -31707,7 +31707,7 @@
         <v>351</v>
       </c>
       <c r="G660" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H660" s="11" t="s">
         <v>1148</v>
@@ -31743,7 +31743,7 @@
         <v>2290.62</v>
       </c>
       <c r="G661" s="42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H661" s="11" t="s">
         <v>1148</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1404FAAB-8975-4C67-B2DE-EBA265FA7649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D9812B-44E9-4859-BC35-C3C75FDF4D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8400" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8408" uniqueCount="2355">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -7099,6 +7099,9 @@
   </si>
   <si>
     <t>RAW/M/2026/0001755</t>
+  </si>
+  <si>
+    <t>HQ89598</t>
   </si>
 </sst>
 </file>
@@ -7957,7 +7960,7 @@
     <col min="6" max="6" width="19.7109375" style="66" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.28515625" style="49" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.42578125" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.5703125" style="49" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" style="49" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="60" bestFit="1" customWidth="1"/>
   </cols>
@@ -31814,14 +31817,14 @@
         <f t="shared" si="10"/>
         <v>3215</v>
       </c>
-      <c r="G663" s="42">
-        <v>89598</v>
+      <c r="G663" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H663" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I663" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J663" s="42">
         <v>6250</v>
@@ -31850,14 +31853,14 @@
         <f t="shared" si="10"/>
         <v>346</v>
       </c>
-      <c r="G664" s="42">
-        <v>89598</v>
+      <c r="G664" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H664" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I664" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J664" s="42">
         <v>6250</v>
@@ -31886,14 +31889,14 @@
         <f t="shared" si="10"/>
         <v>354</v>
       </c>
-      <c r="G665" s="42">
-        <v>89598</v>
+      <c r="G665" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H665" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I665" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J665" s="42">
         <v>6250</v>
@@ -31922,14 +31925,14 @@
         <f t="shared" si="10"/>
         <v>1218</v>
       </c>
-      <c r="G666" s="42">
-        <v>89598</v>
+      <c r="G666" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H666" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I666" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J666" s="42">
         <v>6250</v>
@@ -31958,14 +31961,14 @@
         <f t="shared" si="10"/>
         <v>346</v>
       </c>
-      <c r="G667" s="42">
-        <v>89598</v>
+      <c r="G667" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H667" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I667" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J667" s="42">
         <v>6250</v>
@@ -31994,14 +31997,14 @@
         <f t="shared" si="10"/>
         <v>1105</v>
       </c>
-      <c r="G668" s="42">
-        <v>89598</v>
+      <c r="G668" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H668" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I668" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J668" s="42">
         <v>6250</v>
@@ -32030,14 +32033,14 @@
         <f t="shared" si="10"/>
         <v>1057</v>
       </c>
-      <c r="G669" s="42">
-        <v>89598</v>
+      <c r="G669" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H669" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I669" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J669" s="42">
         <v>6250</v>
@@ -32066,14 +32069,14 @@
         <f t="shared" si="10"/>
         <v>362</v>
       </c>
-      <c r="G670" s="42">
-        <v>89598</v>
+      <c r="G670" s="42" t="s">
+        <v>2354</v>
       </c>
       <c r="H670" s="11" t="s">
         <v>1164</v>
       </c>
       <c r="I670" s="42" t="s">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="J670" s="42">
         <v>6250</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D9812B-44E9-4859-BC35-C3C75FDF4D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278CBBD1-E3B1-44DF-A41C-49EA7C89E59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7101,7 +7101,7 @@
     <t>RAW/M/2026/0001755</t>
   </si>
   <si>
-    <t>HQ89598</t>
+    <t>3HQ89598</t>
   </si>
 </sst>
 </file>
